--- a/research/traditional_assets/database/data/china/china_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/china/china_bank_money_center.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.047</v>
+        <v>0.05880000000000001</v>
       </c>
       <c r="E2">
-        <v>0.0552</v>
+        <v>0.0567</v>
       </c>
       <c r="F2">
-        <v>0.0617</v>
+        <v>0.0407</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,103 +603,97 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.0005502702740185986</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>0.0004697849845759615</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>273995.3</v>
+        <v>267445.5</v>
       </c>
       <c r="L2">
-        <v>0.4564040077623327</v>
+        <v>0.4463663713984245</v>
       </c>
       <c r="M2">
-        <v>69526.95600000001</v>
+        <v>74096.27800000001</v>
       </c>
       <c r="N2">
-        <v>0.05200623683284383</v>
+        <v>0.064349581506964</v>
       </c>
       <c r="O2">
-        <v>0.2537523672851323</v>
+        <v>0.2770518778592274</v>
       </c>
       <c r="P2">
-        <v>63763.356</v>
+        <v>70276.878</v>
       </c>
       <c r="Q2">
-        <v>0.04769505791959213</v>
+        <v>0.06103258909868543</v>
       </c>
       <c r="R2">
-        <v>0.2327169699626234</v>
+        <v>0.2627708374229516</v>
       </c>
       <c r="S2">
-        <v>5763.6</v>
+        <v>3819.4</v>
       </c>
       <c r="T2">
-        <v>0.08289734416101864</v>
+        <v>0.05154644879733365</v>
       </c>
       <c r="U2">
-        <v>1201688</v>
+        <v>1221706.3</v>
       </c>
       <c r="V2">
-        <v>0.8988638985890082</v>
+        <v>1.061001864755223</v>
       </c>
       <c r="W2">
-        <v>0.1214565560078931</v>
+        <v>0.1003176154409968</v>
       </c>
       <c r="X2">
-        <v>0.1373069058772343</v>
+        <v>0.2114570373466015</v>
       </c>
       <c r="Y2">
-        <v>-0.01585034986934118</v>
+        <v>-0.1111394219056047</v>
       </c>
       <c r="Z2">
-        <v>0.1257501769501143</v>
+        <v>0.1079023598660635</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.0460176972250918</v>
+        <v>0.07153320962178572</v>
       </c>
       <c r="AC2">
-        <v>-0.04587883677531512</v>
+        <v>-0.07153320962178572</v>
       </c>
       <c r="AD2">
-        <v>4097327.9</v>
+        <v>4124134.4</v>
       </c>
       <c r="AE2">
-        <v>5024.967475235224</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>4102352.867475235</v>
+        <v>4124134.4</v>
       </c>
       <c r="AG2">
-        <v>2900664.867475235</v>
+        <v>2902428.1</v>
       </c>
       <c r="AH2">
-        <v>0.7542130522652329</v>
+        <v>0.781737627073717</v>
       </c>
       <c r="AI2">
-        <v>0.6031627869535677</v>
+        <v>0.6056696883273074</v>
       </c>
       <c r="AJ2">
-        <v>0.6845127694760604</v>
+        <v>0.7159607250601021</v>
       </c>
       <c r="AK2">
-        <v>0.518002281066854</v>
+        <v>0.519449521991693</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
         <v>0</v>
-      </c>
-      <c r="AN2">
-        <v>3068.378016085791</v>
-      </c>
-      <c r="AP2">
-        <v>2172.229445291263</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Zhejiang Shaoxing RuiFeng Rural Commercial Bank Co.,Ltd (SHSE:601528)</t>
+          <t>Bank of Shanghai Co., Ltd. (SHSE:601229)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,10 +713,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0519</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="E3">
-        <v>0.0902</v>
+        <v>0.0843</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -731,34 +725,34 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.004764109709660792</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>0.004476376350958506</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>187.4</v>
+        <v>3171.8</v>
       </c>
       <c r="L3">
-        <v>0.517822602928986</v>
+        <v>0.6058603300733497</v>
       </c>
       <c r="M3">
-        <v>33.1</v>
+        <v>795.5752000000001</v>
       </c>
       <c r="N3">
-        <v>0.01235028543711056</v>
+        <v>0.06535464791509217</v>
       </c>
       <c r="O3">
-        <v>0.1766275346851654</v>
+        <v>0.2508276688315783</v>
       </c>
       <c r="P3">
-        <v>33.1</v>
+        <v>795.5752000000001</v>
       </c>
       <c r="Q3">
-        <v>0.01235028543711056</v>
+        <v>0.06535464791509217</v>
       </c>
       <c r="R3">
-        <v>0.1766275346851654</v>
+        <v>0.2508276688315783</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -767,61 +761,61 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1457.4</v>
+        <v>9534.1</v>
       </c>
       <c r="V3">
-        <v>0.5437856796388195</v>
+        <v>0.783204087667992</v>
+      </c>
+      <c r="W3">
+        <v>0.1132551114412015</v>
       </c>
       <c r="X3">
-        <v>0.06874409400765759</v>
+        <v>0.2261901369685548</v>
+      </c>
+      <c r="Y3">
+        <v>-0.1129350255273533</v>
       </c>
       <c r="Z3">
-        <v>42.18271489282338</v>
+        <v>0.05695133267554428</v>
       </c>
       <c r="AA3">
-        <v>0.1888257073654597</v>
+        <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.0460176972250918</v>
+        <v>0.06628411852907684</v>
       </c>
       <c r="AC3">
-        <v>0.1428080101403679</v>
+        <v>-0.06628411852907684</v>
       </c>
       <c r="AD3">
-        <v>3325.4</v>
+        <v>79981.3</v>
       </c>
       <c r="AE3">
-        <v>8.579343480368797</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>3333.979343480369</v>
+        <v>79981.3</v>
       </c>
       <c r="AG3">
-        <v>1876.579343480369</v>
+        <v>70447.2</v>
       </c>
       <c r="AH3">
-        <v>0.5543623808512947</v>
+        <v>0.8679044430819982</v>
       </c>
       <c r="AI3">
-        <v>0.6156047231676609</v>
+        <v>0.723770094971789</v>
       </c>
       <c r="AJ3">
-        <v>0.4118304585477035</v>
+        <v>0.8526610861240081</v>
       </c>
       <c r="AK3">
-        <v>0.4740776920663706</v>
+        <v>0.6976876849515313</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
         <v>0</v>
-      </c>
-      <c r="AN3">
-        <v>966.686046511628</v>
-      </c>
-      <c r="AP3">
-        <v>545.5172510117351</v>
       </c>
     </row>
     <row r="4">
@@ -832,7 +826,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bank of Shanghai Co., Ltd. (SHSE:601229)</t>
+          <t>Bank of Beijing Co., Ltd. (SHSE:601169)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -841,10 +835,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0738</v>
+        <v>0.04190000000000001</v>
       </c>
       <c r="E4">
-        <v>0.0993</v>
+        <v>0.04969999999999999</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -853,34 +847,34 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0.008303264007259828</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>0.007704407302879038</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>3487.9</v>
+        <v>3289.7</v>
       </c>
       <c r="L4">
-        <v>0.6314884217768363</v>
+        <v>0.5226225653734947</v>
       </c>
       <c r="M4">
-        <v>9.119999999999999</v>
+        <v>8.15</v>
       </c>
       <c r="N4">
-        <v>0.0005719589594360685</v>
+        <v>0.0006168634574629125</v>
       </c>
       <c r="O4">
-        <v>0.002614753863356174</v>
+        <v>0.002477429552846764</v>
       </c>
       <c r="P4">
-        <v>9.119999999999999</v>
+        <v>8.15</v>
       </c>
       <c r="Q4">
-        <v>0.0005719589594360685</v>
+        <v>0.0006168634574629125</v>
       </c>
       <c r="R4">
-        <v>0.002614753863356174</v>
+        <v>0.002477429552846764</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -889,67 +883,61 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>11337.7</v>
+        <v>22319.3</v>
       </c>
       <c r="V4">
-        <v>0.7110415673682362</v>
+        <v>1.689320314865274</v>
       </c>
       <c r="W4">
-        <v>0.1419501613671234</v>
+        <v>0.09938520566154589</v>
       </c>
       <c r="X4">
-        <v>0.1373069058772343</v>
+        <v>0.2223952204158292</v>
       </c>
       <c r="Y4">
-        <v>0.004643255489889114</v>
+        <v>-0.1230100147542833</v>
       </c>
       <c r="Z4">
-        <v>0.06020392167346776</v>
+        <v>0.05849902139183545</v>
       </c>
       <c r="AA4">
-        <v>0.0004638355338030226</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.04282095636387204</v>
+        <v>0.06629769086120871</v>
       </c>
       <c r="AC4">
-        <v>-0.04235712083006901</v>
+        <v>-0.06629769086120871</v>
       </c>
       <c r="AD4">
-        <v>72102.39999999999</v>
+        <v>84691.8</v>
       </c>
       <c r="AE4">
-        <v>257.692909543509</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>72360.0929095435</v>
+        <v>84691.8</v>
       </c>
       <c r="AG4">
-        <v>61022.3929095435</v>
+        <v>62372.5</v>
       </c>
       <c r="AH4">
-        <v>0.8194309822817344</v>
+        <v>0.8650512033240794</v>
       </c>
       <c r="AI4">
-        <v>0.6984201389277114</v>
+        <v>0.6606750303066234</v>
       </c>
       <c r="AJ4">
-        <v>0.7928322895749168</v>
+        <v>0.8252022570765171</v>
       </c>
       <c r="AK4">
-        <v>0.6613625092952962</v>
+        <v>0.5891395620120808</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
         <v>0</v>
-      </c>
-      <c r="AN4">
-        <v>740.2710472279259</v>
-      </c>
-      <c r="AP4">
-        <v>626.5132742252925</v>
       </c>
     </row>
     <row r="5">
@@ -960,7 +948,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bank of Beijing Co., Ltd. (SHSE:601169)</t>
+          <t>Industrial Bank Co., Ltd. (SHSE:601166)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -969,10 +957,13 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0377</v>
+        <v>0.103</v>
       </c>
       <c r="E5">
-        <v>0.0552</v>
+        <v>0.09669999999999999</v>
+      </c>
+      <c r="F5">
+        <v>0.105</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -981,34 +972,34 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0.006999124538148191</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>0.006278416752322578</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>3583.9</v>
+        <v>12713.8</v>
       </c>
       <c r="L5">
-        <v>0.5378324029053364</v>
+        <v>0.526412110070471</v>
       </c>
       <c r="M5">
-        <v>993.721</v>
+        <v>3012.259</v>
       </c>
       <c r="N5">
-        <v>0.06724599726609552</v>
+        <v>0.05685588687179836</v>
       </c>
       <c r="O5">
-        <v>0.2772736404475571</v>
+        <v>0.2369282983844327</v>
       </c>
       <c r="P5">
-        <v>993.721</v>
+        <v>3012.259</v>
       </c>
       <c r="Q5">
-        <v>0.06724599726609552</v>
+        <v>0.05685588687179836</v>
       </c>
       <c r="R5">
-        <v>0.2772736404475571</v>
+        <v>0.2369282983844327</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1017,67 +1008,61 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>27410.2</v>
+        <v>55016.4</v>
       </c>
       <c r="V5">
-        <v>1.854872981715322</v>
+        <v>1.03842538589597</v>
       </c>
       <c r="W5">
-        <v>0.1242029166320109</v>
+        <v>0.1347563134230592</v>
       </c>
       <c r="X5">
-        <v>0.1835455436331779</v>
+        <v>0.1839164729599142</v>
       </c>
       <c r="Y5">
-        <v>-0.05934262700116706</v>
+        <v>-0.04916015953685501</v>
       </c>
       <c r="Z5">
-        <v>0.07160941480821718</v>
+        <v>0.07437309539001238</v>
       </c>
       <c r="AA5">
-        <v>0.0004495937495559273</v>
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.04281899844644542</v>
+        <v>0.06647770634259816</v>
       </c>
       <c r="AC5">
-        <v>-0.04236940469688949</v>
+        <v>-0.06647770634259816</v>
       </c>
       <c r="AD5">
-        <v>99143</v>
+        <v>253633.4</v>
       </c>
       <c r="AE5">
-        <v>745.8031686379786</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>99888.80316863798</v>
+        <v>253633.4</v>
       </c>
       <c r="AG5">
-        <v>72478.60316863799</v>
+        <v>198617</v>
       </c>
       <c r="AH5">
-        <v>0.8711268046586745</v>
+        <v>0.8272074986791209</v>
       </c>
       <c r="AI5">
-        <v>0.7341105011068568</v>
+        <v>0.7090864054500763</v>
       </c>
       <c r="AJ5">
-        <v>0.8306431710900166</v>
+        <v>0.7894232695383422</v>
       </c>
       <c r="AK5">
-        <v>0.6670366458953662</v>
+        <v>0.6562076689771834</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
         <v>0</v>
-      </c>
-      <c r="AN5">
-        <v>506.3483146067416</v>
-      </c>
-      <c r="AP5">
-        <v>370.166512607957</v>
       </c>
     </row>
     <row r="6">
@@ -1088,7 +1073,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Industrial Bank Co., Ltd. (SHSE:601166)</t>
+          <t>Bank of China Limited (SEHK:3988)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1097,13 +1082,13 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.06370000000000001</v>
+        <v>0.0509</v>
       </c>
       <c r="E6">
-        <v>0.0827</v>
+        <v>0.05230000000000001</v>
       </c>
       <c r="F6">
-        <v>0.09359999999999999</v>
+        <v>0.0378</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1112,34 +1097,34 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>-0.002424772387331528</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>-0.002095054508399085</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>12226</v>
+        <v>31783.5</v>
       </c>
       <c r="L6">
-        <v>0.540748538218617</v>
+        <v>0.4372592449922958</v>
       </c>
       <c r="M6">
-        <v>1162.1</v>
+        <v>9145.700000000001</v>
       </c>
       <c r="N6">
-        <v>0.01866395564720771</v>
+        <v>0.07200102659543481</v>
       </c>
       <c r="O6">
-        <v>0.09505152952723703</v>
+        <v>0.2877499331414099</v>
       </c>
       <c r="P6">
-        <v>1162.1</v>
+        <v>9145.700000000001</v>
       </c>
       <c r="Q6">
-        <v>0.01866395564720771</v>
+        <v>0.07200102659543481</v>
       </c>
       <c r="R6">
-        <v>0.09505152952723703</v>
+        <v>0.2877499331414099</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1148,67 +1133,61 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>57329.6</v>
+        <v>119186.4</v>
       </c>
       <c r="V6">
-        <v>0.9207444382343682</v>
+        <v>0.9383145255381359</v>
       </c>
       <c r="W6">
-        <v>0.1620082342480584</v>
+        <v>0.09480471871483059</v>
       </c>
       <c r="X6">
-        <v>0.1366577392067578</v>
+        <v>0.2114570373466015</v>
       </c>
       <c r="Y6">
-        <v>0.0253504950413006</v>
+        <v>-0.1166523186317709</v>
       </c>
       <c r="Z6">
-        <v>0.08487371602446542</v>
+        <v>0.06775344858603079</v>
       </c>
       <c r="AA6">
-        <v>-0.0001778150614016399</v>
+        <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.04282099509667699</v>
+        <v>0.07000010151982883</v>
       </c>
       <c r="AC6">
-        <v>-0.04299881015807863</v>
+        <v>-0.07000010151982883</v>
       </c>
       <c r="AD6">
-        <v>279138.8</v>
+        <v>755636.8</v>
       </c>
       <c r="AE6">
-        <v>1478.113244070667</v>
+        <v>0</v>
       </c>
       <c r="AF6">
-        <v>280616.9132440707</v>
+        <v>755636.8</v>
       </c>
       <c r="AG6">
-        <v>223287.3132440707</v>
+        <v>636450.4</v>
       </c>
       <c r="AH6">
-        <v>0.818408301663034</v>
+        <v>0.8560918117151977</v>
       </c>
       <c r="AI6">
-        <v>0.7286263950280117</v>
+        <v>0.6809339226182779</v>
       </c>
       <c r="AJ6">
-        <v>0.7819505290560784</v>
+        <v>0.8336261621575742</v>
       </c>
       <c r="AK6">
-        <v>0.6811655830525201</v>
+        <v>0.6425416304020484</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
         <v>0</v>
-      </c>
-      <c r="AN6">
-        <v>1159.214285714286</v>
-      </c>
-      <c r="AP6">
-        <v>927.2728955318548</v>
       </c>
     </row>
     <row r="7">
@@ -1219,7 +1198,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Postal Savings Bank of China Co., Ltd. (SEHK:1658)</t>
+          <t>Agricultural Bank of China Limited (SEHK:1288)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1228,13 +1207,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0866</v>
+        <v>0.0566</v>
       </c>
       <c r="E7">
-        <v>0.145</v>
+        <v>0.0583</v>
       </c>
       <c r="F7">
-        <v>0.113</v>
+        <v>0.0397</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1249,28 +1228,28 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>11771.8</v>
+        <v>35418.7</v>
       </c>
       <c r="L7">
-        <v>0.2901602169090461</v>
+        <v>0.4394308776657448</v>
       </c>
       <c r="M7">
-        <v>2837</v>
+        <v>11541.5</v>
       </c>
       <c r="N7">
-        <v>0.03931791660776602</v>
+        <v>0.07945512160767626</v>
       </c>
       <c r="O7">
-        <v>0.2409996771946517</v>
+        <v>0.3258589389220948</v>
       </c>
       <c r="P7">
-        <v>2837</v>
+        <v>11541.5</v>
       </c>
       <c r="Q7">
-        <v>0.03931791660776602</v>
+        <v>0.07945512160767626</v>
       </c>
       <c r="R7">
-        <v>0.2409996771946517</v>
+        <v>0.3258589389220948</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1279,55 +1258,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>46602.8</v>
+        <v>282910.1</v>
       </c>
       <c r="V7">
-        <v>0.6458671145887904</v>
+        <v>1.947637343459676</v>
       </c>
       <c r="W7">
-        <v>0.1311974928058596</v>
+        <v>0.1018742735582837</v>
       </c>
       <c r="X7">
-        <v>0.05360055433576136</v>
+        <v>0.1446867725389413</v>
       </c>
       <c r="Y7">
-        <v>0.07759693847009827</v>
+        <v>-0.0428124989806576</v>
       </c>
       <c r="Z7">
-        <v>0.3490273776145867</v>
+        <v>0.1413333375417023</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.04363942949974919</v>
+        <v>0.07004735076958807</v>
       </c>
       <c r="AC7">
-        <v>-0.04363942949974919</v>
+        <v>-0.07004735076958807</v>
       </c>
       <c r="AD7">
-        <v>37261.8</v>
+        <v>455047.9</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>37261.8</v>
+        <v>455047.9</v>
       </c>
       <c r="AG7">
-        <v>-9341</v>
+        <v>172137.8</v>
       </c>
       <c r="AH7">
-        <v>0.3405479211677872</v>
+        <v>0.7580265731143784</v>
       </c>
       <c r="AI7">
-        <v>0.2355945566755838</v>
+        <v>0.551580031656149</v>
       </c>
       <c r="AJ7">
-        <v>-0.1487079395807331</v>
+        <v>0.5423441197570606</v>
       </c>
       <c r="AK7">
-        <v>-0.0837323040322559</v>
+        <v>0.3175507217850069</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1344,7 +1323,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Industrial and Commercial Bank of China Limited (SEHK:1398)</t>
+          <t>China Construction Bank Corporation (SEHK:939)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1353,13 +1332,13 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0287</v>
+        <v>0.0723</v>
       </c>
       <c r="E8">
-        <v>0.0404</v>
+        <v>0.0587</v>
       </c>
       <c r="F8">
-        <v>0.0537</v>
+        <v>0.0407</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1374,28 +1353,28 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>52611.9</v>
+        <v>44648.4</v>
       </c>
       <c r="L8">
-        <v>0.525144332119586</v>
+        <v>0.480369763486071</v>
       </c>
       <c r="M8">
-        <v>14827</v>
+        <v>12750.561</v>
       </c>
       <c r="N8">
-        <v>0.06040077074430598</v>
+        <v>0.08039090960676389</v>
       </c>
       <c r="O8">
-        <v>0.2818183718892494</v>
+        <v>0.2855771091461284</v>
       </c>
       <c r="P8">
-        <v>14827</v>
+        <v>12750.561</v>
       </c>
       <c r="Q8">
-        <v>0.06040077074430598</v>
+        <v>0.08039090960676389</v>
       </c>
       <c r="R8">
-        <v>0.2818183718892494</v>
+        <v>0.2855771091461284</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1404,55 +1383,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>352808.6</v>
+        <v>155855.8</v>
       </c>
       <c r="V8">
-        <v>1.437236889810451</v>
+        <v>0.9826539812240317</v>
       </c>
       <c r="W8">
-        <v>0.127313385305454</v>
+        <v>0.11684468782508</v>
       </c>
       <c r="X8">
-        <v>0.05919846784869488</v>
+        <v>0.1328465852039336</v>
       </c>
       <c r="Y8">
-        <v>0.06811491745675909</v>
+        <v>-0.01600189737885357</v>
       </c>
       <c r="Z8">
-        <v>0.408716958317117</v>
+        <v>0.1614278598393535</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.04386913238781309</v>
+        <v>0.07006337524656986</v>
       </c>
       <c r="AC8">
-        <v>-0.04386913238781309</v>
+        <v>-0.07006337524656986</v>
       </c>
       <c r="AD8">
-        <v>192787.8</v>
+        <v>417659.5</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>192787.8</v>
+        <v>417659.5</v>
       </c>
       <c r="AG8">
-        <v>-160020.8</v>
+        <v>261803.7</v>
       </c>
       <c r="AH8">
-        <v>0.4398888525840998</v>
+        <v>0.7247679675983247</v>
       </c>
       <c r="AI8">
-        <v>0.2819995383574359</v>
+        <v>0.5136582767571873</v>
       </c>
       <c r="AJ8">
-        <v>-1.872547574078884</v>
+        <v>0.6227331987506503</v>
       </c>
       <c r="AK8">
-        <v>-0.4836844224289166</v>
+        <v>0.3983308378416251</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1469,7 +1448,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>China Construction Bank Corporation (SEHK:939)</t>
+          <t>Industrial and Commercial Bank of China Limited (SEHK:1398)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1478,13 +1457,13 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.0508</v>
+        <v>0.0659</v>
       </c>
       <c r="E9">
-        <v>0.05230000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="F9">
-        <v>0.0646</v>
+        <v>0.0328</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1499,85 +1478,85 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>46144.1</v>
+        <v>50931.1</v>
       </c>
       <c r="L9">
-        <v>0.4810084226326982</v>
+        <v>0.4768008133430195</v>
       </c>
       <c r="M9">
-        <v>15843.661</v>
+        <v>14693.5</v>
       </c>
       <c r="N9">
-        <v>0.0903594952215777</v>
+        <v>0.06853324353217077</v>
       </c>
       <c r="O9">
-        <v>0.3433518261272839</v>
+        <v>0.2884975977349792</v>
       </c>
       <c r="P9">
-        <v>12750.561</v>
+        <v>14693.5</v>
       </c>
       <c r="Q9">
-        <v>0.07271894139567459</v>
+        <v>0.06853324353217077</v>
       </c>
       <c r="R9">
-        <v>0.2763205046799049</v>
+        <v>0.2884975977349792</v>
       </c>
       <c r="S9">
-        <v>3093.1</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>0.1952263432043895</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>164933.6</v>
+        <v>369833.4</v>
       </c>
       <c r="V9">
-        <v>0.9406485559794298</v>
+        <v>1.724972434650065</v>
       </c>
       <c r="W9">
-        <v>0.139723442414318</v>
+        <v>0.1043262397255826</v>
       </c>
       <c r="X9">
-        <v>0.08435405471574091</v>
+        <v>0.09586117636008816</v>
       </c>
       <c r="Y9">
-        <v>0.05536938769857709</v>
+        <v>0.008465063365494477</v>
       </c>
       <c r="Z9">
-        <v>0.1735099759373648</v>
+        <v>0.325497250052488</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.04439194605565382</v>
+        <v>0.07016314864012467</v>
       </c>
       <c r="AC9">
-        <v>-0.04439194605565382</v>
+        <v>-0.07016314864012467</v>
       </c>
       <c r="AD9">
-        <v>349619.8</v>
+        <v>230126.5</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>349619.8</v>
+        <v>230126.5</v>
       </c>
       <c r="AG9">
-        <v>184686.2</v>
+        <v>-139706.9</v>
       </c>
       <c r="AH9">
-        <v>0.6659930916654427</v>
+        <v>0.5176895124943171</v>
       </c>
       <c r="AI9">
-        <v>0.4692667169820235</v>
+        <v>0.3231595437922738</v>
       </c>
       <c r="AJ9">
-        <v>0.5129794612341035</v>
+        <v>-1.870422410757679</v>
       </c>
       <c r="AK9">
-        <v>0.3183692072772882</v>
+        <v>-0.408164582997352</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1594,7 +1573,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Agricultural Bank of China Limited (SEHK:1288)</t>
+          <t>Postal Savings Bank of China Co., Ltd. (SEHK:1658)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1603,13 +1582,13 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.0449</v>
+        <v>0.09810000000000001</v>
       </c>
       <c r="E10">
-        <v>0.055</v>
+        <v>0.134</v>
       </c>
       <c r="F10">
-        <v>0.0421</v>
+        <v>0.11</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1624,28 +1603,28 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>36822.5</v>
+        <v>12019.7</v>
       </c>
       <c r="L10">
-        <v>0.4404547308588044</v>
+        <v>0.2879846084916849</v>
       </c>
       <c r="M10">
-        <v>11504.6</v>
+        <v>3470.39</v>
       </c>
       <c r="N10">
-        <v>0.07267083609424733</v>
+        <v>0.05300927481685598</v>
       </c>
       <c r="O10">
-        <v>0.3124339737931971</v>
+        <v>0.2887251761691224</v>
       </c>
       <c r="P10">
-        <v>11504.6</v>
+        <v>3470.39</v>
       </c>
       <c r="Q10">
-        <v>0.07267083609424733</v>
+        <v>0.05300927481685598</v>
       </c>
       <c r="R10">
-        <v>0.3124339737931971</v>
+        <v>0.2887251761691224</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1654,55 +1633,55 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>188475.6</v>
+        <v>22506.5</v>
       </c>
       <c r="V10">
-        <v>1.190539387320283</v>
+        <v>0.3437807403967764</v>
       </c>
       <c r="W10">
-        <v>0.1205981945560261</v>
+        <v>0.1061329043172976</v>
       </c>
       <c r="X10">
-        <v>0.09529920919270506</v>
+        <v>0.0842139528616507</v>
       </c>
       <c r="Y10">
-        <v>0.02529898536332099</v>
+        <v>0.02191895145564693</v>
       </c>
       <c r="Z10">
-        <v>0.1627979616249749</v>
+        <v>0.3748688682431219</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.04450732896294574</v>
+        <v>0.07023530465205577</v>
       </c>
       <c r="AC10">
-        <v>-0.04450732896294574</v>
+        <v>-0.07023530465205577</v>
       </c>
       <c r="AD10">
-        <v>398913.2</v>
+        <v>38109</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>398913.2</v>
+        <v>38109</v>
       </c>
       <c r="AG10">
-        <v>210437.6</v>
+        <v>15602.5</v>
       </c>
       <c r="AH10">
-        <v>0.7158934023516204</v>
+        <v>0.367930594362047</v>
       </c>
       <c r="AI10">
-        <v>0.5248683859429925</v>
+        <v>0.2489324885998209</v>
       </c>
       <c r="AJ10">
-        <v>0.5706802491778276</v>
+        <v>0.1924568984126083</v>
       </c>
       <c r="AK10">
-        <v>0.3681878178201857</v>
+        <v>0.1194832107039803</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1719,7 +1698,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bank of China Limited (SEHK:3988)</t>
+          <t>Zhejiang Shaoxing RuiFeng Rural Commercial Bank Co.,Ltd (SHSE:601528)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1728,13 +1707,10 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.0358</v>
+        <v>0.0707</v>
       </c>
       <c r="E11">
-        <v>0.0389</v>
-      </c>
-      <c r="F11">
-        <v>0.0617</v>
+        <v>0.13</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1749,28 +1725,28 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>32692.3</v>
+        <v>205.3</v>
       </c>
       <c r="L11">
-        <v>0.4314021232094905</v>
+        <v>0.5389866106589657</v>
       </c>
       <c r="M11">
-        <v>273.4</v>
+        <v>61.7</v>
       </c>
       <c r="N11">
-        <v>0.002081859571185662</v>
+        <v>0.04468100514157433</v>
       </c>
       <c r="O11">
-        <v>0.00836282549713541</v>
+        <v>0.3005358012664394</v>
       </c>
       <c r="P11">
-        <v>273.4</v>
+        <v>61.7</v>
       </c>
       <c r="Q11">
-        <v>0.002081859571185662</v>
+        <v>0.04468100514157433</v>
       </c>
       <c r="R11">
-        <v>0.00836282549713541</v>
+        <v>0.3005358012664394</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1779,55 +1755,55 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>93105.8</v>
+        <v>1086.4</v>
       </c>
       <c r="V11">
-        <v>0.7089729365870449</v>
+        <v>0.7867332898834094</v>
       </c>
       <c r="W11">
-        <v>0.1121666715844066</v>
+        <v>0.1003176154409968</v>
       </c>
       <c r="X11">
-        <v>0.1745091392355912</v>
+        <v>0.1178743712093715</v>
       </c>
       <c r="Y11">
-        <v>-0.06234246765118456</v>
+        <v>-0.01755675576837464</v>
       </c>
       <c r="Z11">
-        <v>0.09053578129530508</v>
+        <v>0.09730489206795249</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.04484860950313663</v>
+        <v>0.071091573985052</v>
       </c>
       <c r="AC11">
-        <v>-0.04484860950313663</v>
+        <v>-0.071091573985052</v>
       </c>
       <c r="AD11">
-        <v>830684.5</v>
+        <v>2764.3</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>830684.5</v>
+        <v>2764.3</v>
       </c>
       <c r="AG11">
-        <v>737578.7</v>
+        <v>1677.9</v>
       </c>
       <c r="AH11">
-        <v>0.8634889638292516</v>
+        <v>0.666867702402779</v>
       </c>
       <c r="AI11">
-        <v>0.7007275065605328</v>
+        <v>0.5706647398843931</v>
       </c>
       <c r="AJ11">
-        <v>0.8488613696617208</v>
+        <v>0.5485484503726952</v>
       </c>
       <c r="AK11">
-        <v>0.6752192946922075</v>
+        <v>0.4465350223546945</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1844,7 +1820,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>China Merchants Bank Co., Ltd. (SHSE:600036)</t>
+          <t>Bank of Communications Co., Ltd. (SEHK:3328)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1853,13 +1829,13 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.119</v>
+        <v>0.0476</v>
       </c>
       <c r="E12">
-        <v>0.133</v>
+        <v>0.0551</v>
       </c>
       <c r="F12">
-        <v>0.133</v>
+        <v>0.031</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1874,28 +1850,28 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>17744.7</v>
+        <v>13374.8</v>
       </c>
       <c r="L12">
-        <v>0.4553752899874767</v>
+        <v>0.4297207335723741</v>
       </c>
       <c r="M12">
-        <v>5246.6</v>
+        <v>251.5</v>
       </c>
       <c r="N12">
-        <v>0.02706860792669714</v>
+        <v>0.005335624575695859</v>
       </c>
       <c r="O12">
-        <v>0.2956713835680513</v>
+        <v>0.018804019499357</v>
       </c>
       <c r="P12">
-        <v>5246.6</v>
+        <v>251.5</v>
       </c>
       <c r="Q12">
-        <v>0.02706860792669714</v>
+        <v>0.005335624575695859</v>
       </c>
       <c r="R12">
-        <v>0.2956713835680513</v>
+        <v>0.018804019499357</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -1904,55 +1880,55 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>1824.5</v>
+        <v>26740.6</v>
       </c>
       <c r="V12">
-        <v>0.009413081836286153</v>
+        <v>0.5673073659198914</v>
       </c>
       <c r="W12">
-        <v>0.1800558289050046</v>
+        <v>0.09828926356540725</v>
       </c>
       <c r="X12">
-        <v>0.06137429355190954</v>
+        <v>0.2555810166427711</v>
       </c>
       <c r="Y12">
-        <v>0.1186815353530951</v>
+        <v>-0.1572917530773639</v>
       </c>
       <c r="Z12">
-        <v>0.1504550656459028</v>
+        <v>0.06313442445244918</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.04486615962629789</v>
+        <v>0.07131519166166993</v>
       </c>
       <c r="AC12">
-        <v>-0.04486615962629789</v>
+        <v>-0.07131519166166993</v>
       </c>
       <c r="AD12">
-        <v>172485.1</v>
+        <v>368127.7</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>172485.1</v>
+        <v>368127.7</v>
       </c>
       <c r="AG12">
-        <v>170660.6</v>
+        <v>341387.1</v>
       </c>
       <c r="AH12">
-        <v>0.4708705250810036</v>
+        <v>0.8864914029326426</v>
       </c>
       <c r="AI12">
-        <v>0.5827701372922329</v>
+        <v>0.7137778225888544</v>
       </c>
       <c r="AJ12">
-        <v>0.4682218770182498</v>
+        <v>0.87867902835121</v>
       </c>
       <c r="AK12">
-        <v>0.5801822199558049</v>
+        <v>0.6981261332964148</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -1969,7 +1945,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bank of Communications Co., Ltd. (SEHK:3328)</t>
+          <t>China Merchants Bank Co., Ltd. (SHSE:600036)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1978,13 +1954,13 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.0347</v>
+        <v>0.134</v>
       </c>
       <c r="E13">
-        <v>0.0604</v>
+        <v>0.141</v>
       </c>
       <c r="F13">
-        <v>0.0325</v>
+        <v>0.112</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1999,85 +1975,85 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>13953.5</v>
+        <v>18726.9</v>
       </c>
       <c r="L13">
-        <v>0.4553865735452498</v>
+        <v>0.4677632071937056</v>
       </c>
       <c r="M13">
-        <v>6296.1723</v>
+        <v>5435.7</v>
       </c>
       <c r="N13">
-        <v>0.1268581367515857</v>
+        <v>0.03963570472832804</v>
       </c>
       <c r="O13">
-        <v>0.4512253054789121</v>
+        <v>0.2902616022940262</v>
       </c>
       <c r="P13">
-        <v>3638.8723</v>
+        <v>5435.7</v>
       </c>
       <c r="Q13">
-        <v>0.07331765044850458</v>
+        <v>0.03963570472832804</v>
       </c>
       <c r="R13">
-        <v>0.2607856308453076</v>
+        <v>0.2902616022940262</v>
       </c>
       <c r="S13">
-        <v>2657.3</v>
+        <v>0</v>
       </c>
       <c r="T13">
-        <v>0.4220500763614745</v>
+        <v>0</v>
       </c>
       <c r="U13">
-        <v>34374.8</v>
+        <v>1647.7</v>
       </c>
       <c r="V13">
-        <v>0.6925990699473723</v>
+        <v>0.01201459806112665</v>
       </c>
       <c r="W13">
-        <v>0.1214565560078931</v>
+        <v>0.1598665879010558</v>
       </c>
       <c r="X13">
-        <v>0.2008879726937661</v>
+        <v>0.09050211968471944</v>
       </c>
       <c r="Y13">
-        <v>-0.07943141668587296</v>
+        <v>0.06936446821633641</v>
       </c>
       <c r="Z13">
-        <v>0.07279274604998209</v>
+        <v>0.1373211754843542</v>
       </c>
       <c r="AA13">
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.04587883677531512</v>
+        <v>0.07153320962178572</v>
       </c>
       <c r="AC13">
-        <v>-0.04587883677531512</v>
+        <v>-0.07153320962178572</v>
       </c>
       <c r="AD13">
-        <v>376841.6</v>
+        <v>116203.1</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>376841.6</v>
+        <v>116203.1</v>
       </c>
       <c r="AG13">
-        <v>342466.8</v>
+        <v>114555.4</v>
       </c>
       <c r="AH13">
-        <v>0.8836231678801857</v>
+        <v>0.4586760483546916</v>
       </c>
       <c r="AI13">
-        <v>0.7173550490757175</v>
+        <v>0.4711982673990995</v>
       </c>
       <c r="AJ13">
-        <v>0.8734205495355248</v>
+        <v>0.4551323437038756</v>
       </c>
       <c r="AK13">
-        <v>0.6975649669077726</v>
+        <v>0.4676413941302444</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2103,13 +2079,13 @@
         </is>
       </c>
       <c r="D14">
-        <v>0.08119999999999999</v>
+        <v>0.129</v>
       </c>
       <c r="E14">
-        <v>0.09320000000000001</v>
+        <v>0.137</v>
       </c>
       <c r="F14">
-        <v>0.233</v>
+        <v>0.193</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2124,28 +2100,28 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>5534.3</v>
+        <v>6165</v>
       </c>
       <c r="L14">
-        <v>0.3726274398906552</v>
+        <v>0.4128772150711904</v>
       </c>
       <c r="M14">
-        <v>848.5</v>
+        <v>768.6</v>
       </c>
       <c r="N14">
-        <v>0.01685434548130727</v>
+        <v>0.02075793749392332</v>
       </c>
       <c r="O14">
-        <v>0.1533165892705491</v>
+        <v>0.1246715328467153</v>
       </c>
       <c r="P14">
-        <v>848.5</v>
+        <v>768.6</v>
       </c>
       <c r="Q14">
-        <v>0.01685434548130727</v>
+        <v>0.02075793749392332</v>
       </c>
       <c r="R14">
-        <v>0.1533165892705491</v>
+        <v>0.1246715328467153</v>
       </c>
       <c r="S14">
         <v>0</v>
@@ -2154,55 +2130,55 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>42639.8</v>
+        <v>26643.2</v>
       </c>
       <c r="V14">
-        <v>0.8469839958206786</v>
+        <v>0.7195652878455605</v>
       </c>
       <c r="W14">
-        <v>0.1109218197888712</v>
+        <v>0.1076963121219056</v>
       </c>
       <c r="X14">
-        <v>0.1112276205693424</v>
+        <v>0.1649419319754076</v>
       </c>
       <c r="Y14">
-        <v>-0.0003058007804712243</v>
+        <v>-0.05724561985350199</v>
       </c>
       <c r="Z14">
-        <v>0.1067785058299291</v>
+        <v>0.0820846210764378</v>
       </c>
       <c r="AA14">
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.04613129215876594</v>
+        <v>0.07236585292986131</v>
       </c>
       <c r="AC14">
-        <v>-0.04613129215876594</v>
+        <v>-0.07236585292986131</v>
       </c>
       <c r="AD14">
-        <v>165381.1</v>
+        <v>147625.6</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>165381.1</v>
+        <v>147625.6</v>
       </c>
       <c r="AG14">
-        <v>122741.3</v>
+        <v>120982.4</v>
       </c>
       <c r="AH14">
-        <v>0.7666321163782274</v>
+        <v>0.7994783712532303</v>
       </c>
       <c r="AI14">
-        <v>0.7326773334940032</v>
+        <v>0.7117285641003883</v>
       </c>
       <c r="AJ14">
-        <v>0.7091413206505035</v>
+        <v>0.7656668092743967</v>
       </c>
       <c r="AK14">
-        <v>0.670417813239765</v>
+        <v>0.669242241192376</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2219,7 +2195,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>China Everbright Bank Company Limited (SHSE:601818)</t>
+          <t>Jilin Jiutai Rural Commercial Bank Corporation Limited (SEHK:6122)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2228,13 +2204,10 @@
         </is>
       </c>
       <c r="D15">
-        <v>0.0611</v>
+        <v>-0.0136</v>
       </c>
       <c r="E15">
-        <v>0.0755</v>
-      </c>
-      <c r="F15">
-        <v>0.0538</v>
+        <v>-0.0505</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2249,85 +2222,82 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>6718.4</v>
+        <v>179.7</v>
       </c>
       <c r="L15">
-        <v>0.4557133748456852</v>
+        <v>0.2540288379983036</v>
       </c>
       <c r="M15">
-        <v>1743.1</v>
+        <v>-0</v>
       </c>
       <c r="N15">
-        <v>0.06678620827059314</v>
+        <v>-0</v>
       </c>
       <c r="O15">
-        <v>0.2594516551559895</v>
+        <v>-0</v>
       </c>
       <c r="P15">
-        <v>1743.1</v>
+        <v>-0</v>
       </c>
       <c r="Q15">
-        <v>0.06678620827059314</v>
+        <v>-0</v>
       </c>
       <c r="R15">
-        <v>0.2594516551559895</v>
+        <v>-0</v>
       </c>
       <c r="S15">
         <v>0</v>
       </c>
-      <c r="T15">
-        <v>0</v>
-      </c>
       <c r="U15">
-        <v>17424.1</v>
+        <v>4626.9</v>
       </c>
       <c r="V15">
-        <v>0.667597711851094</v>
+        <v>3.246491720460286</v>
       </c>
       <c r="W15">
-        <v>0.1218903306336904</v>
+        <v>0.07734354824825686</v>
       </c>
       <c r="X15">
-        <v>0.1709240388485186</v>
+        <v>0.09953365987851573</v>
       </c>
       <c r="Y15">
-        <v>-0.04903370821482819</v>
+        <v>-0.02219011163025887</v>
       </c>
       <c r="Z15">
-        <v>0.09159727667315729</v>
+        <v>1.310242637525466</v>
       </c>
       <c r="AA15">
         <v>0</v>
       </c>
       <c r="AB15">
-        <v>0.04653154058218481</v>
+        <v>0.07254478877275863</v>
       </c>
       <c r="AC15">
-        <v>-0.04653154058218481</v>
+        <v>-0.07254478877275863</v>
       </c>
       <c r="AD15">
-        <v>160595.9</v>
+        <v>1750.5</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>160595.9</v>
+        <v>1750.5</v>
       </c>
       <c r="AG15">
-        <v>143171.8</v>
+        <v>-2876.4</v>
       </c>
       <c r="AH15">
-        <v>0.8602018472850993</v>
+        <v>0.5512170545076677</v>
       </c>
       <c r="AI15">
-        <v>0.6850323436510255</v>
+        <v>0.3920141532673445</v>
       </c>
       <c r="AJ15">
-        <v>0.8458116103419654</v>
+        <v>1.982083792723264</v>
       </c>
       <c r="AK15">
-        <v>0.6597432208630514</v>
+        <v>17.81052631578952</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2353,13 +2323,13 @@
         </is>
       </c>
       <c r="D16">
-        <v>0.0132</v>
+        <v>0.061</v>
       </c>
       <c r="E16">
-        <v>0.047</v>
+        <v>0.0784</v>
       </c>
       <c r="F16">
-        <v>0.058</v>
+        <v>0.0501</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2374,85 +2344,85 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>8351.1</v>
+        <v>8572.6</v>
       </c>
       <c r="L16">
-        <v>0.4469964191471254</v>
+        <v>0.4444893811183009</v>
       </c>
       <c r="M16">
-        <v>2187.9</v>
+        <v>3026</v>
       </c>
       <c r="N16">
-        <v>0.07008928142388975</v>
+        <v>0.09701485359605785</v>
       </c>
       <c r="O16">
-        <v>0.2619894385170816</v>
+        <v>0.3529850920374215</v>
       </c>
       <c r="P16">
-        <v>2187.9</v>
+        <v>2558.8</v>
       </c>
       <c r="Q16">
-        <v>0.07008928142388975</v>
+        <v>0.08203622187098243</v>
       </c>
       <c r="R16">
-        <v>0.2619894385170816</v>
+        <v>0.298485873597275</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>467.1999999999998</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>0.1543952412425644</v>
       </c>
       <c r="U16">
-        <v>45170.2</v>
+        <v>34803.3</v>
       </c>
       <c r="V16">
-        <v>1.447025394110053</v>
+        <v>1.115808676192888</v>
       </c>
       <c r="W16">
-        <v>0.1061870273074517</v>
+        <v>0.09001163391390904</v>
       </c>
       <c r="X16">
-        <v>0.1785580500866462</v>
+        <v>0.2481377484981385</v>
       </c>
       <c r="Y16">
-        <v>-0.07237102277919448</v>
+        <v>-0.1581261145842295</v>
       </c>
       <c r="Z16">
-        <v>0.09204229983816101</v>
+        <v>0.07609151940005492</v>
       </c>
       <c r="AA16">
         <v>0</v>
       </c>
       <c r="AB16">
-        <v>0.04656070669107164</v>
+        <v>0.0725681944848236</v>
       </c>
       <c r="AC16">
-        <v>-0.04656070669107164</v>
+        <v>-0.0725681944848236</v>
       </c>
       <c r="AD16">
-        <v>203525.9</v>
+        <v>233807.5</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>203525.9</v>
+        <v>233807.5</v>
       </c>
       <c r="AG16">
-        <v>158355.7</v>
+        <v>199004.2</v>
       </c>
       <c r="AH16">
-        <v>0.8670202750426214</v>
+        <v>0.8822971140224892</v>
       </c>
       <c r="AI16">
-        <v>0.6743128764779571</v>
+        <v>0.7103605404643385</v>
       </c>
       <c r="AJ16">
-        <v>0.8353345121315641</v>
+        <v>0.8645015775734778</v>
       </c>
       <c r="AK16">
-        <v>0.6169937375539095</v>
+        <v>0.6761125639108243</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -2469,7 +2439,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Shanghai Rural Commercial Bank Co., Ltd. (SHSE:601825)</t>
+          <t>China Everbright Bank Company Limited (SHSE:601818)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2477,6 +2447,15 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
+      <c r="D17">
+        <v>0.07629999999999999</v>
+      </c>
+      <c r="E17">
+        <v>0.0747</v>
+      </c>
+      <c r="F17">
+        <v>0.062</v>
+      </c>
       <c r="G17">
         <v>0</v>
       </c>
@@ -2484,34 +2463,34 @@
         <v>0</v>
       </c>
       <c r="I17">
-        <v>0.004853354844126777</v>
+        <v>0</v>
       </c>
       <c r="J17">
-        <v>0.004001454401167034</v>
+        <v>0</v>
       </c>
       <c r="K17">
-        <v>1478.1</v>
+        <v>6313.1</v>
       </c>
       <c r="L17">
-        <v>0.4964398468462417</v>
+        <v>0.4441716151183407</v>
       </c>
       <c r="M17">
-        <v>353.6</v>
+        <v>1595</v>
       </c>
       <c r="N17">
-        <v>0.03450496691972912</v>
+        <v>0.0715997953008987</v>
       </c>
       <c r="O17">
-        <v>0.2392260334212841</v>
+        <v>0.2526492531402956</v>
       </c>
       <c r="P17">
-        <v>353.6</v>
+        <v>1595</v>
       </c>
       <c r="Q17">
-        <v>0.03450496691972912</v>
+        <v>0.0715997953008987</v>
       </c>
       <c r="R17">
-        <v>0.2392260334212841</v>
+        <v>0.2526492531402956</v>
       </c>
       <c r="S17">
         <v>0</v>
@@ -2520,67 +2499,61 @@
         <v>0</v>
       </c>
       <c r="U17">
-        <v>5075.5</v>
+        <v>16195.1</v>
       </c>
       <c r="V17">
-        <v>0.4952770350709421</v>
+        <v>0.7270005297038148</v>
       </c>
       <c r="W17">
-        <v>0.1410252740647451</v>
+        <v>0.09941529676877846</v>
       </c>
       <c r="X17">
-        <v>0.09974539090892871</v>
+        <v>0.2536654125926542</v>
       </c>
       <c r="Y17">
-        <v>0.04127988315581639</v>
+        <v>-0.1542501158238757</v>
       </c>
       <c r="Z17">
-        <v>0.1020652037093349</v>
+        <v>0.06563563568186122</v>
       </c>
       <c r="AA17">
-        <v>0.0004084092585887281</v>
+        <v>0</v>
       </c>
       <c r="AB17">
-        <v>0.04703295466701044</v>
+        <v>0.07257587506506158</v>
       </c>
       <c r="AC17">
-        <v>-0.04662454540842172</v>
+        <v>-0.07257587506506158</v>
       </c>
       <c r="AD17">
-        <v>27897.3</v>
+        <v>172178.3</v>
       </c>
       <c r="AE17">
-        <v>114.2481064354847</v>
+        <v>0</v>
       </c>
       <c r="AF17">
-        <v>28011.54810643548</v>
+        <v>172178.3</v>
       </c>
       <c r="AG17">
-        <v>22936.04810643548</v>
+        <v>155983.2</v>
       </c>
       <c r="AH17">
-        <v>0.7321491215299548</v>
+        <v>0.8854407885838824</v>
       </c>
       <c r="AI17">
-        <v>0.6494279701379174</v>
+        <v>0.7085045665623527</v>
       </c>
       <c r="AJ17">
-        <v>0.6911810840282685</v>
+        <v>0.8750329575148182</v>
       </c>
       <c r="AK17">
-        <v>0.6026738536027345</v>
+        <v>0.6876917257366368</v>
       </c>
       <c r="AL17">
         <v>0</v>
       </c>
       <c r="AM17">
         <v>0</v>
-      </c>
-      <c r="AN17">
-        <v>747.916890080429</v>
-      </c>
-      <c r="AP17">
-        <v>614.9074559366081</v>
       </c>
     </row>
     <row r="18">
@@ -2591,7 +2564,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Jilin Jiutai Rural Commercial Bank Corporation Limited (SEHK:6122)</t>
+          <t>Shanghai Rural Commercial Bank Co., Ltd. (SHSE:601825)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2599,12 +2572,6 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D18">
-        <v>-0.0135</v>
-      </c>
-      <c r="E18">
-        <v>-0.0496</v>
-      </c>
       <c r="G18">
         <v>0</v>
       </c>
@@ -2618,28 +2585,28 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>215.8</v>
+        <v>1547.6</v>
       </c>
       <c r="L18">
-        <v>0.2842465753424657</v>
+        <v>0.5125012418452164</v>
       </c>
       <c r="M18">
-        <v>101.4838</v>
+        <v>1081.7</v>
       </c>
       <c r="N18">
-        <v>0.07179102999434069</v>
+        <v>0.1315600637306771</v>
       </c>
       <c r="O18">
-        <v>0.4702678405931417</v>
+        <v>0.6989532178857587</v>
       </c>
       <c r="P18">
-        <v>101.4838</v>
+        <v>1081.7</v>
       </c>
       <c r="Q18">
-        <v>0.07179102999434069</v>
+        <v>0.1315600637306771</v>
       </c>
       <c r="R18">
-        <v>0.4702678405931417</v>
+        <v>0.6989532178857587</v>
       </c>
       <c r="S18">
         <v>0</v>
@@ -2648,55 +2615,55 @@
         <v>0</v>
       </c>
       <c r="U18">
-        <v>4604.5</v>
+        <v>7420.2</v>
       </c>
       <c r="V18">
-        <v>3.25728636106395</v>
+        <v>0.9024701718539059</v>
       </c>
       <c r="W18">
-        <v>0.1021006813020439</v>
+        <v>0.1061039237060957</v>
       </c>
       <c r="X18">
-        <v>0.08530600056777168</v>
+        <v>0.1528005630839277</v>
       </c>
       <c r="Y18">
-        <v>0.01679468073427223</v>
+        <v>-0.04669663937783204</v>
       </c>
       <c r="Z18">
-        <v>0.3996210127381831</v>
+        <v>0.08072445365234245</v>
       </c>
       <c r="AA18">
         <v>0</v>
       </c>
       <c r="AB18">
-        <v>0.04668386690772186</v>
+        <v>0.07341634673419581</v>
       </c>
       <c r="AC18">
-        <v>-0.04668386690772186</v>
+        <v>-0.07341634673419581</v>
       </c>
       <c r="AD18">
-        <v>2883.3</v>
+        <v>28571</v>
       </c>
       <c r="AE18">
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>2883.3</v>
+        <v>28571</v>
       </c>
       <c r="AG18">
-        <v>-1721.2</v>
+        <v>21150.8</v>
       </c>
       <c r="AH18">
-        <v>0.6710186413460868</v>
+        <v>0.7765314692156954</v>
       </c>
       <c r="AI18">
-        <v>0.5100116743906322</v>
+        <v>0.6608670308979798</v>
       </c>
       <c r="AJ18">
-        <v>5.595578673602081</v>
+        <v>0.72007871201005</v>
       </c>
       <c r="AK18">
-        <v>-1.640957193250071</v>
+        <v>0.5905999039438853</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -2722,13 +2689,13 @@
         </is>
       </c>
       <c r="D19">
-        <v>-0.00113</v>
+        <v>-0.00181</v>
       </c>
       <c r="E19">
-        <v>0.00365</v>
+        <v>-0.008920000000000001</v>
       </c>
       <c r="F19">
-        <v>-0.0177</v>
+        <v>0.0286</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2737,34 +2704,34 @@
         <v>0</v>
       </c>
       <c r="I19">
-        <v>0.01031382280577162</v>
+        <v>0</v>
       </c>
       <c r="J19">
-        <v>0.009244998658773299</v>
+        <v>0</v>
       </c>
       <c r="K19">
-        <v>8553</v>
+        <v>7299.2</v>
       </c>
       <c r="L19">
-        <v>0.4883047779991664</v>
+        <v>0.4614489821722089</v>
       </c>
       <c r="M19">
-        <v>2172.0628</v>
+        <v>1702.4276</v>
       </c>
       <c r="N19">
-        <v>0.05511045368394612</v>
+        <v>0.0549503440796354</v>
       </c>
       <c r="O19">
-        <v>0.2539533263182509</v>
+        <v>0.2332348202542745</v>
       </c>
       <c r="P19">
-        <v>2172.0628</v>
+        <v>1702.4276</v>
       </c>
       <c r="Q19">
-        <v>0.05511045368394612</v>
+        <v>0.0549503440796354</v>
       </c>
       <c r="R19">
-        <v>0.2539533263182509</v>
+        <v>0.2332348202542745</v>
       </c>
       <c r="S19">
         <v>0</v>
@@ -2773,67 +2740,61 @@
         <v>0</v>
       </c>
       <c r="U19">
-        <v>45135.9</v>
+        <v>25515.5</v>
       </c>
       <c r="V19">
-        <v>1.14520626495386</v>
+        <v>0.8235801066453203</v>
       </c>
       <c r="W19">
-        <v>0.1069583583961624</v>
+        <v>0.07435719815818426</v>
       </c>
       <c r="X19">
-        <v>0.1996914153987733</v>
+        <v>0.3023221179855862</v>
       </c>
       <c r="Y19">
-        <v>-0.09273305700261095</v>
+        <v>-0.227964919827402</v>
       </c>
       <c r="Z19">
-        <v>0.05669420803431083</v>
+        <v>0.04490542833896474</v>
       </c>
       <c r="AA19">
-        <v>0.0005241378772374181</v>
+        <v>0</v>
       </c>
       <c r="AB19">
-        <v>0.04789347640554938</v>
+        <v>0.07392197854592872</v>
       </c>
       <c r="AC19">
-        <v>-0.04736933852831196</v>
+        <v>-0.07392197854592872</v>
       </c>
       <c r="AD19">
-        <v>295663.8</v>
+        <v>303037</v>
       </c>
       <c r="AE19">
-        <v>1323.73086940473</v>
+        <v>0</v>
       </c>
       <c r="AF19">
-        <v>296987.5308694047</v>
+        <v>303037</v>
       </c>
       <c r="AG19">
-        <v>251851.6308694047</v>
+        <v>277521.5</v>
       </c>
       <c r="AH19">
-        <v>0.8828393296104289</v>
+        <v>0.9072469703746682</v>
       </c>
       <c r="AI19">
-        <v>0.7405241535973158</v>
+        <v>0.7546747387911488</v>
       </c>
       <c r="AJ19">
-        <v>0.8646834893271927</v>
+        <v>0.8995755952865242</v>
       </c>
       <c r="AK19">
-        <v>0.7076182876102249</v>
+        <v>0.7380282476710697</v>
       </c>
       <c r="AL19">
         <v>0</v>
       </c>
       <c r="AM19">
         <v>0</v>
-      </c>
-      <c r="AN19">
-        <v>663.8163448585541</v>
-      </c>
-      <c r="AP19">
-        <v>565.4504509865396</v>
       </c>
     </row>
     <row r="20">
@@ -2844,7 +2805,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Hua Xia Bank Co., Limited (SHSE:600015)</t>
+          <t>China Zheshang Bank Co., Ltd (SEHK:2016)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2853,10 +2814,10 @@
         </is>
       </c>
       <c r="D20">
-        <v>0.0315</v>
+        <v>0.052</v>
       </c>
       <c r="E20">
-        <v>0.0334</v>
+        <v>0.04219999999999999</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -2865,103 +2826,97 @@
         <v>0</v>
       </c>
       <c r="I20">
-        <v>0.01047226045887181</v>
+        <v>0</v>
       </c>
       <c r="J20">
-        <v>0.008161833147612029</v>
+        <v>0</v>
       </c>
       <c r="K20">
-        <v>3549.3</v>
+        <v>1912.6</v>
       </c>
       <c r="L20">
-        <v>0.3878253458336066</v>
+        <v>0.4136424585838487</v>
       </c>
       <c r="M20">
-        <v>723.1984</v>
+        <v>2064.4</v>
       </c>
       <c r="N20">
-        <v>0.0533163082503336</v>
+        <v>0.2358155420764653</v>
       </c>
       <c r="O20">
-        <v>0.2037580367959879</v>
+        <v>1.079368399037959</v>
       </c>
       <c r="P20">
-        <v>723.1984</v>
+        <v>-0</v>
       </c>
       <c r="Q20">
-        <v>0.0533163082503336</v>
+        <v>-0</v>
       </c>
       <c r="R20">
-        <v>0.2037580367959879</v>
+        <v>-0</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>2064.4</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U20">
-        <v>4560.6</v>
+        <v>11162.6</v>
       </c>
       <c r="V20">
-        <v>0.3362208149333176</v>
+        <v>1.275099094159442</v>
       </c>
       <c r="W20">
-        <v>0.1003052140737601</v>
+        <v>0.1008712712543774</v>
       </c>
       <c r="X20">
-        <v>0.226184017490785</v>
+        <v>0.2344462329477097</v>
       </c>
       <c r="Y20">
-        <v>-0.125878803417025</v>
+        <v>-0.1335749616933322</v>
       </c>
       <c r="Z20">
-        <v>0.06648258615834961</v>
+        <v>0.06000166101747702</v>
       </c>
       <c r="AA20">
-        <v>0.0005426197754461905</v>
+        <v>0</v>
       </c>
       <c r="AB20">
-        <v>0.04905077469765257</v>
+        <v>0.0751683631392818</v>
       </c>
       <c r="AC20">
-        <v>-0.04850815492220638</v>
+        <v>-0.0751683631392818</v>
       </c>
       <c r="AD20">
-        <v>118379.1</v>
+        <v>60566.6</v>
       </c>
       <c r="AE20">
-        <v>1096.799833662485</v>
+        <v>0</v>
       </c>
       <c r="AF20">
-        <v>119475.8998336625</v>
+        <v>60566.6</v>
       </c>
       <c r="AG20">
-        <v>114915.2998336625</v>
+        <v>49404</v>
       </c>
       <c r="AH20">
-        <v>0.8980435987246023</v>
+        <v>0.8737134111068957</v>
       </c>
       <c r="AI20">
-        <v>0.728811553260587</v>
+        <v>0.7257761459446763</v>
       </c>
       <c r="AJ20">
-        <v>0.8944244843729185</v>
+        <v>0.8494746235704963</v>
       </c>
       <c r="AK20">
-        <v>0.721051201332232</v>
+        <v>0.6834310440708166</v>
       </c>
       <c r="AL20">
         <v>0</v>
       </c>
       <c r="AM20">
         <v>0</v>
-      </c>
-      <c r="AN20">
-        <v>375.5682106598985</v>
-      </c>
-      <c r="AP20">
-        <v>364.5789969342084</v>
       </c>
     </row>
     <row r="21">
@@ -2972,7 +2927,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>China Zheshang Bank Co., Ltd (SEHK:2016)</t>
+          <t>China Minsheng Banking Corp., Ltd. (SHSE:600016)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2981,10 +2936,13 @@
         </is>
       </c>
       <c r="D21">
-        <v>0.0491</v>
+        <v>-0.0365</v>
       </c>
       <c r="E21">
-        <v>0.0587</v>
+        <v>-0.0776</v>
+      </c>
+      <c r="F21">
+        <v>-0.0126</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -2999,85 +2957,85 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>1977.4</v>
+        <v>4592.4</v>
       </c>
       <c r="L21">
-        <v>0.4397936034873894</v>
+        <v>0.3591038823943387</v>
       </c>
       <c r="M21">
-        <v>531.7175000000001</v>
+        <v>1560.5</v>
       </c>
       <c r="N21">
-        <v>0.04798201523245741</v>
+        <v>0.07568152168114339</v>
       </c>
       <c r="O21">
-        <v>0.2688972893698797</v>
+        <v>0.3398005400226461</v>
       </c>
       <c r="P21">
-        <v>531.7175000000001</v>
+        <v>272.7</v>
       </c>
       <c r="Q21">
-        <v>0.04798201523245741</v>
+        <v>0.01322547322169036</v>
       </c>
       <c r="R21">
-        <v>0.2688972893698797</v>
+        <v>0.05938071596550824</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1287.8</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>0.8252483178468439</v>
       </c>
       <c r="U21">
-        <v>9644.799999999999</v>
+        <v>10668.7</v>
       </c>
       <c r="V21">
-        <v>0.8703436326884203</v>
+        <v>0.5174132972506341</v>
       </c>
       <c r="W21">
-        <v>0.1183618254082268</v>
+        <v>0.05317160938943653</v>
       </c>
       <c r="X21">
-        <v>0.1657346790375899</v>
+        <v>0.2790636029502559</v>
       </c>
       <c r="Y21">
-        <v>-0.04737285362936312</v>
+        <v>-0.2258919935608193</v>
       </c>
       <c r="Z21">
-        <v>0.07344427891903194</v>
+        <v>0.05403193539405477</v>
       </c>
       <c r="AA21">
         <v>0</v>
       </c>
       <c r="AB21">
-        <v>0.04875472245872863</v>
+        <v>0.07530035650825825</v>
       </c>
       <c r="AC21">
-        <v>-0.04875472245872863</v>
+        <v>-0.07530035650825825</v>
       </c>
       <c r="AD21">
-        <v>65424.1</v>
+        <v>181456.8</v>
       </c>
       <c r="AE21">
         <v>0</v>
       </c>
       <c r="AF21">
-        <v>65424.1</v>
+        <v>181456.8</v>
       </c>
       <c r="AG21">
-        <v>55779.3</v>
+        <v>170788.1</v>
       </c>
       <c r="AH21">
-        <v>0.8551532761611227</v>
+        <v>0.8979626982112185</v>
       </c>
       <c r="AI21">
-        <v>0.7516080670453957</v>
+        <v>0.6786790920066605</v>
       </c>
       <c r="AJ21">
-        <v>0.8342588867335019</v>
+        <v>0.8922753247784568</v>
       </c>
       <c r="AK21">
-        <v>0.7206562731344807</v>
+        <v>0.6653246274136742</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3094,7 +3052,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>China Minsheng Banking Corp., Ltd. (SHSE:600016)</t>
+          <t>Hua Xia Bank Co., Limited (SHSE:600015)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3103,13 +3061,10 @@
         </is>
       </c>
       <c r="D22">
-        <v>-0.0566</v>
+        <v>0.0501</v>
       </c>
       <c r="E22">
-        <v>-0.0709</v>
-      </c>
-      <c r="F22">
-        <v>0.109</v>
+        <v>0.0483</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3124,85 +3079,85 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>5038</v>
+        <v>3432</v>
       </c>
       <c r="L22">
-        <v>0.380982629672482</v>
+        <v>0.384098845017459</v>
       </c>
       <c r="M22">
-        <v>1458.0192</v>
+        <v>763.9152</v>
       </c>
       <c r="N22">
-        <v>0.0584360037994926</v>
+        <v>0.06378930492000401</v>
       </c>
       <c r="O22">
-        <v>0.2894043668122271</v>
+        <v>0.222586013986014</v>
       </c>
       <c r="P22">
-        <v>1444.8192</v>
+        <v>763.9152</v>
       </c>
       <c r="Q22">
-        <v>0.05790696052615758</v>
+        <v>0.06378930492000401</v>
       </c>
       <c r="R22">
-        <v>0.2867842794759826</v>
+        <v>0.222586013986014</v>
       </c>
       <c r="S22">
-        <v>13.20000000000005</v>
+        <v>0</v>
       </c>
       <c r="T22">
-        <v>0.009053378720938685</v>
+        <v>0</v>
       </c>
       <c r="U22">
-        <v>33116.8</v>
+        <v>9091.700000000001</v>
       </c>
       <c r="V22">
-        <v>1.327289414725839</v>
+        <v>0.7591853435318481</v>
       </c>
       <c r="W22">
-        <v>0.06802923177470145</v>
+        <v>0.08163886695148291</v>
       </c>
       <c r="X22">
-        <v>0.1920052220727106</v>
+        <v>0.3127597575901053</v>
       </c>
       <c r="Y22">
-        <v>-0.1239759902980092</v>
+        <v>-0.2311208906386223</v>
       </c>
       <c r="Z22">
-        <v>0.04619376600566118</v>
+        <v>0.05676314385180291</v>
       </c>
       <c r="AA22">
         <v>0</v>
       </c>
       <c r="AB22">
-        <v>0.04890925558202848</v>
+        <v>0.07537069910378753</v>
       </c>
       <c r="AC22">
-        <v>-0.04890925558202848</v>
+        <v>-0.07537069910378753</v>
       </c>
       <c r="AD22">
-        <v>178796.9</v>
+        <v>122409.2</v>
       </c>
       <c r="AE22">
         <v>0</v>
       </c>
       <c r="AF22">
-        <v>178796.9</v>
+        <v>122409.2</v>
       </c>
       <c r="AG22">
-        <v>145680.1</v>
+        <v>113317.5</v>
       </c>
       <c r="AH22">
-        <v>0.8775411342268571</v>
+        <v>0.9108857549365703</v>
       </c>
       <c r="AI22">
-        <v>0.6581099843052034</v>
+        <v>0.7378639840334376</v>
       </c>
       <c r="AJ22">
-        <v>0.8537737618296344</v>
+        <v>0.9044193175841287</v>
       </c>
       <c r="AK22">
-        <v>0.6106500685765257</v>
+        <v>0.7226650935875769</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -3228,10 +3183,10 @@
         </is>
       </c>
       <c r="D23">
-        <v>0.0503</v>
+        <v>0.0154</v>
       </c>
       <c r="E23">
-        <v>0.0552</v>
+        <v>0.00927</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3246,28 +3201,28 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>1353.9</v>
+        <v>1147.6</v>
       </c>
       <c r="L23">
-        <v>0.4371649983855344</v>
+        <v>0.4062876159456206</v>
       </c>
       <c r="M23">
-        <v>380.9</v>
+        <v>367.2</v>
       </c>
       <c r="N23">
-        <v>0.05574010389990488</v>
+        <v>0.08713190802743041</v>
       </c>
       <c r="O23">
-        <v>0.2813354014328975</v>
+        <v>0.319972115719763</v>
       </c>
       <c r="P23">
-        <v>380.9</v>
+        <v>367.2</v>
       </c>
       <c r="Q23">
-        <v>0.05574010389990488</v>
+        <v>0.08713190802743041</v>
       </c>
       <c r="R23">
-        <v>0.2813354014328975</v>
+        <v>0.319972115719763</v>
       </c>
       <c r="S23">
         <v>0</v>
@@ -3276,55 +3231,55 @@
         <v>0</v>
       </c>
       <c r="U23">
-        <v>14655.2</v>
+        <v>8942.4</v>
       </c>
       <c r="V23">
-        <v>2.14461110704617</v>
+        <v>2.121918230785658</v>
       </c>
       <c r="W23">
-        <v>0.1092788997045862</v>
+        <v>0.06912253650074687</v>
       </c>
       <c r="X23">
-        <v>0.2453329933416132</v>
+        <v>0.4684518013964469</v>
       </c>
       <c r="Y23">
-        <v>-0.136054093637027</v>
+        <v>-0.3993292648957001</v>
       </c>
       <c r="Z23">
-        <v>0.06205567177218334</v>
+        <v>0.04128065614116622</v>
       </c>
       <c r="AA23">
         <v>0</v>
       </c>
       <c r="AB23">
-        <v>0.04911112647951365</v>
+        <v>0.07554976504198216</v>
       </c>
       <c r="AC23">
-        <v>-0.04911112647951365</v>
+        <v>-0.07554976504198216</v>
       </c>
       <c r="AD23">
-        <v>66477.10000000001</v>
+        <v>70750.60000000001</v>
       </c>
       <c r="AE23">
         <v>0</v>
       </c>
       <c r="AF23">
-        <v>66477.10000000001</v>
+        <v>70750.60000000001</v>
       </c>
       <c r="AG23">
-        <v>51821.90000000001</v>
+        <v>61808.2</v>
       </c>
       <c r="AH23">
-        <v>0.9067870130649592</v>
+        <v>0.9437830237884663</v>
       </c>
       <c r="AI23">
-        <v>0.8001624949596472</v>
+        <v>0.812439928758522</v>
       </c>
       <c r="AJ23">
-        <v>0.8834975125904861</v>
+        <v>0.9361687303570753</v>
       </c>
       <c r="AK23">
-        <v>0.7573610544791834</v>
+        <v>0.7909758809956783</v>
       </c>
       <c r="AL23">
         <v>0</v>

--- a/research/traditional_assets/database/data/china/china_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/china/china_bank_money_center.xlsx
@@ -588,112 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.05880000000000001</v>
+        <v>0.06059999999999999</v>
       </c>
       <c r="E2">
-        <v>0.0567</v>
+        <v>0.0521</v>
       </c>
       <c r="F2">
-        <v>0.0407</v>
+        <v>0.0317</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.006567627546606233</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.006567627546606233</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>0.006378296287460962</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.005650070941139129</v>
       </c>
       <c r="K2">
-        <v>267445.5</v>
+        <v>267493.1</v>
       </c>
       <c r="L2">
-        <v>0.4463663713984245</v>
+        <v>0.4493771555960238</v>
       </c>
       <c r="M2">
-        <v>74096.27800000001</v>
+        <v>75833.0552</v>
       </c>
       <c r="N2">
-        <v>0.064349581506964</v>
+        <v>0.06554727801324463</v>
       </c>
       <c r="O2">
-        <v>0.2770518778592274</v>
+        <v>0.2834953694132671</v>
       </c>
       <c r="P2">
-        <v>70276.878</v>
+        <v>75827.1652</v>
       </c>
       <c r="Q2">
-        <v>0.06103258909868543</v>
+        <v>0.06554218691587978</v>
       </c>
       <c r="R2">
-        <v>0.2627708374229516</v>
+        <v>0.283473350153705</v>
       </c>
       <c r="S2">
-        <v>3819.4</v>
+        <v>5.889999999999873</v>
       </c>
       <c r="T2">
-        <v>0.05154644879733365</v>
+        <v>7.767061454224348e-05</v>
       </c>
       <c r="U2">
-        <v>1221706.3</v>
+        <v>1366458.3</v>
       </c>
       <c r="V2">
-        <v>1.061001864755223</v>
+        <v>1.181115831973042</v>
       </c>
       <c r="W2">
-        <v>0.1003176154409968</v>
+        <v>0.1010994208906393</v>
       </c>
       <c r="X2">
-        <v>0.2114570373466015</v>
+        <v>0.162966551850205</v>
       </c>
       <c r="Y2">
-        <v>-0.1111394219056047</v>
+        <v>-0.06186713095956571</v>
       </c>
       <c r="Z2">
-        <v>0.1079023598660635</v>
+        <v>0.1075003814731816</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07153320962178572</v>
+        <v>0.0606857579155532</v>
       </c>
       <c r="AC2">
-        <v>-0.07153320962178572</v>
+        <v>-0.06058329636954127</v>
       </c>
       <c r="AD2">
-        <v>4124134.4</v>
+        <v>4465152.399999999</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>4124134.4</v>
+        <v>4465152.399999999</v>
       </c>
       <c r="AG2">
-        <v>2902428.1</v>
+        <v>3098694.1</v>
       </c>
       <c r="AH2">
-        <v>0.781737627073717</v>
+        <v>0.7942180197951506</v>
       </c>
       <c r="AI2">
-        <v>0.6056696883273074</v>
+        <v>0.611496525654218</v>
       </c>
       <c r="AJ2">
-        <v>0.7159607250601021</v>
+        <v>0.7281423867324859</v>
       </c>
       <c r="AK2">
-        <v>0.519449521991693</v>
+        <v>0.5220568205184709</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>2547.3</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>1923.9</v>
+      </c>
+      <c r="AN2">
+        <v>1150.604890870204</v>
+      </c>
+      <c r="AO2">
+        <v>1.490480116201468</v>
+      </c>
+      <c r="AP2">
+        <v>798.4884428067101</v>
+      </c>
+      <c r="AQ2">
+        <v>1.973439367950517</v>
       </c>
     </row>
     <row r="3">
@@ -704,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bank of Shanghai Co., Ltd. (SHSE:601229)</t>
+          <t>CNPC Capital Company Limited (SZSE:000617)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,46 +725,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.09089999999999999</v>
+        <v>0.0222</v>
       </c>
       <c r="E3">
-        <v>0.0843</v>
+        <v>-0.0728</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.7638381430609015</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.7638381430609015</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>0.7418182528672749</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>0.6516438003876238</v>
       </c>
       <c r="K3">
-        <v>3171.8</v>
+        <v>714.6</v>
       </c>
       <c r="L3">
-        <v>0.6058603300733497</v>
+        <v>0.139622125398097</v>
       </c>
       <c r="M3">
-        <v>795.5752000000001</v>
+        <v>441.4</v>
       </c>
       <c r="N3">
-        <v>0.06535464791509217</v>
+        <v>0.04584783173201765</v>
       </c>
       <c r="O3">
-        <v>0.2508276688315783</v>
+        <v>0.6176882171844388</v>
       </c>
       <c r="P3">
-        <v>795.5752000000001</v>
+        <v>441.4</v>
       </c>
       <c r="Q3">
-        <v>0.06535464791509217</v>
+        <v>0.04584783173201765</v>
       </c>
       <c r="R3">
-        <v>0.2508276688315783</v>
+        <v>0.6176882171844388</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -761,61 +773,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>9534.1</v>
+        <v>5353.5</v>
       </c>
       <c r="V3">
-        <v>0.783204087667992</v>
+        <v>0.5560633601661906</v>
       </c>
       <c r="W3">
-        <v>0.1132551114412015</v>
+        <v>0.05311707908096899</v>
       </c>
       <c r="X3">
-        <v>0.2261901369685548</v>
+        <v>0.09074660601228665</v>
       </c>
       <c r="Y3">
-        <v>-0.1129350255273533</v>
+        <v>-0.03762952693131767</v>
       </c>
       <c r="Z3">
-        <v>0.05695133267554428</v>
+        <v>0.1743681747163592</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>0.1136259400388215</v>
       </c>
       <c r="AB3">
-        <v>0.06628411852907684</v>
+        <v>0.0606857579155532</v>
       </c>
       <c r="AC3">
-        <v>-0.06628411852907684</v>
+        <v>0.05294018212326827</v>
       </c>
       <c r="AD3">
-        <v>79981.3</v>
+        <v>17244.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>79981.3</v>
+        <v>17244.8</v>
       </c>
       <c r="AG3">
-        <v>70447.2</v>
+        <v>11891.3</v>
       </c>
       <c r="AH3">
-        <v>0.8679044430819982</v>
+        <v>0.6417314483687664</v>
       </c>
       <c r="AI3">
-        <v>0.723770094971789</v>
+        <v>0.4057332693375495</v>
       </c>
       <c r="AJ3">
-        <v>0.8526610861240081</v>
+        <v>0.55260051675744</v>
       </c>
       <c r="AK3">
-        <v>0.6976876849515313</v>
+        <v>0.3200948604684341</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>2547.3</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>1923.9</v>
+      </c>
+      <c r="AN3">
+        <v>4.443734377818435</v>
+      </c>
+      <c r="AO3">
+        <v>1.490480116201468</v>
+      </c>
+      <c r="AP3">
+        <v>3.064215218903806</v>
+      </c>
+      <c r="AQ3">
+        <v>1.973439367950517</v>
       </c>
     </row>
     <row r="4">
@@ -835,10 +859,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.04190000000000001</v>
+        <v>0.0501</v>
       </c>
       <c r="E4">
-        <v>0.04969999999999999</v>
+        <v>0.0525</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -853,28 +877,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>3289.7</v>
+        <v>3512.9</v>
       </c>
       <c r="L4">
-        <v>0.5226225653734947</v>
+        <v>0.5307938714454081</v>
       </c>
       <c r="M4">
-        <v>8.15</v>
+        <v>888.0060000000001</v>
       </c>
       <c r="N4">
-        <v>0.0006168634574629125</v>
+        <v>0.06574364593436045</v>
       </c>
       <c r="O4">
-        <v>0.002477429552846764</v>
+        <v>0.2527843092601554</v>
       </c>
       <c r="P4">
-        <v>8.15</v>
+        <v>888.0060000000001</v>
       </c>
       <c r="Q4">
-        <v>0.0006168634574629125</v>
+        <v>0.06574364593436045</v>
       </c>
       <c r="R4">
-        <v>0.002477429552846764</v>
+        <v>0.2527843092601554</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -883,55 +907,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>22319.3</v>
+        <v>23066.4</v>
       </c>
       <c r="V4">
-        <v>1.689320314865274</v>
+        <v>1.707724085851145</v>
       </c>
       <c r="W4">
-        <v>0.09938520566154589</v>
+        <v>0.08633707069863007</v>
       </c>
       <c r="X4">
-        <v>0.2223952204158292</v>
+        <v>0.1920588486861554</v>
       </c>
       <c r="Y4">
-        <v>-0.1230100147542833</v>
+        <v>-0.1057217779875254</v>
       </c>
       <c r="Z4">
-        <v>0.05849902139183545</v>
+        <v>0.06269104893978791</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.06629769086120871</v>
+        <v>0.05670960177483945</v>
       </c>
       <c r="AC4">
-        <v>-0.06629769086120871</v>
+        <v>-0.05670960177483945</v>
       </c>
       <c r="AD4">
-        <v>84691.8</v>
+        <v>106503.9</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>84691.8</v>
+        <v>106503.9</v>
       </c>
       <c r="AG4">
-        <v>62372.5</v>
+        <v>83437.5</v>
       </c>
       <c r="AH4">
-        <v>0.8650512033240794</v>
+        <v>0.8874511503112215</v>
       </c>
       <c r="AI4">
-        <v>0.6606750303066234</v>
+        <v>0.7054425048981749</v>
       </c>
       <c r="AJ4">
-        <v>0.8252022570765171</v>
+        <v>0.8606719714146017</v>
       </c>
       <c r="AK4">
-        <v>0.5891395620120808</v>
+        <v>0.6523233068716471</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -948,7 +972,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Industrial Bank Co., Ltd. (SHSE:601166)</t>
+          <t>Bank of Shanghai Co., Ltd. (SHSE:601229)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -957,13 +981,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.103</v>
+        <v>0.0622</v>
       </c>
       <c r="E5">
-        <v>0.09669999999999999</v>
-      </c>
-      <c r="F5">
-        <v>0.105</v>
+        <v>0.0459</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -978,28 +999,28 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>12713.8</v>
+        <v>3077.8</v>
       </c>
       <c r="L5">
-        <v>0.526412110070471</v>
+        <v>0.583812287789981</v>
       </c>
       <c r="M5">
-        <v>3012.259</v>
+        <v>781.3685</v>
       </c>
       <c r="N5">
-        <v>0.05685588687179836</v>
+        <v>0.06532635231167963</v>
       </c>
       <c r="O5">
-        <v>0.2369282983844327</v>
+        <v>0.2538724088634739</v>
       </c>
       <c r="P5">
-        <v>3012.259</v>
+        <v>781.3685</v>
       </c>
       <c r="Q5">
-        <v>0.05685588687179836</v>
+        <v>0.06532635231167963</v>
       </c>
       <c r="R5">
-        <v>0.2369282983844327</v>
+        <v>0.2538724088634739</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1008,55 +1029,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>55016.4</v>
+        <v>6277.5</v>
       </c>
       <c r="V5">
-        <v>1.03842538589597</v>
+        <v>0.5248306997742663</v>
       </c>
       <c r="W5">
-        <v>0.1347563134230592</v>
+        <v>0.1010994208906393</v>
       </c>
       <c r="X5">
-        <v>0.1839164729599142</v>
+        <v>0.1788816172747101</v>
       </c>
       <c r="Y5">
-        <v>-0.04916015953685501</v>
+        <v>-0.07778219638407079</v>
       </c>
       <c r="Z5">
-        <v>0.07437309539001238</v>
+        <v>0.05225368097095365</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.06647770634259816</v>
+        <v>0.05676248677298197</v>
       </c>
       <c r="AC5">
-        <v>-0.06647770634259816</v>
+        <v>-0.05676248677298197</v>
       </c>
       <c r="AD5">
-        <v>253633.4</v>
+        <v>84832.60000000001</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>253633.4</v>
+        <v>84832.60000000001</v>
       </c>
       <c r="AG5">
-        <v>198617</v>
+        <v>78555.10000000001</v>
       </c>
       <c r="AH5">
-        <v>0.8272074986791209</v>
+        <v>0.8764277803491139</v>
       </c>
       <c r="AI5">
-        <v>0.7090864054500763</v>
+        <v>0.7268236219433518</v>
       </c>
       <c r="AJ5">
-        <v>0.7894232695383422</v>
+        <v>0.8678577623207363</v>
       </c>
       <c r="AK5">
-        <v>0.6562076689771834</v>
+        <v>0.7112959686488699</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1073,7 +1094,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bank of China Limited (SEHK:3988)</t>
+          <t>Industrial Bank Co., Ltd. (SHSE:601166)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1082,13 +1103,13 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0509</v>
+        <v>0.0824</v>
       </c>
       <c r="E6">
-        <v>0.05230000000000001</v>
+        <v>0.0687</v>
       </c>
       <c r="F6">
-        <v>0.0378</v>
+        <v>0.0317</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1103,28 +1124,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>31783.5</v>
+        <v>11585.4</v>
       </c>
       <c r="L6">
-        <v>0.4372592449922958</v>
+        <v>0.5215031014521457</v>
       </c>
       <c r="M6">
-        <v>9145.700000000001</v>
+        <v>3386.2109</v>
       </c>
       <c r="N6">
-        <v>0.07200102659543481</v>
+        <v>0.07130261082696192</v>
       </c>
       <c r="O6">
-        <v>0.2877499331414099</v>
+        <v>0.2922826056933727</v>
       </c>
       <c r="P6">
-        <v>9145.700000000001</v>
+        <v>3386.2109</v>
       </c>
       <c r="Q6">
-        <v>0.07200102659543481</v>
+        <v>0.07130261082696192</v>
       </c>
       <c r="R6">
-        <v>0.2877499331414099</v>
+        <v>0.2922826056933727</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1133,55 +1154,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>119186.4</v>
+        <v>51956.5</v>
       </c>
       <c r="V6">
-        <v>0.9383145255381359</v>
+        <v>1.094035253217998</v>
       </c>
       <c r="W6">
-        <v>0.09480471871483059</v>
+        <v>0.1222942603379153</v>
       </c>
       <c r="X6">
-        <v>0.2114570373466015</v>
+        <v>0.163702874365051</v>
       </c>
       <c r="Y6">
-        <v>-0.1166523186317709</v>
+        <v>-0.04140861402713568</v>
       </c>
       <c r="Z6">
-        <v>0.06775344858603079</v>
+        <v>0.07377460479076318</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.07000010151982883</v>
+        <v>0.05683787647469577</v>
       </c>
       <c r="AC6">
-        <v>-0.07000010151982883</v>
+        <v>-0.05683787647469577</v>
       </c>
       <c r="AD6">
-        <v>755636.8</v>
+        <v>293466.3</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>755636.8</v>
+        <v>293466.3</v>
       </c>
       <c r="AG6">
-        <v>636450.4</v>
+        <v>241509.8</v>
       </c>
       <c r="AH6">
-        <v>0.8560918117151977</v>
+        <v>0.8607135210598403</v>
       </c>
       <c r="AI6">
-        <v>0.6809339226182779</v>
+        <v>0.7293360465595989</v>
       </c>
       <c r="AJ6">
-        <v>0.8336261621575742</v>
+        <v>0.8356726026425559</v>
       </c>
       <c r="AK6">
-        <v>0.6425416304020484</v>
+        <v>0.6892046957620055</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1198,7 +1219,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Agricultural Bank of China Limited (SEHK:1288)</t>
+          <t>Zhejiang Shaoxing RuiFeng Rural Commercial Bank Co.,Ltd (SHSE:601528)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1206,15 +1227,6 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D7">
-        <v>0.0566</v>
-      </c>
-      <c r="E7">
-        <v>0.0583</v>
-      </c>
-      <c r="F7">
-        <v>0.0397</v>
-      </c>
       <c r="G7">
         <v>0</v>
       </c>
@@ -1228,28 +1240,28 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>35418.7</v>
+        <v>234.3</v>
       </c>
       <c r="L7">
-        <v>0.4394308776657448</v>
+        <v>0.5936154041043831</v>
       </c>
       <c r="M7">
-        <v>11541.5</v>
+        <v>48</v>
       </c>
       <c r="N7">
-        <v>0.07945512160767626</v>
+        <v>0.03504417025626049</v>
       </c>
       <c r="O7">
-        <v>0.3258589389220948</v>
+        <v>0.204865556978233</v>
       </c>
       <c r="P7">
-        <v>11541.5</v>
+        <v>48</v>
       </c>
       <c r="Q7">
-        <v>0.07945512160767626</v>
+        <v>0.03504417025626049</v>
       </c>
       <c r="R7">
-        <v>0.3258589389220948</v>
+        <v>0.204865556978233</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1258,55 +1270,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>282910.1</v>
+        <v>1213.6</v>
       </c>
       <c r="V7">
-        <v>1.947637343459676</v>
+        <v>0.8860334379791194</v>
       </c>
       <c r="W7">
-        <v>0.1018742735582837</v>
+        <v>0.114605752298963</v>
       </c>
       <c r="X7">
-        <v>0.1446867725389413</v>
+        <v>0.1081086470044246</v>
       </c>
       <c r="Y7">
-        <v>-0.0428124989806576</v>
+        <v>0.006497105294538438</v>
       </c>
       <c r="Z7">
-        <v>0.1413333375417023</v>
+        <v>0.1060365902802031</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.07004735076958807</v>
+        <v>0.05742046481710792</v>
       </c>
       <c r="AC7">
-        <v>-0.07004735076958807</v>
+        <v>-0.05742046481710792</v>
       </c>
       <c r="AD7">
-        <v>455047.9</v>
+        <v>3883.8</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>455047.9</v>
+        <v>3883.8</v>
       </c>
       <c r="AG7">
-        <v>172137.8</v>
+        <v>2670.2</v>
       </c>
       <c r="AH7">
-        <v>0.7580265731143784</v>
+        <v>0.7392785761873037</v>
       </c>
       <c r="AI7">
-        <v>0.551580031656149</v>
+        <v>0.6346078431372549</v>
       </c>
       <c r="AJ7">
-        <v>0.5423441197570606</v>
+        <v>0.6609569543800589</v>
       </c>
       <c r="AK7">
-        <v>0.3175507217850069</v>
+        <v>0.5442279471710419</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1323,7 +1335,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>China Construction Bank Corporation (SEHK:939)</t>
+          <t>Bank of China Limited (SEHK:3988)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1332,13 +1344,13 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0723</v>
+        <v>0.06059999999999999</v>
       </c>
       <c r="E8">
-        <v>0.0587</v>
+        <v>0.05019999999999999</v>
       </c>
       <c r="F8">
-        <v>0.0407</v>
+        <v>0.0254</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1353,28 +1365,28 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>44648.4</v>
+        <v>31537.6</v>
       </c>
       <c r="L8">
-        <v>0.480369763486071</v>
+        <v>0.4274094091435169</v>
       </c>
       <c r="M8">
-        <v>12750.561</v>
+        <v>9360.1</v>
       </c>
       <c r="N8">
-        <v>0.08039090960676389</v>
+        <v>0.0621948845254003</v>
       </c>
       <c r="O8">
-        <v>0.2855771091461284</v>
+        <v>0.2967917660189742</v>
       </c>
       <c r="P8">
-        <v>12750.561</v>
+        <v>9360.1</v>
       </c>
       <c r="Q8">
-        <v>0.08039090960676389</v>
+        <v>0.0621948845254003</v>
       </c>
       <c r="R8">
-        <v>0.2855771091461284</v>
+        <v>0.2967917660189742</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1383,55 +1395,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>155855.8</v>
+        <v>101408.6</v>
       </c>
       <c r="V8">
-        <v>0.9826539812240317</v>
+        <v>0.6738278615487557</v>
       </c>
       <c r="W8">
-        <v>0.11684468782508</v>
+        <v>0.09418240524451363</v>
       </c>
       <c r="X8">
-        <v>0.1328465852039336</v>
+        <v>0.1448603906615534</v>
       </c>
       <c r="Y8">
-        <v>-0.01600189737885357</v>
+        <v>-0.0506779854170398</v>
       </c>
       <c r="Z8">
-        <v>0.1614278598393535</v>
+        <v>0.07596753652552696</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.07006337524656986</v>
+        <v>0.05976552953971447</v>
       </c>
       <c r="AC8">
-        <v>-0.07006337524656986</v>
+        <v>-0.05976552953971447</v>
       </c>
       <c r="AD8">
-        <v>417659.5</v>
+        <v>759418.1</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>417659.5</v>
+        <v>759418.1</v>
       </c>
       <c r="AG8">
-        <v>261803.7</v>
+        <v>658009.5</v>
       </c>
       <c r="AH8">
-        <v>0.7247679675983247</v>
+        <v>0.8346038924100992</v>
       </c>
       <c r="AI8">
-        <v>0.5136582767571873</v>
+        <v>0.6731847492628297</v>
       </c>
       <c r="AJ8">
-        <v>0.6227331987506503</v>
+        <v>0.8138587255651103</v>
       </c>
       <c r="AK8">
-        <v>0.3983308378416251</v>
+        <v>0.6409044024042334</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1448,7 +1460,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Industrial and Commercial Bank of China Limited (SEHK:1398)</t>
+          <t>China Construction Bank Corporation (SEHK:939)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1457,13 +1469,13 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.0659</v>
+        <v>0.0701</v>
       </c>
       <c r="E9">
-        <v>0.0503</v>
+        <v>0.0538</v>
       </c>
       <c r="F9">
-        <v>0.0328</v>
+        <v>0.0163</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1478,28 +1490,28 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>50931.1</v>
+        <v>45441.2</v>
       </c>
       <c r="L9">
-        <v>0.4768008133430195</v>
+        <v>0.4881070026037415</v>
       </c>
       <c r="M9">
-        <v>14693.5</v>
+        <v>13250.583</v>
       </c>
       <c r="N9">
-        <v>0.06853324353217077</v>
+        <v>0.08722286073129694</v>
       </c>
       <c r="O9">
-        <v>0.2884975977349792</v>
+        <v>0.291598439301779</v>
       </c>
       <c r="P9">
-        <v>14693.5</v>
+        <v>13250.583</v>
       </c>
       <c r="Q9">
-        <v>0.06853324353217077</v>
+        <v>0.08722286073129694</v>
       </c>
       <c r="R9">
-        <v>0.2884975977349792</v>
+        <v>0.291598439301779</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1508,55 +1520,55 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>369833.4</v>
+        <v>115275.1</v>
       </c>
       <c r="V9">
-        <v>1.724972434650065</v>
+        <v>0.7588061591770211</v>
       </c>
       <c r="W9">
-        <v>0.1043262397255826</v>
+        <v>0.1183648782337842</v>
       </c>
       <c r="X9">
-        <v>0.09586117636008816</v>
+        <v>0.1091013031622659</v>
       </c>
       <c r="Y9">
-        <v>0.008465063365494477</v>
+        <v>0.009263575071518329</v>
       </c>
       <c r="Z9">
-        <v>0.325497250052488</v>
+        <v>0.1423897771943998</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.07016314864012467</v>
+        <v>0.05989702346072887</v>
       </c>
       <c r="AC9">
-        <v>-0.07016314864012467</v>
+        <v>-0.05989702346072887</v>
       </c>
       <c r="AD9">
-        <v>230126.5</v>
+        <v>439831.2</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>230126.5</v>
+        <v>439831.2</v>
       </c>
       <c r="AG9">
-        <v>-139706.9</v>
+        <v>324556.1</v>
       </c>
       <c r="AH9">
-        <v>0.5176895124943171</v>
+        <v>0.7432750044106643</v>
       </c>
       <c r="AI9">
-        <v>0.3231595437922738</v>
+        <v>0.5088917845145426</v>
       </c>
       <c r="AJ9">
-        <v>-1.870422410757679</v>
+        <v>0.6811643903897916</v>
       </c>
       <c r="AK9">
-        <v>-0.408164582997352</v>
+        <v>0.4333093329911961</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1573,7 +1585,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Postal Savings Bank of China Co., Ltd. (SEHK:1658)</t>
+          <t>Agricultural Bank of China Limited (SEHK:1288)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1582,13 +1594,13 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.09810000000000001</v>
+        <v>0.0505</v>
       </c>
       <c r="E10">
-        <v>0.134</v>
+        <v>0.0563</v>
       </c>
       <c r="F10">
-        <v>0.11</v>
+        <v>0.0325</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1603,28 +1615,28 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>12019.7</v>
+        <v>36860.7</v>
       </c>
       <c r="L10">
-        <v>0.2879846084916849</v>
+        <v>0.4551895063893265</v>
       </c>
       <c r="M10">
-        <v>3470.39</v>
+        <v>12609</v>
       </c>
       <c r="N10">
-        <v>0.05300927481685598</v>
+        <v>0.07175477383503061</v>
       </c>
       <c r="O10">
-        <v>0.2887251761691224</v>
+        <v>0.3420716372722168</v>
       </c>
       <c r="P10">
-        <v>3470.39</v>
+        <v>12609</v>
       </c>
       <c r="Q10">
-        <v>0.05300927481685598</v>
+        <v>0.07175477383503061</v>
       </c>
       <c r="R10">
-        <v>0.2887251761691224</v>
+        <v>0.3420716372722168</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1633,55 +1645,55 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>22506.5</v>
+        <v>341911.3</v>
       </c>
       <c r="V10">
-        <v>0.3437807403967764</v>
+        <v>1.945734634240725</v>
       </c>
       <c r="W10">
-        <v>0.1061329043172976</v>
+        <v>0.1030195386846952</v>
       </c>
       <c r="X10">
-        <v>0.0842139528616507</v>
+        <v>0.10896459390847</v>
       </c>
       <c r="Y10">
-        <v>0.02191895145564693</v>
+        <v>-0.005945055223774837</v>
       </c>
       <c r="Z10">
-        <v>0.3748688682431219</v>
+        <v>0.1496897745285155</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.07023530465205577</v>
+        <v>0.05989780540861271</v>
       </c>
       <c r="AC10">
-        <v>-0.07023530465205577</v>
+        <v>-0.05989780540861271</v>
       </c>
       <c r="AD10">
-        <v>38109</v>
+        <v>507313</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>38109</v>
+        <v>507313</v>
       </c>
       <c r="AG10">
-        <v>15602.5</v>
+        <v>165401.7</v>
       </c>
       <c r="AH10">
-        <v>0.367930594362047</v>
+        <v>0.7427319037855225</v>
       </c>
       <c r="AI10">
-        <v>0.2489324885998209</v>
+        <v>0.5674678873755558</v>
       </c>
       <c r="AJ10">
-        <v>0.1924568984126083</v>
+        <v>0.4848709506069913</v>
       </c>
       <c r="AK10">
-        <v>0.1194832107039803</v>
+        <v>0.2995957672298852</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1698,7 +1710,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Zhejiang Shaoxing RuiFeng Rural Commercial Bank Co.,Ltd (SHSE:601528)</t>
+          <t>Postal Savings Bank of China Co., Ltd. (SEHK:1658)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1707,10 +1719,13 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.0707</v>
+        <v>0.08</v>
       </c>
       <c r="E11">
-        <v>0.13</v>
+        <v>0.1</v>
+      </c>
+      <c r="F11">
+        <v>0.0552</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1725,28 +1740,28 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>205.3</v>
+        <v>11927.5</v>
       </c>
       <c r="L11">
-        <v>0.5389866106589657</v>
+        <v>0.2775521886540435</v>
       </c>
       <c r="M11">
-        <v>61.7</v>
+        <v>5142.3</v>
       </c>
       <c r="N11">
-        <v>0.04468100514157433</v>
+        <v>0.08845948079963256</v>
       </c>
       <c r="O11">
-        <v>0.3005358012664394</v>
+        <v>0.4311297421924125</v>
       </c>
       <c r="P11">
-        <v>61.7</v>
+        <v>5142.3</v>
       </c>
       <c r="Q11">
-        <v>0.04468100514157433</v>
+        <v>0.08845948079963256</v>
       </c>
       <c r="R11">
-        <v>0.3005358012664394</v>
+        <v>0.4311297421924125</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1755,55 +1770,55 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>1086.4</v>
+        <v>35377.4</v>
       </c>
       <c r="V11">
-        <v>0.7867332898834094</v>
+        <v>0.6085732913367405</v>
       </c>
       <c r="W11">
-        <v>0.1003176154409968</v>
+        <v>0.1039310373672488</v>
       </c>
       <c r="X11">
-        <v>0.1178743712093715</v>
+        <v>0.09108035266801605</v>
       </c>
       <c r="Y11">
-        <v>-0.01755675576837464</v>
+        <v>0.0128506846992328</v>
       </c>
       <c r="Z11">
-        <v>0.09730489206795249</v>
+        <v>0.3296401441785863</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.071091573985052</v>
+        <v>0.06003954091199037</v>
       </c>
       <c r="AC11">
-        <v>-0.071091573985052</v>
+        <v>-0.06003954091199037</v>
       </c>
       <c r="AD11">
-        <v>2764.3</v>
+        <v>105292.6</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>2764.3</v>
+        <v>105292.6</v>
       </c>
       <c r="AG11">
-        <v>1677.9</v>
+        <v>69915.20000000001</v>
       </c>
       <c r="AH11">
-        <v>0.666867702402779</v>
+        <v>0.6442897414888729</v>
       </c>
       <c r="AI11">
-        <v>0.5706647398843931</v>
+        <v>0.4562893485134236</v>
       </c>
       <c r="AJ11">
-        <v>0.5485484503726952</v>
+        <v>0.5460124376302746</v>
       </c>
       <c r="AK11">
-        <v>0.4465350223546945</v>
+        <v>0.3578403222421833</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1820,7 +1835,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bank of Communications Co., Ltd. (SEHK:3328)</t>
+          <t>Industrial and Commercial Bank of China Limited (SEHK:1398)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1829,13 +1844,13 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.0476</v>
+        <v>0.0388</v>
       </c>
       <c r="E12">
-        <v>0.0551</v>
+        <v>0.04019999999999999</v>
       </c>
       <c r="F12">
-        <v>0.031</v>
+        <v>0.0211</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1850,28 +1865,28 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>13374.8</v>
+        <v>49693</v>
       </c>
       <c r="L12">
-        <v>0.4297207335723741</v>
+        <v>0.495198785047474</v>
       </c>
       <c r="M12">
-        <v>251.5</v>
+        <v>14824.6</v>
       </c>
       <c r="N12">
-        <v>0.005335624575695859</v>
+        <v>0.06612530916925191</v>
       </c>
       <c r="O12">
-        <v>0.018804019499357</v>
+        <v>0.2983237075644457</v>
       </c>
       <c r="P12">
-        <v>251.5</v>
+        <v>14824.6</v>
       </c>
       <c r="Q12">
-        <v>0.005335624575695859</v>
+        <v>0.06612530916925191</v>
       </c>
       <c r="R12">
-        <v>0.018804019499357</v>
+        <v>0.2983237075644457</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -1880,55 +1895,55 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>26740.6</v>
+        <v>453848.8</v>
       </c>
       <c r="V12">
-        <v>0.5673073659198914</v>
+        <v>2.024398109634929</v>
       </c>
       <c r="W12">
-        <v>0.09828926356540725</v>
+        <v>0.1079405474421003</v>
       </c>
       <c r="X12">
-        <v>0.2555810166427711</v>
+        <v>0.08413289000977314</v>
       </c>
       <c r="Y12">
-        <v>-0.1572917530773639</v>
+        <v>0.02380765743232717</v>
       </c>
       <c r="Z12">
-        <v>0.06313442445244918</v>
+        <v>0.2955035285352715</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.07131519166166993</v>
+        <v>0.0601289608212585</v>
       </c>
       <c r="AC12">
-        <v>-0.07131519166166993</v>
+        <v>-0.0601289608212585</v>
       </c>
       <c r="AD12">
-        <v>368127.7</v>
+        <v>312384.3</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>368127.7</v>
+        <v>312384.3</v>
       </c>
       <c r="AG12">
-        <v>341387.1</v>
+        <v>-141464.5</v>
       </c>
       <c r="AH12">
-        <v>0.8864914029326426</v>
+        <v>0.5821832896052695</v>
       </c>
       <c r="AI12">
-        <v>0.7137778225888544</v>
+        <v>0.3827470193180561</v>
       </c>
       <c r="AJ12">
-        <v>0.87867902835121</v>
+        <v>-1.710057419159867</v>
       </c>
       <c r="AK12">
-        <v>0.6981261332964148</v>
+        <v>-0.3904460509650302</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -1945,7 +1960,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>China Merchants Bank Co., Ltd. (SHSE:600036)</t>
+          <t>Bank of Communications Co., Ltd. (SEHK:3328)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1954,13 +1969,13 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.134</v>
+        <v>0.0591</v>
       </c>
       <c r="E13">
-        <v>0.141</v>
+        <v>0.0503</v>
       </c>
       <c r="F13">
-        <v>0.112</v>
+        <v>0.0386</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1975,28 +1990,28 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>18726.9</v>
+        <v>12803.9</v>
       </c>
       <c r="L13">
-        <v>0.4677632071937056</v>
+        <v>0.426961758546638</v>
       </c>
       <c r="M13">
-        <v>5435.7</v>
+        <v>246.7</v>
       </c>
       <c r="N13">
-        <v>0.03963570472832804</v>
+        <v>0.004602603353351953</v>
       </c>
       <c r="O13">
-        <v>0.2902616022940262</v>
+        <v>0.01926756691320613</v>
       </c>
       <c r="P13">
-        <v>5435.7</v>
+        <v>246.7</v>
       </c>
       <c r="Q13">
-        <v>0.03963570472832804</v>
+        <v>0.004602603353351953</v>
       </c>
       <c r="R13">
-        <v>0.2902616022940262</v>
+        <v>0.01926756691320613</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -2005,55 +2020,55 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>1647.7</v>
+        <v>26257.3</v>
       </c>
       <c r="V13">
-        <v>0.01201459806112665</v>
+        <v>0.4898740860558096</v>
       </c>
       <c r="W13">
-        <v>0.1598665879010558</v>
+        <v>0.09539849897440597</v>
       </c>
       <c r="X13">
-        <v>0.09050211968471944</v>
+        <v>0.1777469809858484</v>
       </c>
       <c r="Y13">
-        <v>0.06936446821633641</v>
+        <v>-0.0823484820114424</v>
       </c>
       <c r="Z13">
-        <v>0.1373211754843542</v>
+        <v>0.06441907499240099</v>
       </c>
       <c r="AA13">
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.07153320962178572</v>
+        <v>0.06058329636954127</v>
       </c>
       <c r="AC13">
-        <v>-0.07153320962178572</v>
+        <v>-0.06058329636954127</v>
       </c>
       <c r="AD13">
-        <v>116203.1</v>
+        <v>376497.1</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>116203.1</v>
+        <v>376497.1</v>
       </c>
       <c r="AG13">
-        <v>114555.4</v>
+        <v>350239.8</v>
       </c>
       <c r="AH13">
-        <v>0.4586760483546916</v>
+        <v>0.8753767752963749</v>
       </c>
       <c r="AI13">
-        <v>0.4711982673990995</v>
+        <v>0.7191270551625316</v>
       </c>
       <c r="AJ13">
-        <v>0.4551323437038756</v>
+        <v>0.8672738874984864</v>
       </c>
       <c r="AK13">
-        <v>0.4676413941302444</v>
+        <v>0.7042967475121664</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2070,7 +2085,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ping An Bank Co., Ltd. (SZSE:000001)</t>
+          <t>China Merchants Bank Co., Ltd. (SHSE:600036)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2079,13 +2094,13 @@
         </is>
       </c>
       <c r="D14">
-        <v>0.129</v>
+        <v>0.101</v>
       </c>
       <c r="E14">
-        <v>0.137</v>
+        <v>0.13</v>
       </c>
       <c r="F14">
-        <v>0.193</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2100,28 +2115,28 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>6165</v>
+        <v>19869.5</v>
       </c>
       <c r="L14">
-        <v>0.4128772150711904</v>
+        <v>0.4940179312882582</v>
       </c>
       <c r="M14">
-        <v>768.6</v>
+        <v>6531.3</v>
       </c>
       <c r="N14">
-        <v>0.02075793749392332</v>
+        <v>0.06738891554331172</v>
       </c>
       <c r="O14">
-        <v>0.1246715328467153</v>
+        <v>0.3287098316515262</v>
       </c>
       <c r="P14">
-        <v>768.6</v>
+        <v>6531.3</v>
       </c>
       <c r="Q14">
-        <v>0.02075793749392332</v>
+        <v>0.06738891554331172</v>
       </c>
       <c r="R14">
-        <v>0.1246715328467153</v>
+        <v>0.3287098316515262</v>
       </c>
       <c r="S14">
         <v>0</v>
@@ -2130,55 +2145,55 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>26643.2</v>
+        <v>1954.6</v>
       </c>
       <c r="V14">
-        <v>0.7195652878455605</v>
+        <v>0.0201672522041488</v>
       </c>
       <c r="W14">
-        <v>0.1076963121219056</v>
+        <v>0.1584523749713909</v>
       </c>
       <c r="X14">
-        <v>0.1649419319754076</v>
+        <v>0.08141074406157253</v>
       </c>
       <c r="Y14">
-        <v>-0.05724561985350199</v>
+        <v>0.07704163090981839</v>
       </c>
       <c r="Z14">
-        <v>0.0820846210764378</v>
+        <v>0.1659149927087695</v>
       </c>
       <c r="AA14">
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.07236585292986131</v>
+        <v>0.06127710386714286</v>
       </c>
       <c r="AC14">
-        <v>-0.07236585292986131</v>
+        <v>-0.06127710386714286</v>
       </c>
       <c r="AD14">
-        <v>147625.6</v>
+        <v>119178</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>147625.6</v>
+        <v>119178</v>
       </c>
       <c r="AG14">
-        <v>120982.4</v>
+        <v>117223.4</v>
       </c>
       <c r="AH14">
-        <v>0.7994783712532303</v>
+        <v>0.5515010585499601</v>
       </c>
       <c r="AI14">
-        <v>0.7117285641003883</v>
+        <v>0.4598757643180119</v>
       </c>
       <c r="AJ14">
-        <v>0.7656668092743967</v>
+        <v>0.5474073620932564</v>
       </c>
       <c r="AK14">
-        <v>0.669242241192376</v>
+        <v>0.455771040210266</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2195,7 +2210,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Jilin Jiutai Rural Commercial Bank Corporation Limited (SEHK:6122)</t>
+          <t>Ping An Bank Co., Ltd. (SZSE:000001)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2204,10 +2219,13 @@
         </is>
       </c>
       <c r="D15">
-        <v>-0.0136</v>
+        <v>0.0955</v>
       </c>
       <c r="E15">
-        <v>-0.0505</v>
+        <v>0.146</v>
+      </c>
+      <c r="F15">
+        <v>0.08869999999999999</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2222,82 +2240,85 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>179.7</v>
+        <v>6645.8</v>
       </c>
       <c r="L15">
-        <v>0.2540288379983036</v>
+        <v>0.4457276995305164</v>
       </c>
       <c r="M15">
-        <v>-0</v>
+        <v>877.1</v>
       </c>
       <c r="N15">
-        <v>-0</v>
+        <v>0.03413106078294031</v>
       </c>
       <c r="O15">
-        <v>-0</v>
+        <v>0.1319780914261639</v>
       </c>
       <c r="P15">
-        <v>-0</v>
+        <v>877.1</v>
       </c>
       <c r="Q15">
-        <v>-0</v>
+        <v>0.03413106078294031</v>
       </c>
       <c r="R15">
-        <v>-0</v>
+        <v>0.1319780914261639</v>
       </c>
       <c r="S15">
         <v>0</v>
       </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
       <c r="U15">
-        <v>4626.9</v>
+        <v>41213</v>
       </c>
       <c r="V15">
-        <v>3.246491720460286</v>
+        <v>1.603743481983034</v>
       </c>
       <c r="W15">
-        <v>0.07734354824825686</v>
+        <v>0.1166171242467739</v>
       </c>
       <c r="X15">
-        <v>0.09953365987851573</v>
+        <v>0.1496697969152062</v>
       </c>
       <c r="Y15">
-        <v>-0.02219011163025887</v>
+        <v>-0.0330526726684323</v>
       </c>
       <c r="Z15">
-        <v>1.310242637525466</v>
+        <v>0.0829663560575456</v>
       </c>
       <c r="AA15">
         <v>0</v>
       </c>
       <c r="AB15">
-        <v>0.07254478877275863</v>
+        <v>0.0614404419512195</v>
       </c>
       <c r="AC15">
-        <v>-0.07254478877275863</v>
+        <v>-0.0614404419512195</v>
       </c>
       <c r="AD15">
-        <v>1750.5</v>
+        <v>137108.4</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>1750.5</v>
+        <v>137108.4</v>
       </c>
       <c r="AG15">
-        <v>-2876.4</v>
+        <v>95895.39999999999</v>
       </c>
       <c r="AH15">
-        <v>0.5512170545076677</v>
+        <v>0.8421560823161743</v>
       </c>
       <c r="AI15">
-        <v>0.3920141532673445</v>
+        <v>0.6822854515398006</v>
       </c>
       <c r="AJ15">
-        <v>1.982083792723264</v>
+        <v>0.7886562922000701</v>
       </c>
       <c r="AK15">
-        <v>17.81052631578952</v>
+        <v>0.600315759952323</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2323,13 +2344,13 @@
         </is>
       </c>
       <c r="D16">
-        <v>0.061</v>
+        <v>0.0626</v>
       </c>
       <c r="E16">
-        <v>0.0784</v>
+        <v>0.0828</v>
       </c>
       <c r="F16">
-        <v>0.0501</v>
+        <v>0.0675</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2344,85 +2365,85 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>8572.6</v>
+        <v>9104.700000000001</v>
       </c>
       <c r="L16">
-        <v>0.4444893811183009</v>
+        <v>0.4586334740426561</v>
       </c>
       <c r="M16">
-        <v>3026</v>
+        <v>2690.29</v>
       </c>
       <c r="N16">
-        <v>0.09701485359605785</v>
+        <v>0.08293406989756126</v>
       </c>
       <c r="O16">
-        <v>0.3529850920374215</v>
+        <v>0.2954836513009764</v>
       </c>
       <c r="P16">
-        <v>2558.8</v>
+        <v>2684.4</v>
       </c>
       <c r="Q16">
-        <v>0.08203622187098243</v>
+        <v>0.08275249777273581</v>
       </c>
       <c r="R16">
-        <v>0.298485873597275</v>
+        <v>0.2948367326765297</v>
       </c>
       <c r="S16">
-        <v>467.1999999999998</v>
+        <v>5.889999999999873</v>
       </c>
       <c r="T16">
-        <v>0.1543952412425644</v>
+        <v>0.002189355050942416</v>
       </c>
       <c r="U16">
-        <v>34803.3</v>
+        <v>45030</v>
       </c>
       <c r="V16">
-        <v>1.115808676192888</v>
+        <v>1.388148180117082</v>
       </c>
       <c r="W16">
-        <v>0.09001163391390904</v>
+        <v>0.09012627002542031</v>
       </c>
       <c r="X16">
-        <v>0.2481377484981385</v>
+        <v>0.162966551850205</v>
       </c>
       <c r="Y16">
-        <v>-0.1581261145842295</v>
+        <v>-0.07284028182478472</v>
       </c>
       <c r="Z16">
-        <v>0.07609151940005492</v>
+        <v>0.07191245515840858</v>
       </c>
       <c r="AA16">
         <v>0</v>
       </c>
       <c r="AB16">
-        <v>0.0725681944848236</v>
+        <v>0.06145038473061266</v>
       </c>
       <c r="AC16">
-        <v>-0.0725681944848236</v>
+        <v>-0.06145038473061266</v>
       </c>
       <c r="AD16">
-        <v>233807.5</v>
+        <v>199017.8</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>233807.5</v>
+        <v>199017.8</v>
       </c>
       <c r="AG16">
-        <v>199004.2</v>
+        <v>153987.8</v>
       </c>
       <c r="AH16">
-        <v>0.8822971140224892</v>
+        <v>0.8598489479889759</v>
       </c>
       <c r="AI16">
-        <v>0.7103605404643385</v>
+        <v>0.6595081635831618</v>
       </c>
       <c r="AJ16">
-        <v>0.8645015775734778</v>
+        <v>0.8259964908460001</v>
       </c>
       <c r="AK16">
-        <v>0.6761125639108243</v>
+        <v>0.5997881100114124</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -2448,13 +2469,13 @@
         </is>
       </c>
       <c r="D17">
-        <v>0.07629999999999999</v>
+        <v>0.0617</v>
       </c>
       <c r="E17">
-        <v>0.0747</v>
+        <v>0.06269999999999999</v>
       </c>
       <c r="F17">
-        <v>0.062</v>
+        <v>0.0236</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2469,28 +2490,28 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>6313.1</v>
+        <v>6291.4</v>
       </c>
       <c r="L17">
-        <v>0.4441716151183407</v>
+        <v>0.455189378866259</v>
       </c>
       <c r="M17">
-        <v>1595</v>
+        <v>1488.2</v>
       </c>
       <c r="N17">
-        <v>0.0715997953008987</v>
+        <v>0.06543091547004565</v>
       </c>
       <c r="O17">
-        <v>0.2526492531402956</v>
+        <v>0.2365451250913946</v>
       </c>
       <c r="P17">
-        <v>1595</v>
+        <v>1488.2</v>
       </c>
       <c r="Q17">
-        <v>0.0715997953008987</v>
+        <v>0.06543091547004565</v>
       </c>
       <c r="R17">
-        <v>0.2526492531402956</v>
+        <v>0.2365451250913946</v>
       </c>
       <c r="S17">
         <v>0</v>
@@ -2499,55 +2520,55 @@
         <v>0</v>
       </c>
       <c r="U17">
-        <v>16195.1</v>
+        <v>14096.8</v>
       </c>
       <c r="V17">
-        <v>0.7270005297038148</v>
+        <v>0.6197866746392551</v>
       </c>
       <c r="W17">
-        <v>0.09941529676877846</v>
+        <v>0.10241709154604</v>
       </c>
       <c r="X17">
-        <v>0.2536654125926542</v>
+        <v>0.2193807511961028</v>
       </c>
       <c r="Y17">
-        <v>-0.1542501158238757</v>
+        <v>-0.1169636596500628</v>
       </c>
       <c r="Z17">
-        <v>0.06563563568186122</v>
+        <v>0.06106100312958902</v>
       </c>
       <c r="AA17">
         <v>0</v>
       </c>
       <c r="AB17">
-        <v>0.07257587506506158</v>
+        <v>0.06147576870955785</v>
       </c>
       <c r="AC17">
-        <v>-0.07257587506506158</v>
+        <v>-0.06147576870955785</v>
       </c>
       <c r="AD17">
-        <v>172178.3</v>
+        <v>216720</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>172178.3</v>
+        <v>216720</v>
       </c>
       <c r="AG17">
-        <v>155983.2</v>
+        <v>202623.2</v>
       </c>
       <c r="AH17">
-        <v>0.8854407885838824</v>
+        <v>0.905018946433001</v>
       </c>
       <c r="AI17">
-        <v>0.7085045665623527</v>
+        <v>0.7418033502320188</v>
       </c>
       <c r="AJ17">
-        <v>0.8750329575148182</v>
+        <v>0.8990778629422659</v>
       </c>
       <c r="AK17">
-        <v>0.6876917257366368</v>
+        <v>0.7287133783434351</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -2585,28 +2606,28 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>1547.6</v>
+        <v>1698.8</v>
       </c>
       <c r="L18">
-        <v>0.5125012418452164</v>
+        <v>0.5374928810985256</v>
       </c>
       <c r="M18">
-        <v>1081.7</v>
+        <v>799.4</v>
       </c>
       <c r="N18">
-        <v>0.1315600637306771</v>
+        <v>0.1023939747153232</v>
       </c>
       <c r="O18">
-        <v>0.6989532178857587</v>
+        <v>0.470567459383094</v>
       </c>
       <c r="P18">
-        <v>1081.7</v>
+        <v>799.4</v>
       </c>
       <c r="Q18">
-        <v>0.1315600637306771</v>
+        <v>0.1023939747153232</v>
       </c>
       <c r="R18">
-        <v>0.6989532178857587</v>
+        <v>0.470567459383094</v>
       </c>
       <c r="S18">
         <v>0</v>
@@ -2615,55 +2636,55 @@
         <v>0</v>
       </c>
       <c r="U18">
-        <v>7420.2</v>
+        <v>4287.2</v>
       </c>
       <c r="V18">
-        <v>0.9024701718539059</v>
+        <v>0.5491411663741977</v>
       </c>
       <c r="W18">
-        <v>0.1061039237060957</v>
+        <v>0.120247743762166</v>
       </c>
       <c r="X18">
-        <v>0.1528005630839277</v>
+        <v>0.132577012595021</v>
       </c>
       <c r="Y18">
-        <v>-0.04669663937783204</v>
+        <v>-0.01232926883285498</v>
       </c>
       <c r="Z18">
-        <v>0.08072445365234245</v>
+        <v>0.08959048480227221</v>
       </c>
       <c r="AA18">
         <v>0</v>
       </c>
       <c r="AB18">
-        <v>0.07341634673419581</v>
+        <v>0.06223585186809145</v>
       </c>
       <c r="AC18">
-        <v>-0.07341634673419581</v>
+        <v>-0.06223585186809145</v>
       </c>
       <c r="AD18">
-        <v>28571</v>
+        <v>33627.2</v>
       </c>
       <c r="AE18">
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>28571</v>
+        <v>33627.2</v>
       </c>
       <c r="AG18">
-        <v>21150.8</v>
+        <v>29340</v>
       </c>
       <c r="AH18">
-        <v>0.7765314692156954</v>
+        <v>0.8115788127227925</v>
       </c>
       <c r="AI18">
-        <v>0.6608670308979798</v>
+        <v>0.6830354241143971</v>
       </c>
       <c r="AJ18">
-        <v>0.72007871201005</v>
+        <v>0.789832853708634</v>
       </c>
       <c r="AK18">
-        <v>0.5905999039438853</v>
+        <v>0.652800768943237</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -2689,13 +2710,13 @@
         </is>
       </c>
       <c r="D19">
-        <v>-0.00181</v>
+        <v>-0.0249</v>
       </c>
       <c r="E19">
-        <v>-0.008920000000000001</v>
+        <v>-0.0698</v>
       </c>
       <c r="F19">
-        <v>0.0286</v>
+        <v>-0.08779999999999999</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2710,28 +2731,28 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>7299.2</v>
+        <v>5303.2</v>
       </c>
       <c r="L19">
-        <v>0.4614489821722089</v>
+        <v>0.3978752775943821</v>
       </c>
       <c r="M19">
-        <v>1702.4276</v>
+        <v>1291.4968</v>
       </c>
       <c r="N19">
-        <v>0.0549503440796354</v>
+        <v>0.04712975951538152</v>
       </c>
       <c r="O19">
-        <v>0.2332348202542745</v>
+        <v>0.2435316035601146</v>
       </c>
       <c r="P19">
-        <v>1702.4276</v>
+        <v>1291.4968</v>
       </c>
       <c r="Q19">
-        <v>0.0549503440796354</v>
+        <v>0.04712975951538152</v>
       </c>
       <c r="R19">
-        <v>0.2332348202542745</v>
+        <v>0.2435316035601146</v>
       </c>
       <c r="S19">
         <v>0</v>
@@ -2740,55 +2761,55 @@
         <v>0</v>
       </c>
       <c r="U19">
-        <v>25515.5</v>
+        <v>25652.8</v>
       </c>
       <c r="V19">
-        <v>0.8235801066453203</v>
+        <v>0.9361310805386271</v>
       </c>
       <c r="W19">
-        <v>0.07435719815818426</v>
+        <v>0.05698339989921099</v>
       </c>
       <c r="X19">
-        <v>0.3023221179855862</v>
+        <v>0.2320719501957128</v>
       </c>
       <c r="Y19">
-        <v>-0.227964919827402</v>
+        <v>-0.1750885502965018</v>
       </c>
       <c r="Z19">
-        <v>0.04490542833896474</v>
+        <v>0.03565647391800413</v>
       </c>
       <c r="AA19">
         <v>0</v>
       </c>
       <c r="AB19">
-        <v>0.07392197854592872</v>
+        <v>0.06239195640379271</v>
       </c>
       <c r="AC19">
-        <v>-0.07392197854592872</v>
+        <v>-0.06239195640379271</v>
       </c>
       <c r="AD19">
-        <v>303037</v>
+        <v>282025.6</v>
       </c>
       <c r="AE19">
         <v>0</v>
       </c>
       <c r="AF19">
-        <v>303037</v>
+        <v>282025.6</v>
       </c>
       <c r="AG19">
-        <v>277521.5</v>
+        <v>256372.8</v>
       </c>
       <c r="AH19">
-        <v>0.9072469703746682</v>
+        <v>0.9114399897100656</v>
       </c>
       <c r="AI19">
-        <v>0.7546747387911488</v>
+        <v>0.7397883715299665</v>
       </c>
       <c r="AJ19">
-        <v>0.8995755952865242</v>
+        <v>0.9034343309048904</v>
       </c>
       <c r="AK19">
-        <v>0.7380282476710697</v>
+        <v>0.7210153558253618</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -2805,7 +2826,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>China Zheshang Bank Co., Ltd (SEHK:2016)</t>
+          <t>China Minsheng Banking Corp., Ltd. (SHSE:600016)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2814,10 +2835,13 @@
         </is>
       </c>
       <c r="D20">
-        <v>0.052</v>
+        <v>-0.0373</v>
       </c>
       <c r="E20">
-        <v>0.04219999999999999</v>
+        <v>-0.0767</v>
+      </c>
+      <c r="F20">
+        <v>0.0314</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -2832,85 +2856,85 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>1912.6</v>
+        <v>4806.1</v>
       </c>
       <c r="L20">
-        <v>0.4136424585838487</v>
+        <v>0.3744001620341519</v>
       </c>
       <c r="M20">
-        <v>2064.4</v>
+        <v>28.8</v>
       </c>
       <c r="N20">
-        <v>0.2358155420764653</v>
+        <v>0.001337885861612431</v>
       </c>
       <c r="O20">
-        <v>1.079368399037959</v>
+        <v>0.005992384677805289</v>
       </c>
       <c r="P20">
-        <v>-0</v>
+        <v>28.8</v>
       </c>
       <c r="Q20">
-        <v>-0</v>
+        <v>0.001337885861612431</v>
       </c>
       <c r="R20">
-        <v>-0</v>
+        <v>0.005992384677805289</v>
       </c>
       <c r="S20">
-        <v>2064.4</v>
+        <v>0</v>
       </c>
       <c r="T20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U20">
-        <v>11162.6</v>
+        <v>28615.2</v>
       </c>
       <c r="V20">
-        <v>1.275099094159442</v>
+        <v>1.329301094000418</v>
       </c>
       <c r="W20">
-        <v>0.1008712712543774</v>
+        <v>0.05909781185251677</v>
       </c>
       <c r="X20">
-        <v>0.2344462329477097</v>
+        <v>0.1895524202837576</v>
       </c>
       <c r="Y20">
-        <v>-0.1335749616933322</v>
+        <v>-0.1304546084312408</v>
       </c>
       <c r="Z20">
-        <v>0.06000166101747702</v>
+        <v>0.05035613091621185</v>
       </c>
       <c r="AA20">
         <v>0</v>
       </c>
       <c r="AB20">
-        <v>0.0751683631392818</v>
+        <v>0.06324666895327041</v>
       </c>
       <c r="AC20">
-        <v>-0.0751683631392818</v>
+        <v>-0.06324666895327041</v>
       </c>
       <c r="AD20">
-        <v>60566.6</v>
+        <v>166491.8</v>
       </c>
       <c r="AE20">
         <v>0</v>
       </c>
       <c r="AF20">
-        <v>60566.6</v>
+        <v>166491.8</v>
       </c>
       <c r="AG20">
-        <v>49404</v>
+        <v>137876.6</v>
       </c>
       <c r="AH20">
-        <v>0.8737134111068957</v>
+        <v>0.8855084850783141</v>
       </c>
       <c r="AI20">
-        <v>0.7257761459446763</v>
+        <v>0.6569457580718541</v>
       </c>
       <c r="AJ20">
-        <v>0.8494746235704963</v>
+        <v>0.8649555748915799</v>
       </c>
       <c r="AK20">
-        <v>0.6834310440708166</v>
+        <v>0.6132812378373786</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -2927,7 +2951,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>China Minsheng Banking Corp., Ltd. (SHSE:600016)</t>
+          <t>China Zheshang Bank Co., Ltd (SEHK:2016)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2936,13 +2960,10 @@
         </is>
       </c>
       <c r="D21">
-        <v>-0.0365</v>
+        <v>0.0776</v>
       </c>
       <c r="E21">
-        <v>-0.0776</v>
-      </c>
-      <c r="F21">
-        <v>-0.0126</v>
+        <v>0.0481</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -2957,85 +2978,85 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>4592.4</v>
+        <v>2033</v>
       </c>
       <c r="L21">
-        <v>0.3591038823943387</v>
+        <v>0.405918057663126</v>
       </c>
       <c r="M21">
-        <v>1560.5</v>
+        <v>629.6</v>
       </c>
       <c r="N21">
-        <v>0.07568152168114339</v>
+        <v>0.06852789115646259</v>
       </c>
       <c r="O21">
-        <v>0.3398005400226461</v>
+        <v>0.3096901131333005</v>
       </c>
       <c r="P21">
-        <v>272.7</v>
+        <v>629.6</v>
       </c>
       <c r="Q21">
-        <v>0.01322547322169036</v>
+        <v>0.06852789115646259</v>
       </c>
       <c r="R21">
-        <v>0.05938071596550824</v>
+        <v>0.3096901131333005</v>
       </c>
       <c r="S21">
-        <v>1287.8</v>
+        <v>0</v>
       </c>
       <c r="T21">
-        <v>0.8252483178468439</v>
+        <v>0</v>
       </c>
       <c r="U21">
-        <v>10668.7</v>
+        <v>11358</v>
       </c>
       <c r="V21">
-        <v>0.5174132972506341</v>
+        <v>1.236244897959184</v>
       </c>
       <c r="W21">
-        <v>0.05317160938943653</v>
+        <v>0.09045726972996303</v>
       </c>
       <c r="X21">
-        <v>0.2790636029502559</v>
+        <v>0.2244042543255101</v>
       </c>
       <c r="Y21">
-        <v>-0.2258919935608193</v>
+        <v>-0.1339469845955471</v>
       </c>
       <c r="Z21">
-        <v>0.05403193539405477</v>
+        <v>0.06967850002852027</v>
       </c>
       <c r="AA21">
         <v>0</v>
       </c>
       <c r="AB21">
-        <v>0.07530035650825825</v>
+        <v>0.06330371435665214</v>
       </c>
       <c r="AC21">
-        <v>-0.07530035650825825</v>
+        <v>-0.06330371435665214</v>
       </c>
       <c r="AD21">
-        <v>181456.8</v>
+        <v>90318.39999999999</v>
       </c>
       <c r="AE21">
         <v>0</v>
       </c>
       <c r="AF21">
-        <v>181456.8</v>
+        <v>90318.39999999999</v>
       </c>
       <c r="AG21">
-        <v>170788.1</v>
+        <v>78960.39999999999</v>
       </c>
       <c r="AH21">
-        <v>0.8979626982112185</v>
+        <v>0.9076687914987955</v>
       </c>
       <c r="AI21">
-        <v>0.6786790920066605</v>
+        <v>0.7791852400790586</v>
       </c>
       <c r="AJ21">
-        <v>0.8922753247784568</v>
+        <v>0.895771765407911</v>
       </c>
       <c r="AK21">
-        <v>0.6653246274136742</v>
+        <v>0.7551979371800156</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3061,10 +3082,10 @@
         </is>
       </c>
       <c r="D22">
-        <v>0.0501</v>
+        <v>0.05980000000000001</v>
       </c>
       <c r="E22">
-        <v>0.0483</v>
+        <v>0.0521</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3079,28 +3100,28 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>3432</v>
+        <v>3551.5</v>
       </c>
       <c r="L22">
-        <v>0.384098845017459</v>
+        <v>0.399246810184925</v>
       </c>
       <c r="M22">
-        <v>763.9152</v>
+        <v>174.5</v>
       </c>
       <c r="N22">
-        <v>0.06378930492000401</v>
+        <v>0.01383427411682628</v>
       </c>
       <c r="O22">
-        <v>0.222586013986014</v>
+        <v>0.0491341686611291</v>
       </c>
       <c r="P22">
-        <v>763.9152</v>
+        <v>174.5</v>
       </c>
       <c r="Q22">
-        <v>0.06378930492000401</v>
+        <v>0.01383427411682628</v>
       </c>
       <c r="R22">
-        <v>0.222586013986014</v>
+        <v>0.0491341686611291</v>
       </c>
       <c r="S22">
         <v>0</v>
@@ -3109,55 +3130,55 @@
         <v>0</v>
       </c>
       <c r="U22">
-        <v>9091.700000000001</v>
+        <v>24168.9</v>
       </c>
       <c r="V22">
-        <v>0.7591853435318481</v>
+        <v>1.916098496860531</v>
       </c>
       <c r="W22">
-        <v>0.08163886695148291</v>
+        <v>0.08814886149844377</v>
       </c>
       <c r="X22">
-        <v>0.3127597575901053</v>
+        <v>0.2557287820104563</v>
       </c>
       <c r="Y22">
-        <v>-0.2311208906386223</v>
+        <v>-0.1675799205120125</v>
       </c>
       <c r="Z22">
-        <v>0.05676314385180291</v>
+        <v>0.05687099863568421</v>
       </c>
       <c r="AA22">
         <v>0</v>
       </c>
       <c r="AB22">
-        <v>0.07537069910378753</v>
+        <v>0.06333893519560696</v>
       </c>
       <c r="AC22">
-        <v>-0.07537069910378753</v>
+        <v>-0.06333893519560696</v>
       </c>
       <c r="AD22">
-        <v>122409.2</v>
+        <v>147764.7</v>
       </c>
       <c r="AE22">
         <v>0</v>
       </c>
       <c r="AF22">
-        <v>122409.2</v>
+        <v>147764.7</v>
       </c>
       <c r="AG22">
-        <v>113317.5</v>
+        <v>123595.8</v>
       </c>
       <c r="AH22">
-        <v>0.9108857549365703</v>
+        <v>0.9213509558338004</v>
       </c>
       <c r="AI22">
-        <v>0.7378639840334376</v>
+        <v>0.7750501175441302</v>
       </c>
       <c r="AJ22">
-        <v>0.9044193175841287</v>
+        <v>0.9073955248316196</v>
       </c>
       <c r="AK22">
-        <v>0.7226650935875769</v>
+        <v>0.7423933629219578</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -3183,10 +3204,10 @@
         </is>
       </c>
       <c r="D23">
-        <v>0.0154</v>
+        <v>-0.00641</v>
       </c>
       <c r="E23">
-        <v>0.00927</v>
+        <v>-0.0444</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3201,28 +3222,28 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>1147.6</v>
+        <v>800.2</v>
       </c>
       <c r="L23">
-        <v>0.4062876159456206</v>
+        <v>0.3298705581663781</v>
       </c>
       <c r="M23">
-        <v>367.2</v>
+        <v>344.1</v>
       </c>
       <c r="N23">
-        <v>0.08713190802743041</v>
+        <v>0.1339275288989219</v>
       </c>
       <c r="O23">
-        <v>0.319972115719763</v>
+        <v>0.4300174956260935</v>
       </c>
       <c r="P23">
-        <v>367.2</v>
+        <v>344.1</v>
       </c>
       <c r="Q23">
-        <v>0.08713190802743041</v>
+        <v>0.1339275288989219</v>
       </c>
       <c r="R23">
-        <v>0.319972115719763</v>
+        <v>0.4300174956260935</v>
       </c>
       <c r="S23">
         <v>0</v>
@@ -3231,55 +3252,55 @@
         <v>0</v>
       </c>
       <c r="U23">
-        <v>8942.4</v>
+        <v>8135.8</v>
       </c>
       <c r="V23">
-        <v>2.121918230785658</v>
+        <v>3.166543416494765</v>
       </c>
       <c r="W23">
-        <v>0.06912253650074687</v>
+        <v>0.04899133682309365</v>
       </c>
       <c r="X23">
-        <v>0.4684518013964469</v>
+        <v>0.4895453001744814</v>
       </c>
       <c r="Y23">
-        <v>-0.3993292648957001</v>
+        <v>-0.4405539633513878</v>
       </c>
       <c r="Z23">
-        <v>0.04128065614116622</v>
+        <v>0.03104360411918348</v>
       </c>
       <c r="AA23">
         <v>0</v>
       </c>
       <c r="AB23">
-        <v>0.07554976504198216</v>
+        <v>0.06344526498581979</v>
       </c>
       <c r="AC23">
-        <v>-0.07554976504198216</v>
+        <v>-0.06344526498581979</v>
       </c>
       <c r="AD23">
-        <v>70750.60000000001</v>
+        <v>66232.8</v>
       </c>
       <c r="AE23">
         <v>0</v>
       </c>
       <c r="AF23">
-        <v>70750.60000000001</v>
+        <v>66232.8</v>
       </c>
       <c r="AG23">
-        <v>61808.2</v>
+        <v>58097</v>
       </c>
       <c r="AH23">
-        <v>0.9437830237884663</v>
+        <v>0.9626566630960391</v>
       </c>
       <c r="AI23">
-        <v>0.812439928758522</v>
+        <v>0.8078885031701849</v>
       </c>
       <c r="AJ23">
-        <v>0.9361687303570753</v>
+        <v>0.9576486451291738</v>
       </c>
       <c r="AK23">
-        <v>0.7909758809956783</v>
+        <v>0.7867233245042439</v>
       </c>
       <c r="AL23">
         <v>0</v>

--- a/research/traditional_assets/database/data/china/china_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/china/china_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ23"/>
+  <dimension ref="A1:AQ18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,112 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.06059999999999999</v>
+        <v>0.03605</v>
       </c>
       <c r="E2">
-        <v>0.0521</v>
+        <v>0.04535</v>
       </c>
       <c r="F2">
-        <v>0.0317</v>
+        <v>0.011995</v>
       </c>
       <c r="G2">
-        <v>0.006567627546606233</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>0.006567627546606233</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>0.006378296287460962</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>0.005650070941139129</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>267493.1</v>
+        <v>259760.2</v>
       </c>
       <c r="L2">
-        <v>0.4493771555960238</v>
+        <v>0.4715312500850901</v>
       </c>
       <c r="M2">
-        <v>75833.0552</v>
+        <v>141104.5081</v>
       </c>
       <c r="N2">
-        <v>0.06554727801324463</v>
+        <v>0.09587547383291307</v>
       </c>
       <c r="O2">
-        <v>0.2834953694132671</v>
+        <v>0.5432106539031</v>
       </c>
       <c r="P2">
-        <v>75827.1652</v>
+        <v>94983.50810000001</v>
       </c>
       <c r="Q2">
-        <v>0.06554218691587978</v>
+        <v>0.06453790150309052</v>
       </c>
       <c r="R2">
-        <v>0.283473350153705</v>
+        <v>0.3656584345869768</v>
       </c>
       <c r="S2">
-        <v>5.889999999999873</v>
+        <v>46121</v>
       </c>
       <c r="T2">
-        <v>7.767061454224348e-05</v>
+        <v>0.3268570269017507</v>
       </c>
       <c r="U2">
-        <v>1366458.3</v>
+        <v>1409670.8</v>
       </c>
       <c r="V2">
-        <v>1.181115831973042</v>
+        <v>0.957820963470845</v>
       </c>
       <c r="W2">
-        <v>0.1010994208906393</v>
+        <v>0.09870087969447311</v>
       </c>
       <c r="X2">
-        <v>0.162966551850205</v>
+        <v>0.1444013036825047</v>
       </c>
       <c r="Y2">
-        <v>-0.06186713095956571</v>
+        <v>-0.04570042398803162</v>
       </c>
       <c r="Z2">
-        <v>0.1075003814731816</v>
+        <v>0.1042209615719441</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.0606857579155532</v>
+        <v>0.06389506258956437</v>
       </c>
       <c r="AC2">
-        <v>-0.06058329636954127</v>
+        <v>-0.06389506258956437</v>
       </c>
       <c r="AD2">
-        <v>4465152.399999999</v>
+        <v>4845258.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>4465152.399999999</v>
+        <v>4845258.5</v>
       </c>
       <c r="AG2">
-        <v>3098694.1</v>
+        <v>3435587.7</v>
       </c>
       <c r="AH2">
-        <v>0.7942180197951506</v>
+        <v>0.7670181643956594</v>
       </c>
       <c r="AI2">
-        <v>0.611496525654218</v>
+        <v>0.6231343619496005</v>
       </c>
       <c r="AJ2">
-        <v>0.7281423867324859</v>
+        <v>0.7000922944863316</v>
       </c>
       <c r="AK2">
-        <v>0.5220568205184709</v>
+        <v>0.5396815829560293</v>
       </c>
       <c r="AL2">
-        <v>2547.3</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>1923.9</v>
-      </c>
-      <c r="AN2">
-        <v>1150.604890870204</v>
-      </c>
-      <c r="AO2">
-        <v>1.490480116201468</v>
-      </c>
-      <c r="AP2">
-        <v>798.4884428067101</v>
-      </c>
-      <c r="AQ2">
-        <v>1.973439367950517</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CNPC Capital Company Limited (SZSE:000617)</t>
+          <t>Bank of China Limited (SEHK:3988)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,121 +713,112 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0222</v>
+        <v>0.0391</v>
       </c>
       <c r="E3">
-        <v>-0.0728</v>
+        <v>0.0455</v>
+      </c>
+      <c r="F3">
+        <v>0.00555</v>
       </c>
       <c r="G3">
-        <v>0.7638381430609015</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>0.7638381430609015</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>0.7418182528672749</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>0.6516438003876238</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>714.6</v>
+        <v>33189.7</v>
       </c>
       <c r="L3">
-        <v>0.139622125398097</v>
+        <v>0.437788954533643</v>
       </c>
       <c r="M3">
-        <v>441.4</v>
+        <v>15623.8</v>
       </c>
       <c r="N3">
-        <v>0.04584783173201765</v>
+        <v>0.0774050928288396</v>
       </c>
       <c r="O3">
-        <v>0.6176882171844388</v>
+        <v>0.4707424291271087</v>
       </c>
       <c r="P3">
-        <v>441.4</v>
+        <v>9921.299999999999</v>
       </c>
       <c r="Q3">
-        <v>0.04584783173201765</v>
+        <v>0.04915316040161589</v>
       </c>
       <c r="R3">
-        <v>0.6176882171844388</v>
+        <v>0.2989270767738184</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>5702.5</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.364988031080787</v>
       </c>
       <c r="U3">
-        <v>5353.5</v>
+        <v>76029.39999999999</v>
       </c>
       <c r="V3">
-        <v>0.5560633601661906</v>
+        <v>0.3766729454243511</v>
       </c>
       <c r="W3">
-        <v>0.05311707908096899</v>
+        <v>0.09900900605275953</v>
       </c>
       <c r="X3">
-        <v>0.09074660601228665</v>
+        <v>0.1387775609890181</v>
       </c>
       <c r="Y3">
-        <v>-0.03762952693131767</v>
+        <v>-0.03976855493625855</v>
       </c>
       <c r="Z3">
-        <v>0.1743681747163592</v>
+        <v>0.07509027223109692</v>
       </c>
       <c r="AA3">
-        <v>0.1136259400388215</v>
+        <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.0606857579155532</v>
+        <v>0.06242487499525222</v>
       </c>
       <c r="AC3">
-        <v>0.05294018212326827</v>
+        <v>-0.06242487499525222</v>
       </c>
       <c r="AD3">
-        <v>17244.8</v>
+        <v>936196.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>17244.8</v>
+        <v>936196.9</v>
       </c>
       <c r="AG3">
-        <v>11891.3</v>
+        <v>860167.5</v>
       </c>
       <c r="AH3">
-        <v>0.6417314483687664</v>
+        <v>0.8226386296106074</v>
       </c>
       <c r="AI3">
-        <v>0.4057332693375495</v>
+        <v>0.6955828337731326</v>
       </c>
       <c r="AJ3">
-        <v>0.55260051675744</v>
+        <v>0.8099413368265765</v>
       </c>
       <c r="AK3">
-        <v>0.3200948604684341</v>
+        <v>0.6773570861929692</v>
       </c>
       <c r="AL3">
-        <v>2547.3</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>1923.9</v>
-      </c>
-      <c r="AN3">
-        <v>4.443734377818435</v>
-      </c>
-      <c r="AO3">
-        <v>1.490480116201468</v>
-      </c>
-      <c r="AP3">
-        <v>3.064215218903806</v>
-      </c>
-      <c r="AQ3">
-        <v>1.973439367950517</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -850,7 +829,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bank of Beijing Co., Ltd. (SHSE:601169)</t>
+          <t>Bank of Communications Co., Ltd. (SEHK:3328)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -859,10 +838,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0501</v>
+        <v>0.0216</v>
       </c>
       <c r="E4">
-        <v>0.0525</v>
+        <v>0.0382</v>
+      </c>
+      <c r="F4">
+        <v>0.0146</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -877,28 +859,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>3512.9</v>
+        <v>13151.6</v>
       </c>
       <c r="L4">
-        <v>0.5307938714454081</v>
+        <v>0.4579439252336449</v>
       </c>
       <c r="M4">
-        <v>888.0060000000001</v>
+        <v>5866.753299999999</v>
       </c>
       <c r="N4">
-        <v>0.06574364593436045</v>
+        <v>0.0831147348915227</v>
       </c>
       <c r="O4">
-        <v>0.2527843092601554</v>
+        <v>0.4460866586575017</v>
       </c>
       <c r="P4">
-        <v>888.0060000000001</v>
+        <v>5866.753299999999</v>
       </c>
       <c r="Q4">
-        <v>0.06574364593436045</v>
+        <v>0.0831147348915227</v>
       </c>
       <c r="R4">
-        <v>0.2527843092601554</v>
+        <v>0.4460866586575017</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -907,55 +889,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>23066.4</v>
+        <v>22847.1</v>
       </c>
       <c r="V4">
-        <v>1.707724085851145</v>
+        <v>0.3236765826748004</v>
       </c>
       <c r="W4">
-        <v>0.08633707069863007</v>
+        <v>0.09441002706330805</v>
       </c>
       <c r="X4">
-        <v>0.1920588486861554</v>
+        <v>0.1634185212218977</v>
       </c>
       <c r="Y4">
-        <v>-0.1057217779875254</v>
+        <v>-0.06900849415858969</v>
       </c>
       <c r="Z4">
-        <v>0.06269104893978791</v>
+        <v>0.05793543922929735</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.05670960177483945</v>
+        <v>0.06287560304862097</v>
       </c>
       <c r="AC4">
-        <v>-0.05670960177483945</v>
+        <v>-0.06287560304862097</v>
       </c>
       <c r="AD4">
-        <v>106503.9</v>
+        <v>439101.7</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>106503.9</v>
+        <v>439101.7</v>
       </c>
       <c r="AG4">
-        <v>83437.5</v>
+        <v>416254.6</v>
       </c>
       <c r="AH4">
-        <v>0.8874511503112215</v>
+        <v>0.8615109363985294</v>
       </c>
       <c r="AI4">
-        <v>0.7054425048981749</v>
+        <v>0.7299054451134341</v>
       </c>
       <c r="AJ4">
-        <v>0.8606719714146017</v>
+        <v>0.8550117410044515</v>
       </c>
       <c r="AK4">
-        <v>0.6523233068716471</v>
+        <v>0.7192428378892076</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -972,7 +954,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bank of Shanghai Co., Ltd. (SHSE:601229)</t>
+          <t>China Construction Bank Corporation (SEHK:939)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -981,10 +963,13 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0622</v>
+        <v>0.0312</v>
       </c>
       <c r="E5">
-        <v>0.0459</v>
+        <v>0.046</v>
+      </c>
+      <c r="F5">
+        <v>0.00481</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -999,28 +984,28 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>3077.8</v>
+        <v>47469.5</v>
       </c>
       <c r="L5">
-        <v>0.583812287789981</v>
+        <v>0.5379845822217286</v>
       </c>
       <c r="M5">
-        <v>781.3685</v>
+        <v>21250.935</v>
       </c>
       <c r="N5">
-        <v>0.06532635231167963</v>
+        <v>0.1001830794687938</v>
       </c>
       <c r="O5">
-        <v>0.2538724088634739</v>
+        <v>0.447675560096483</v>
       </c>
       <c r="P5">
-        <v>781.3685</v>
+        <v>21250.935</v>
       </c>
       <c r="Q5">
-        <v>0.06532635231167963</v>
+        <v>0.1001830794687938</v>
       </c>
       <c r="R5">
-        <v>0.2538724088634739</v>
+        <v>0.447675560096483</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1029,55 +1014,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>6277.5</v>
+        <v>197560.6</v>
       </c>
       <c r="V5">
-        <v>0.5248306997742663</v>
+        <v>0.9313580456437599</v>
       </c>
       <c r="W5">
-        <v>0.1010994208906393</v>
+        <v>0.1148303772726833</v>
       </c>
       <c r="X5">
-        <v>0.1788816172747101</v>
+        <v>0.1084589001396917</v>
       </c>
       <c r="Y5">
-        <v>-0.07778219638407079</v>
+        <v>0.006371477132991618</v>
       </c>
       <c r="Z5">
-        <v>0.05225368097095365</v>
+        <v>0.1183040685316712</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.05676248677298197</v>
+        <v>0.06289523690518523</v>
       </c>
       <c r="AC5">
-        <v>-0.05676248677298197</v>
+        <v>-0.06289523690518523</v>
       </c>
       <c r="AD5">
-        <v>84832.60000000001</v>
+        <v>570811.7</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>84832.60000000001</v>
+        <v>570811.7</v>
       </c>
       <c r="AG5">
-        <v>78555.10000000001</v>
+        <v>373251.1</v>
       </c>
       <c r="AH5">
-        <v>0.8764277803491139</v>
+        <v>0.7290686670770041</v>
       </c>
       <c r="AI5">
-        <v>0.7268236219433518</v>
+        <v>0.5449576554240744</v>
       </c>
       <c r="AJ5">
-        <v>0.8678577623207363</v>
+        <v>0.6376304917846273</v>
       </c>
       <c r="AK5">
-        <v>0.7112959686488699</v>
+        <v>0.4391800647078293</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1094,7 +1079,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Industrial Bank Co., Ltd. (SHSE:601166)</t>
+          <t>China CITIC Bank Corporation Limited (SEHK:998)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1103,13 +1088,13 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0824</v>
+        <v>0.0567</v>
       </c>
       <c r="E6">
-        <v>0.0687</v>
+        <v>0.0682</v>
       </c>
       <c r="F6">
-        <v>0.0317</v>
+        <v>-0.00461</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1124,85 +1109,85 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>11585.4</v>
+        <v>9610</v>
       </c>
       <c r="L6">
-        <v>0.5215031014521457</v>
+        <v>0.4466090706720514</v>
       </c>
       <c r="M6">
-        <v>3386.2109</v>
+        <v>3713.5</v>
       </c>
       <c r="N6">
-        <v>0.07130261082696192</v>
+        <v>0.07842843233950525</v>
       </c>
       <c r="O6">
-        <v>0.2922826056933727</v>
+        <v>0.386420395421436</v>
       </c>
       <c r="P6">
-        <v>3386.2109</v>
+        <v>3212.3</v>
       </c>
       <c r="Q6">
-        <v>0.07130261082696192</v>
+        <v>0.06784318115098767</v>
       </c>
       <c r="R6">
-        <v>0.2922826056933727</v>
+        <v>0.3342663891779397</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>501.1999999999998</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>0.1349670122525918</v>
       </c>
       <c r="U6">
-        <v>51956.5</v>
+        <v>33779.6</v>
       </c>
       <c r="V6">
-        <v>1.094035253217998</v>
+        <v>0.7134188967431133</v>
       </c>
       <c r="W6">
-        <v>0.1222942603379153</v>
+        <v>0.1050179109631705</v>
       </c>
       <c r="X6">
-        <v>0.163702874365051</v>
+        <v>0.1500250463759914</v>
       </c>
       <c r="Y6">
-        <v>-0.04140861402713568</v>
+        <v>-0.04500713541282085</v>
       </c>
       <c r="Z6">
-        <v>0.07377460479076318</v>
+        <v>0.07336225633507497</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.05683787647469577</v>
+        <v>0.06295570511968698</v>
       </c>
       <c r="AC6">
-        <v>-0.05683787647469577</v>
+        <v>-0.06295570511968698</v>
       </c>
       <c r="AD6">
-        <v>293466.3</v>
+        <v>253817.7</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>293466.3</v>
+        <v>253817.7</v>
       </c>
       <c r="AG6">
-        <v>241509.8</v>
+        <v>220038.1</v>
       </c>
       <c r="AH6">
-        <v>0.8607135210598403</v>
+        <v>0.8427817028847155</v>
       </c>
       <c r="AI6">
-        <v>0.7293360465595989</v>
+        <v>0.6820540918779417</v>
       </c>
       <c r="AJ6">
-        <v>0.8356726026425559</v>
+        <v>0.8229199624514281</v>
       </c>
       <c r="AK6">
-        <v>0.6892046957620055</v>
+        <v>0.6503122731689787</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1219,7 +1204,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Zhejiang Shaoxing RuiFeng Rural Commercial Bank Co.,Ltd (SHSE:601528)</t>
+          <t>Agricultural Bank of China Limited (SEHK:1288)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1227,6 +1212,15 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
+      <c r="D7">
+        <v>0.033</v>
+      </c>
+      <c r="E7">
+        <v>0.0546</v>
+      </c>
+      <c r="F7">
+        <v>0.0216</v>
+      </c>
       <c r="G7">
         <v>0</v>
       </c>
@@ -1240,85 +1234,85 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>234.3</v>
+        <v>39400.1</v>
       </c>
       <c r="L7">
-        <v>0.5936154041043831</v>
+        <v>0.4888926114120151</v>
       </c>
       <c r="M7">
-        <v>48</v>
+        <v>30483.8</v>
       </c>
       <c r="N7">
-        <v>0.03504417025626049</v>
+        <v>0.1214058220535179</v>
       </c>
       <c r="O7">
-        <v>0.204865556978233</v>
+        <v>0.7736985439123252</v>
       </c>
       <c r="P7">
-        <v>48</v>
+        <v>13376.4</v>
       </c>
       <c r="Q7">
-        <v>0.03504417025626049</v>
+        <v>0.05327330707184393</v>
       </c>
       <c r="R7">
-        <v>0.204865556978233</v>
+        <v>0.3395016763916843</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>17107.4</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>0.561196438764196</v>
       </c>
       <c r="U7">
-        <v>1213.6</v>
+        <v>396326.5</v>
       </c>
       <c r="V7">
-        <v>0.8860334379791194</v>
+        <v>1.578423442421665</v>
       </c>
       <c r="W7">
-        <v>0.114605752298963</v>
+        <v>0.105090137235635</v>
       </c>
       <c r="X7">
-        <v>0.1081086470044246</v>
+        <v>0.1044092230825776</v>
       </c>
       <c r="Y7">
-        <v>0.006497105294538438</v>
+        <v>0.0006809141530574048</v>
       </c>
       <c r="Z7">
-        <v>0.1060365902802031</v>
+        <v>0.1462374086725014</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.05742046481710792</v>
+        <v>0.06299848405221703</v>
       </c>
       <c r="AC7">
-        <v>-0.05742046481710792</v>
+        <v>-0.06299848405221703</v>
       </c>
       <c r="AD7">
-        <v>3883.8</v>
+        <v>610369.7</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>3883.8</v>
+        <v>610369.7</v>
       </c>
       <c r="AG7">
-        <v>2670.2</v>
+        <v>214043.2</v>
       </c>
       <c r="AH7">
-        <v>0.7392785761873037</v>
+        <v>0.7085295216329305</v>
       </c>
       <c r="AI7">
-        <v>0.6346078431372549</v>
+        <v>0.5871638118288982</v>
       </c>
       <c r="AJ7">
-        <v>0.6609569543800589</v>
+        <v>0.4601760398578214</v>
       </c>
       <c r="AK7">
-        <v>0.5442279471710419</v>
+        <v>0.3327809351900005</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1335,7 +1329,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bank of China Limited (SEHK:3988)</t>
+          <t>Industrial and Commercial Bank of China Limited (SEHK:1398)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1344,13 +1338,13 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.06059999999999999</v>
+        <v>0.00369</v>
       </c>
       <c r="E8">
-        <v>0.05019999999999999</v>
+        <v>0.033</v>
       </c>
       <c r="F8">
-        <v>0.0254</v>
+        <v>0.009389999999999999</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1365,85 +1359,85 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>31537.6</v>
+        <v>51941.7</v>
       </c>
       <c r="L8">
-        <v>0.4274094091435169</v>
+        <v>0.5595357104384359</v>
       </c>
       <c r="M8">
-        <v>9360.1</v>
+        <v>28273.5</v>
       </c>
       <c r="N8">
-        <v>0.0621948845254003</v>
+        <v>0.09009271677648842</v>
       </c>
       <c r="O8">
-        <v>0.2967917660189742</v>
+        <v>0.5443314331259855</v>
       </c>
       <c r="P8">
-        <v>9360.1</v>
+        <v>16868.6</v>
       </c>
       <c r="Q8">
-        <v>0.0621948845254003</v>
+        <v>0.05375132198758104</v>
       </c>
       <c r="R8">
-        <v>0.2967917660189742</v>
+        <v>0.3247602600607989</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>11404.9</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>0.4033777211876846</v>
       </c>
       <c r="U8">
-        <v>101408.6</v>
+        <v>432605.6</v>
       </c>
       <c r="V8">
-        <v>0.6738278615487557</v>
+        <v>1.378485641916382</v>
       </c>
       <c r="W8">
-        <v>0.09418240524451363</v>
+        <v>0.107626142143497</v>
       </c>
       <c r="X8">
-        <v>0.1448603906615534</v>
+        <v>0.0930236297858274</v>
       </c>
       <c r="Y8">
-        <v>-0.0506779854170398</v>
+        <v>0.01460251235766956</v>
       </c>
       <c r="Z8">
-        <v>0.07596753652552696</v>
+        <v>0.258150311168039</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.05976552953971447</v>
+        <v>0.06339535511300028</v>
       </c>
       <c r="AC8">
-        <v>-0.05976552953971447</v>
+        <v>-0.06339535511300028</v>
       </c>
       <c r="AD8">
-        <v>759418.1</v>
+        <v>533390.1</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>759418.1</v>
+        <v>533390.1</v>
       </c>
       <c r="AG8">
-        <v>658009.5</v>
+        <v>100784.5</v>
       </c>
       <c r="AH8">
-        <v>0.8346038924100992</v>
+        <v>0.6295792293070676</v>
       </c>
       <c r="AI8">
-        <v>0.6731847492628297</v>
+        <v>0.4882033189472077</v>
       </c>
       <c r="AJ8">
-        <v>0.8138587255651103</v>
+        <v>0.2430819524412269</v>
       </c>
       <c r="AK8">
-        <v>0.6409044024042334</v>
+        <v>0.1527149638375051</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1460,7 +1454,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>China Construction Bank Corporation (SEHK:939)</t>
+          <t>China Everbright Bank Company Limited (SHSE:601818)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1469,13 +1463,13 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.0701</v>
+        <v>0.026</v>
       </c>
       <c r="E9">
-        <v>0.0538</v>
+        <v>0.0217</v>
       </c>
       <c r="F9">
-        <v>0.0163</v>
+        <v>-0.174</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1490,28 +1484,28 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>45441.2</v>
+        <v>5918.6</v>
       </c>
       <c r="L9">
-        <v>0.4881070026037415</v>
+        <v>0.4394825947487228</v>
       </c>
       <c r="M9">
-        <v>13250.583</v>
+        <v>2304.3384</v>
       </c>
       <c r="N9">
-        <v>0.08722286073129694</v>
+        <v>0.0780221843003413</v>
       </c>
       <c r="O9">
-        <v>0.291598439301779</v>
+        <v>0.3893384246274457</v>
       </c>
       <c r="P9">
-        <v>13250.583</v>
+        <v>2304.3384</v>
       </c>
       <c r="Q9">
-        <v>0.08722286073129694</v>
+        <v>0.0780221843003413</v>
       </c>
       <c r="R9">
-        <v>0.291598439301779</v>
+        <v>0.3893384246274457</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1520,55 +1514,55 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>115275.1</v>
+        <v>17130.9</v>
       </c>
       <c r="V9">
-        <v>0.7588061591770211</v>
+        <v>0.5800320981634975</v>
       </c>
       <c r="W9">
-        <v>0.1183648782337842</v>
+        <v>0.09065302465212098</v>
       </c>
       <c r="X9">
-        <v>0.1091013031622659</v>
+        <v>0.1840873109489738</v>
       </c>
       <c r="Y9">
-        <v>0.009263575071518329</v>
+        <v>-0.09343428629685281</v>
       </c>
       <c r="Z9">
-        <v>0.1423897771943998</v>
+        <v>0.05239690797859178</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.05989702346072887</v>
+        <v>0.06351211384848231</v>
       </c>
       <c r="AC9">
-        <v>-0.05989702346072887</v>
+        <v>-0.06351211384848231</v>
       </c>
       <c r="AD9">
-        <v>439831.2</v>
+        <v>222933.1</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>439831.2</v>
+        <v>222933.1</v>
       </c>
       <c r="AG9">
-        <v>324556.1</v>
+        <v>205802.2</v>
       </c>
       <c r="AH9">
-        <v>0.7432750044106643</v>
+        <v>0.8830170219929298</v>
       </c>
       <c r="AI9">
-        <v>0.5088917845145426</v>
+        <v>0.7285421614260704</v>
       </c>
       <c r="AJ9">
-        <v>0.6811643903897916</v>
+        <v>0.8745014587616207</v>
       </c>
       <c r="AK9">
-        <v>0.4333093329911961</v>
+        <v>0.7124437459323982</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1585,7 +1579,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Agricultural Bank of China Limited (SEHK:1288)</t>
+          <t>Ping An Bank Co., Ltd. (SZSE:000001)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1594,13 +1588,13 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.0505</v>
+        <v>0.0524</v>
       </c>
       <c r="E10">
-        <v>0.0563</v>
+        <v>0.107</v>
       </c>
       <c r="F10">
-        <v>0.0325</v>
+        <v>0.046</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1615,28 +1609,28 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>36860.7</v>
+        <v>6636.1</v>
       </c>
       <c r="L10">
-        <v>0.4551895063893265</v>
+        <v>0.4611413005712062</v>
       </c>
       <c r="M10">
-        <v>12609</v>
+        <v>1070.1</v>
       </c>
       <c r="N10">
-        <v>0.07175477383503061</v>
+        <v>0.03440128076537304</v>
       </c>
       <c r="O10">
-        <v>0.3420716372722168</v>
+        <v>0.1612543512002531</v>
       </c>
       <c r="P10">
-        <v>12609</v>
+        <v>1070.1</v>
       </c>
       <c r="Q10">
-        <v>0.07175477383503061</v>
+        <v>0.03440128076537304</v>
       </c>
       <c r="R10">
-        <v>0.3420716372722168</v>
+        <v>0.1612543512002531</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1645,55 +1639,55 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>341911.3</v>
+        <v>39585.6</v>
       </c>
       <c r="V10">
-        <v>1.945734634240725</v>
+        <v>1.272586991744464</v>
       </c>
       <c r="W10">
-        <v>0.1030195386846952</v>
+        <v>0.1085898585538588</v>
       </c>
       <c r="X10">
-        <v>0.10896459390847</v>
+        <v>0.1363975747985429</v>
       </c>
       <c r="Y10">
-        <v>-0.005945055223774837</v>
+        <v>-0.02780771624468405</v>
       </c>
       <c r="Z10">
-        <v>0.1496897745285155</v>
+        <v>0.0906754948192993</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.05989780540861271</v>
+        <v>0.06373759122272799</v>
       </c>
       <c r="AC10">
-        <v>-0.05989780540861271</v>
+        <v>-0.06373759122272799</v>
       </c>
       <c r="AD10">
-        <v>507313</v>
+        <v>139523.1</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>507313</v>
+        <v>139523.1</v>
       </c>
       <c r="AG10">
-        <v>165401.7</v>
+        <v>99937.5</v>
       </c>
       <c r="AH10">
-        <v>0.7427319037855225</v>
+        <v>0.8176962365827715</v>
       </c>
       <c r="AI10">
-        <v>0.5674678873755558</v>
+        <v>0.6661553159703274</v>
       </c>
       <c r="AJ10">
-        <v>0.4848709506069913</v>
+        <v>0.7626261123180859</v>
       </c>
       <c r="AK10">
-        <v>0.2995957672298852</v>
+        <v>0.5883532115033759</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1719,13 +1713,13 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.08</v>
+        <v>0.08199999999999999</v>
       </c>
       <c r="E11">
-        <v>0.1</v>
+        <v>0.0761</v>
       </c>
       <c r="F11">
-        <v>0.0552</v>
+        <v>0.0148</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1740,28 +1734,28 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>11927.5</v>
+        <v>12322</v>
       </c>
       <c r="L11">
-        <v>0.2775521886540435</v>
+        <v>0.2708173532340058</v>
       </c>
       <c r="M11">
-        <v>5142.3</v>
+        <v>5751.343800000001</v>
       </c>
       <c r="N11">
-        <v>0.08845948079963256</v>
+        <v>0.07833323753941285</v>
       </c>
       <c r="O11">
-        <v>0.4311297421924125</v>
+        <v>0.4667540821295245</v>
       </c>
       <c r="P11">
-        <v>5142.3</v>
+        <v>5751.343800000001</v>
       </c>
       <c r="Q11">
-        <v>0.08845948079963256</v>
+        <v>0.07833323753941285</v>
       </c>
       <c r="R11">
-        <v>0.4311297421924125</v>
+        <v>0.4667540821295245</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1770,55 +1764,55 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>35377.4</v>
+        <v>53255.8</v>
       </c>
       <c r="V11">
-        <v>0.6085732913367405</v>
+        <v>0.725343393964983</v>
       </c>
       <c r="W11">
-        <v>0.1039310373672488</v>
+        <v>0.09839275333618669</v>
       </c>
       <c r="X11">
-        <v>0.09108035266801605</v>
+        <v>0.08205852752123782</v>
       </c>
       <c r="Y11">
-        <v>0.0128506846992328</v>
+        <v>0.01633422581494887</v>
       </c>
       <c r="Z11">
-        <v>0.3296401441785863</v>
+        <v>0.2331527866029885</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.06003954091199037</v>
+        <v>0.06405253395640077</v>
       </c>
       <c r="AC11">
-        <v>-0.06003954091199037</v>
+        <v>-0.06405253395640077</v>
       </c>
       <c r="AD11">
-        <v>105292.6</v>
+        <v>73083.2</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>105292.6</v>
+        <v>73083.2</v>
       </c>
       <c r="AG11">
-        <v>69915.20000000001</v>
+        <v>19827.39999999999</v>
       </c>
       <c r="AH11">
-        <v>0.6442897414888729</v>
+        <v>0.4988454295322948</v>
       </c>
       <c r="AI11">
-        <v>0.4562893485134236</v>
+        <v>0.3316976110466626</v>
       </c>
       <c r="AJ11">
-        <v>0.5460124376302746</v>
+        <v>0.2126287816799983</v>
       </c>
       <c r="AK11">
-        <v>0.3578403222421833</v>
+        <v>0.1186736495585814</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1835,7 +1829,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Industrial and Commercial Bank of China Limited (SEHK:1398)</t>
+          <t>Shanghai Pudong Development Bank Co., Ltd. (SHSE:600000)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1844,13 +1838,13 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.0388</v>
+        <v>-0.035</v>
       </c>
       <c r="E12">
-        <v>0.04019999999999999</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="F12">
-        <v>0.0211</v>
+        <v>0.118</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1865,28 +1859,28 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>49693</v>
+        <v>6264</v>
       </c>
       <c r="L12">
-        <v>0.495198785047474</v>
+        <v>0.4410460056609353</v>
       </c>
       <c r="M12">
-        <v>14824.6</v>
+        <v>3945.3</v>
       </c>
       <c r="N12">
-        <v>0.06612530916925191</v>
+        <v>0.09534408259142187</v>
       </c>
       <c r="O12">
-        <v>0.2983237075644457</v>
+        <v>0.6298371647509579</v>
       </c>
       <c r="P12">
-        <v>14824.6</v>
+        <v>3945.3</v>
       </c>
       <c r="Q12">
-        <v>0.06612530916925191</v>
+        <v>0.09534408259142187</v>
       </c>
       <c r="R12">
-        <v>0.2983237075644457</v>
+        <v>0.6298371647509579</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -1895,55 +1889,55 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>453848.8</v>
+        <v>61446.3</v>
       </c>
       <c r="V12">
-        <v>2.024398109634929</v>
+        <v>1.484941855407012</v>
       </c>
       <c r="W12">
-        <v>0.1079405474421003</v>
+        <v>0.06386225979012317</v>
       </c>
       <c r="X12">
-        <v>0.08413289000977314</v>
+        <v>0.1929374315812532</v>
       </c>
       <c r="Y12">
-        <v>0.02380765743232717</v>
+        <v>-0.1290751717911301</v>
       </c>
       <c r="Z12">
-        <v>0.2955035285352715</v>
+        <v>0.04015147338826294</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.0601289608212585</v>
+        <v>0.06442176350752948</v>
       </c>
       <c r="AC12">
-        <v>-0.0601289608212585</v>
+        <v>-0.06442176350752948</v>
       </c>
       <c r="AD12">
-        <v>312384.3</v>
+        <v>335864</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>312384.3</v>
+        <v>335864</v>
       </c>
       <c r="AG12">
-        <v>-141464.5</v>
+        <v>274417.7</v>
       </c>
       <c r="AH12">
-        <v>0.5821832896052695</v>
+        <v>0.8903106639847569</v>
       </c>
       <c r="AI12">
-        <v>0.3827470193180561</v>
+        <v>0.7631940606730462</v>
       </c>
       <c r="AJ12">
-        <v>-1.710057419159867</v>
+        <v>0.868967847413515</v>
       </c>
       <c r="AK12">
-        <v>-0.3904460509650302</v>
+        <v>0.724763852885597</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -1960,7 +1954,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bank of Communications Co., Ltd. (SEHK:3328)</t>
+          <t>China Merchants Bank Co., Ltd. (SHSE:600036)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1969,13 +1963,13 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.0591</v>
+        <v>0.0725</v>
       </c>
       <c r="E13">
-        <v>0.0503</v>
+        <v>0.1</v>
       </c>
       <c r="F13">
-        <v>0.0386</v>
+        <v>0.0285</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1990,28 +1984,28 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>12803.9</v>
+        <v>20799.2</v>
       </c>
       <c r="L13">
-        <v>0.426961758546638</v>
+        <v>0.4966688476361952</v>
       </c>
       <c r="M13">
-        <v>246.7</v>
+        <v>7077.3</v>
       </c>
       <c r="N13">
-        <v>0.004602603353351953</v>
+        <v>0.0525364053616485</v>
       </c>
       <c r="O13">
-        <v>0.01926756691320613</v>
+        <v>0.3402678949190354</v>
       </c>
       <c r="P13">
-        <v>246.7</v>
+        <v>7077.3</v>
       </c>
       <c r="Q13">
-        <v>0.004602603353351953</v>
+        <v>0.0525364053616485</v>
       </c>
       <c r="R13">
-        <v>0.01926756691320613</v>
+        <v>0.3402678949190354</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -2020,55 +2014,55 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>26257.3</v>
+        <v>2184.8</v>
       </c>
       <c r="V13">
-        <v>0.4898740860558096</v>
+        <v>0.01621826663192596</v>
       </c>
       <c r="W13">
-        <v>0.09539849897440597</v>
+        <v>0.1541110709353124</v>
       </c>
       <c r="X13">
-        <v>0.1777469809858484</v>
+        <v>0.07996128533455701</v>
       </c>
       <c r="Y13">
-        <v>-0.0823484820114424</v>
+        <v>0.07414978560075536</v>
       </c>
       <c r="Z13">
-        <v>0.06441907499240099</v>
+        <v>0.1644920912807102</v>
       </c>
       <c r="AA13">
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.06058329636954127</v>
+        <v>0.06458182697923021</v>
       </c>
       <c r="AC13">
-        <v>-0.06058329636954127</v>
+        <v>-0.06458182697923021</v>
       </c>
       <c r="AD13">
-        <v>376497.1</v>
+        <v>115946.3</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>376497.1</v>
+        <v>115946.3</v>
       </c>
       <c r="AG13">
-        <v>350239.8</v>
+        <v>113761.5</v>
       </c>
       <c r="AH13">
-        <v>0.8753767752963749</v>
+        <v>0.462566614510733</v>
       </c>
       <c r="AI13">
-        <v>0.7191270551625316</v>
+        <v>0.4122300598010424</v>
       </c>
       <c r="AJ13">
-        <v>0.8672738874984864</v>
+        <v>0.4578410279071677</v>
       </c>
       <c r="AK13">
-        <v>0.7042967475121664</v>
+        <v>0.4076286758119142</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2085,7 +2079,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>China Merchants Bank Co., Ltd. (SHSE:600036)</t>
+          <t>Shanghai Rural Commercial Bank Co., Ltd. (SHSE:601825)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2094,13 +2088,10 @@
         </is>
       </c>
       <c r="D14">
-        <v>0.101</v>
+        <v>0.0688</v>
       </c>
       <c r="E14">
-        <v>0.13</v>
-      </c>
-      <c r="F14">
-        <v>0.06950000000000001</v>
+        <v>0.0745</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2115,28 +2106,28 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>19869.5</v>
+        <v>1743</v>
       </c>
       <c r="L14">
-        <v>0.4940179312882582</v>
+        <v>0.5161385845424933</v>
       </c>
       <c r="M14">
-        <v>6531.3</v>
+        <v>1218</v>
       </c>
       <c r="N14">
-        <v>0.06738891554331172</v>
+        <v>0.1083205862473765</v>
       </c>
       <c r="O14">
-        <v>0.3287098316515262</v>
+        <v>0.6987951807228916</v>
       </c>
       <c r="P14">
-        <v>6531.3</v>
+        <v>1218</v>
       </c>
       <c r="Q14">
-        <v>0.06738891554331172</v>
+        <v>0.1083205862473765</v>
       </c>
       <c r="R14">
-        <v>0.3287098316515262</v>
+        <v>0.6987951807228916</v>
       </c>
       <c r="S14">
         <v>0</v>
@@ -2145,55 +2136,55 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>1954.6</v>
+        <v>5334.7</v>
       </c>
       <c r="V14">
-        <v>0.0201672522041488</v>
+        <v>0.4744317171214115</v>
       </c>
       <c r="W14">
-        <v>0.1584523749713909</v>
+        <v>0.1156809780119862</v>
       </c>
       <c r="X14">
-        <v>0.08141074406157253</v>
+        <v>0.116549329645686</v>
       </c>
       <c r="Y14">
-        <v>0.07704163090981839</v>
+        <v>-0.0008683516336997349</v>
       </c>
       <c r="Z14">
-        <v>0.1659149927087695</v>
+        <v>0.07604605549087649</v>
       </c>
       <c r="AA14">
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.06127710386714286</v>
+        <v>0.06472873727423292</v>
       </c>
       <c r="AC14">
-        <v>-0.06127710386714286</v>
+        <v>-0.06472873727423292</v>
       </c>
       <c r="AD14">
-        <v>119178</v>
+        <v>36101.1</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>119178</v>
+        <v>36101.1</v>
       </c>
       <c r="AG14">
-        <v>117223.4</v>
+        <v>30766.4</v>
       </c>
       <c r="AH14">
-        <v>0.5515010585499601</v>
+        <v>0.7625033002080451</v>
       </c>
       <c r="AI14">
-        <v>0.4598757643180119</v>
+        <v>0.6719534076864661</v>
       </c>
       <c r="AJ14">
-        <v>0.5474073620932564</v>
+        <v>0.7323450160434936</v>
       </c>
       <c r="AK14">
-        <v>0.455771040210266</v>
+        <v>0.6357889603210521</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2210,7 +2201,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ping An Bank Co., Ltd. (SZSE:000001)</t>
+          <t>China Bohai Bank Co., Ltd. (SEHK:9668)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2219,13 +2210,10 @@
         </is>
       </c>
       <c r="D15">
-        <v>0.0955</v>
+        <v>-0.017</v>
       </c>
       <c r="E15">
-        <v>0.146</v>
-      </c>
-      <c r="F15">
-        <v>0.08869999999999999</v>
+        <v>-0.0605</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2240,28 +2228,28 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>6645.8</v>
+        <v>643.9</v>
       </c>
       <c r="L15">
-        <v>0.4457276995305164</v>
+        <v>0.3121485359705254</v>
       </c>
       <c r="M15">
-        <v>877.1</v>
+        <v>130.7</v>
       </c>
       <c r="N15">
-        <v>0.03413106078294031</v>
+        <v>0.06421973270440251</v>
       </c>
       <c r="O15">
-        <v>0.1319780914261639</v>
+        <v>0.2029818294766268</v>
       </c>
       <c r="P15">
-        <v>877.1</v>
+        <v>130.7</v>
       </c>
       <c r="Q15">
-        <v>0.03413106078294031</v>
+        <v>0.06421973270440251</v>
       </c>
       <c r="R15">
-        <v>0.1319780914261639</v>
+        <v>0.2029818294766268</v>
       </c>
       <c r="S15">
         <v>0</v>
@@ -2270,55 +2258,55 @@
         <v>0</v>
       </c>
       <c r="U15">
-        <v>41213</v>
+        <v>5608.1</v>
       </c>
       <c r="V15">
-        <v>1.603743481983034</v>
+        <v>2.755552279874214</v>
       </c>
       <c r="W15">
-        <v>0.1166171242467739</v>
+        <v>0.04088305883249311</v>
       </c>
       <c r="X15">
-        <v>0.1496697969152062</v>
+        <v>0.5877145275547386</v>
       </c>
       <c r="Y15">
-        <v>-0.0330526726684323</v>
+        <v>-0.5468314687222455</v>
       </c>
       <c r="Z15">
-        <v>0.0829663560575456</v>
+        <v>0.02793350558182616</v>
       </c>
       <c r="AA15">
         <v>0</v>
       </c>
       <c r="AB15">
-        <v>0.0614404419512195</v>
+        <v>0.06568446862480602</v>
       </c>
       <c r="AC15">
-        <v>-0.0614404419512195</v>
+        <v>-0.06568446862480602</v>
       </c>
       <c r="AD15">
-        <v>137108.4</v>
+        <v>68121.10000000001</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>137108.4</v>
+        <v>68121.10000000001</v>
       </c>
       <c r="AG15">
-        <v>95895.39999999999</v>
+        <v>62513.00000000001</v>
       </c>
       <c r="AH15">
-        <v>0.8421560823161743</v>
+        <v>0.9709904883809437</v>
       </c>
       <c r="AI15">
-        <v>0.6822854515398006</v>
+        <v>0.8067626270760894</v>
       </c>
       <c r="AJ15">
-        <v>0.7886562922000701</v>
+        <v>0.9684700735264501</v>
       </c>
       <c r="AK15">
-        <v>0.600315759952323</v>
+        <v>0.7930153051839731</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2335,7 +2323,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>China CITIC Bank Corporation Limited (SEHK:998)</t>
+          <t>China Zheshang Bank Co., Ltd (SEHK:2016)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2344,13 +2332,10 @@
         </is>
       </c>
       <c r="D16">
-        <v>0.0626</v>
+        <v>0.0674</v>
       </c>
       <c r="E16">
-        <v>0.0828</v>
-      </c>
-      <c r="F16">
-        <v>0.0675</v>
+        <v>0.0338</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2365,85 +2350,85 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>9104.700000000001</v>
+        <v>2166.9</v>
       </c>
       <c r="L16">
-        <v>0.4586334740426561</v>
+        <v>0.3951384963256077</v>
       </c>
       <c r="M16">
-        <v>2690.29</v>
+        <v>797.8</v>
       </c>
       <c r="N16">
-        <v>0.08293406989756126</v>
+        <v>0.07759643628299648</v>
       </c>
       <c r="O16">
-        <v>0.2954836513009764</v>
+        <v>0.3681757349208546</v>
       </c>
       <c r="P16">
-        <v>2684.4</v>
+        <v>797.8</v>
       </c>
       <c r="Q16">
-        <v>0.08275249777273581</v>
+        <v>0.07759643628299648</v>
       </c>
       <c r="R16">
-        <v>0.2948367326765297</v>
+        <v>0.3681757349208546</v>
       </c>
       <c r="S16">
-        <v>5.889999999999873</v>
+        <v>0</v>
       </c>
       <c r="T16">
-        <v>0.002189355050942416</v>
+        <v>0</v>
       </c>
       <c r="U16">
-        <v>45030</v>
+        <v>19510.6</v>
       </c>
       <c r="V16">
-        <v>1.388148180117082</v>
+        <v>1.89765985177116</v>
       </c>
       <c r="W16">
-        <v>0.09012627002542031</v>
+        <v>0.08615630516723127</v>
       </c>
       <c r="X16">
-        <v>0.162966551850205</v>
+        <v>0.2264395264810633</v>
       </c>
       <c r="Y16">
-        <v>-0.07284028182478472</v>
+        <v>-0.140283221313832</v>
       </c>
       <c r="Z16">
-        <v>0.07191245515840858</v>
+        <v>0.05267348757866588</v>
       </c>
       <c r="AA16">
         <v>0</v>
       </c>
       <c r="AB16">
-        <v>0.06145038473061266</v>
+        <v>0.06573834014289463</v>
       </c>
       <c r="AC16">
-        <v>-0.06145038473061266</v>
+        <v>-0.06573834014289463</v>
       </c>
       <c r="AD16">
-        <v>199017.8</v>
+        <v>105573</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>199017.8</v>
+        <v>105573</v>
       </c>
       <c r="AG16">
-        <v>153987.8</v>
+        <v>86062.39999999999</v>
       </c>
       <c r="AH16">
-        <v>0.8598489479889759</v>
+        <v>0.9112558521730725</v>
       </c>
       <c r="AI16">
-        <v>0.6595081635831618</v>
+        <v>0.7880805182357411</v>
       </c>
       <c r="AJ16">
-        <v>0.8259964908460001</v>
+        <v>0.8932842590805014</v>
       </c>
       <c r="AK16">
-        <v>0.5997881100114124</v>
+        <v>0.7519545379881103</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -2460,7 +2445,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>China Everbright Bank Company Limited (SHSE:601818)</t>
+          <t>Hua Xia Bank Co., Limited (SHSE:600015)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2469,13 +2454,10 @@
         </is>
       </c>
       <c r="D17">
-        <v>0.0617</v>
+        <v>0.0583</v>
       </c>
       <c r="E17">
-        <v>0.06269999999999999</v>
-      </c>
-      <c r="F17">
-        <v>0.0236</v>
+        <v>0.0452</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2490,85 +2472,85 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>6291.4</v>
+        <v>3837.6</v>
       </c>
       <c r="L17">
-        <v>0.455189378866259</v>
+        <v>0.3840326631908655</v>
       </c>
       <c r="M17">
-        <v>1488.2</v>
+        <v>5749.5</v>
       </c>
       <c r="N17">
-        <v>0.06543091547004565</v>
+        <v>0.3292031445928691</v>
       </c>
       <c r="O17">
-        <v>0.2365451250913946</v>
+        <v>1.498202001250782</v>
       </c>
       <c r="P17">
-        <v>1488.2</v>
+        <v>47</v>
       </c>
       <c r="Q17">
-        <v>0.06543091547004565</v>
+        <v>0.00269111188727104</v>
       </c>
       <c r="R17">
-        <v>0.2365451250913946</v>
+        <v>0.01224723785699395</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>5702.5</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>0.9918253761196626</v>
       </c>
       <c r="U17">
-        <v>14096.8</v>
+        <v>20356.1</v>
       </c>
       <c r="V17">
-        <v>0.6197866746392551</v>
+        <v>1.165543461456979</v>
       </c>
       <c r="W17">
-        <v>0.10241709154604</v>
+        <v>0.09038047126152542</v>
       </c>
       <c r="X17">
-        <v>0.2193807511961028</v>
+        <v>0.219876431080933</v>
       </c>
       <c r="Y17">
-        <v>-0.1169636596500628</v>
+        <v>-0.1294959598194076</v>
       </c>
       <c r="Z17">
-        <v>0.06106100312958902</v>
+        <v>0.06017778307718526</v>
       </c>
       <c r="AA17">
         <v>0</v>
       </c>
       <c r="AB17">
-        <v>0.06147576870955785</v>
+        <v>0.06574145033183033</v>
       </c>
       <c r="AC17">
-        <v>-0.06147576870955785</v>
+        <v>-0.06574145033183033</v>
       </c>
       <c r="AD17">
-        <v>216720</v>
+        <v>171973.9</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>216720</v>
+        <v>171973.9</v>
       </c>
       <c r="AG17">
-        <v>202623.2</v>
+        <v>151617.8</v>
       </c>
       <c r="AH17">
-        <v>0.905018946433001</v>
+        <v>0.9078071651636307</v>
       </c>
       <c r="AI17">
-        <v>0.7418033502320188</v>
+        <v>0.7724661175036394</v>
       </c>
       <c r="AJ17">
-        <v>0.8990778629422659</v>
+        <v>0.8967079423264473</v>
       </c>
       <c r="AK17">
-        <v>0.7287133783434351</v>
+        <v>0.7495679119766495</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -2585,7 +2567,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Shanghai Rural Commercial Bank Co., Ltd. (SHSE:601825)</t>
+          <t>China Minsheng Banking Corp., Ltd. (SHSE:600016)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2593,6 +2575,15 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
+      <c r="D18">
+        <v>-0.04389999999999999</v>
+      </c>
+      <c r="E18">
+        <v>-0.0925</v>
+      </c>
+      <c r="F18">
+        <v>-0.0117</v>
+      </c>
       <c r="G18">
         <v>0</v>
       </c>
@@ -2606,706 +2597,90 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>1698.8</v>
+        <v>4666.3</v>
       </c>
       <c r="L18">
-        <v>0.5374928810985256</v>
+        <v>0.3637618004505804</v>
       </c>
       <c r="M18">
-        <v>799.4</v>
+        <v>7847.837600000001</v>
       </c>
       <c r="N18">
-        <v>0.1023939747153232</v>
+        <v>0.3304338760678903</v>
       </c>
       <c r="O18">
-        <v>0.470567459383094</v>
+        <v>1.68181162805649</v>
       </c>
       <c r="P18">
-        <v>799.4</v>
+        <v>2145.3376</v>
       </c>
       <c r="Q18">
-        <v>0.1023939747153232</v>
+        <v>0.09032962387526791</v>
       </c>
       <c r="R18">
-        <v>0.470567459383094</v>
+        <v>0.4597513233182607</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>5702.5</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>0.7266332830332778</v>
       </c>
       <c r="U18">
-        <v>4287.2</v>
+        <v>26109.1</v>
       </c>
       <c r="V18">
-        <v>0.5491411663741977</v>
+        <v>1.099325897575168</v>
       </c>
       <c r="W18">
-        <v>0.120247743762166</v>
+        <v>0.05664394661293162</v>
       </c>
       <c r="X18">
-        <v>0.132577012595021</v>
+        <v>0.2189512125328051</v>
       </c>
       <c r="Y18">
-        <v>-0.01232926883285498</v>
+        <v>-0.1623072659198734</v>
       </c>
       <c r="Z18">
-        <v>0.08959048480227221</v>
+        <v>0.05752584041611938</v>
       </c>
       <c r="AA18">
         <v>0</v>
       </c>
       <c r="AB18">
-        <v>0.06223585186809145</v>
+        <v>0.06574190833194742</v>
       </c>
       <c r="AC18">
-        <v>-0.06223585186809145</v>
+        <v>-0.06574190833194742</v>
       </c>
       <c r="AD18">
-        <v>33627.2</v>
+        <v>232451.9</v>
       </c>
       <c r="AE18">
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>33627.2</v>
+        <v>232451.9</v>
       </c>
       <c r="AG18">
-        <v>29340</v>
+        <v>206342.8</v>
       </c>
       <c r="AH18">
-        <v>0.8115788127227925</v>
+        <v>0.9072993185064909</v>
       </c>
       <c r="AI18">
-        <v>0.6830354241143971</v>
+        <v>0.7161444662156333</v>
       </c>
       <c r="AJ18">
-        <v>0.789832853708634</v>
+        <v>0.8967803874000457</v>
       </c>
       <c r="AK18">
-        <v>0.652800768943237</v>
+        <v>0.6913145284306528</v>
       </c>
       <c r="AL18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Shanghai Pudong Development Bank Co., Ltd. (SHSE:600000)</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D19">
-        <v>-0.0249</v>
-      </c>
-      <c r="E19">
-        <v>-0.0698</v>
-      </c>
-      <c r="F19">
-        <v>-0.08779999999999999</v>
-      </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-      <c r="K19">
-        <v>5303.2</v>
-      </c>
-      <c r="L19">
-        <v>0.3978752775943821</v>
-      </c>
-      <c r="M19">
-        <v>1291.4968</v>
-      </c>
-      <c r="N19">
-        <v>0.04712975951538152</v>
-      </c>
-      <c r="O19">
-        <v>0.2435316035601146</v>
-      </c>
-      <c r="P19">
-        <v>1291.4968</v>
-      </c>
-      <c r="Q19">
-        <v>0.04712975951538152</v>
-      </c>
-      <c r="R19">
-        <v>0.2435316035601146</v>
-      </c>
-      <c r="S19">
-        <v>0</v>
-      </c>
-      <c r="T19">
-        <v>0</v>
-      </c>
-      <c r="U19">
-        <v>25652.8</v>
-      </c>
-      <c r="V19">
-        <v>0.9361310805386271</v>
-      </c>
-      <c r="W19">
-        <v>0.05698339989921099</v>
-      </c>
-      <c r="X19">
-        <v>0.2320719501957128</v>
-      </c>
-      <c r="Y19">
-        <v>-0.1750885502965018</v>
-      </c>
-      <c r="Z19">
-        <v>0.03565647391800413</v>
-      </c>
-      <c r="AA19">
-        <v>0</v>
-      </c>
-      <c r="AB19">
-        <v>0.06239195640379271</v>
-      </c>
-      <c r="AC19">
-        <v>-0.06239195640379271</v>
-      </c>
-      <c r="AD19">
-        <v>282025.6</v>
-      </c>
-      <c r="AE19">
-        <v>0</v>
-      </c>
-      <c r="AF19">
-        <v>282025.6</v>
-      </c>
-      <c r="AG19">
-        <v>256372.8</v>
-      </c>
-      <c r="AH19">
-        <v>0.9114399897100656</v>
-      </c>
-      <c r="AI19">
-        <v>0.7397883715299665</v>
-      </c>
-      <c r="AJ19">
-        <v>0.9034343309048904</v>
-      </c>
-      <c r="AK19">
-        <v>0.7210153558253618</v>
-      </c>
-      <c r="AL19">
-        <v>0</v>
-      </c>
-      <c r="AM19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>China Minsheng Banking Corp., Ltd. (SHSE:600016)</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D20">
-        <v>-0.0373</v>
-      </c>
-      <c r="E20">
-        <v>-0.0767</v>
-      </c>
-      <c r="F20">
-        <v>0.0314</v>
-      </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="H20">
-        <v>0</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20">
-        <v>0</v>
-      </c>
-      <c r="K20">
-        <v>4806.1</v>
-      </c>
-      <c r="L20">
-        <v>0.3744001620341519</v>
-      </c>
-      <c r="M20">
-        <v>28.8</v>
-      </c>
-      <c r="N20">
-        <v>0.001337885861612431</v>
-      </c>
-      <c r="O20">
-        <v>0.005992384677805289</v>
-      </c>
-      <c r="P20">
-        <v>28.8</v>
-      </c>
-      <c r="Q20">
-        <v>0.001337885861612431</v>
-      </c>
-      <c r="R20">
-        <v>0.005992384677805289</v>
-      </c>
-      <c r="S20">
-        <v>0</v>
-      </c>
-      <c r="T20">
-        <v>0</v>
-      </c>
-      <c r="U20">
-        <v>28615.2</v>
-      </c>
-      <c r="V20">
-        <v>1.329301094000418</v>
-      </c>
-      <c r="W20">
-        <v>0.05909781185251677</v>
-      </c>
-      <c r="X20">
-        <v>0.1895524202837576</v>
-      </c>
-      <c r="Y20">
-        <v>-0.1304546084312408</v>
-      </c>
-      <c r="Z20">
-        <v>0.05035613091621185</v>
-      </c>
-      <c r="AA20">
-        <v>0</v>
-      </c>
-      <c r="AB20">
-        <v>0.06324666895327041</v>
-      </c>
-      <c r="AC20">
-        <v>-0.06324666895327041</v>
-      </c>
-      <c r="AD20">
-        <v>166491.8</v>
-      </c>
-      <c r="AE20">
-        <v>0</v>
-      </c>
-      <c r="AF20">
-        <v>166491.8</v>
-      </c>
-      <c r="AG20">
-        <v>137876.6</v>
-      </c>
-      <c r="AH20">
-        <v>0.8855084850783141</v>
-      </c>
-      <c r="AI20">
-        <v>0.6569457580718541</v>
-      </c>
-      <c r="AJ20">
-        <v>0.8649555748915799</v>
-      </c>
-      <c r="AK20">
-        <v>0.6132812378373786</v>
-      </c>
-      <c r="AL20">
-        <v>0</v>
-      </c>
-      <c r="AM20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>China Zheshang Bank Co., Ltd (SEHK:2016)</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D21">
-        <v>0.0776</v>
-      </c>
-      <c r="E21">
-        <v>0.0481</v>
-      </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
-      <c r="K21">
-        <v>2033</v>
-      </c>
-      <c r="L21">
-        <v>0.405918057663126</v>
-      </c>
-      <c r="M21">
-        <v>629.6</v>
-      </c>
-      <c r="N21">
-        <v>0.06852789115646259</v>
-      </c>
-      <c r="O21">
-        <v>0.3096901131333005</v>
-      </c>
-      <c r="P21">
-        <v>629.6</v>
-      </c>
-      <c r="Q21">
-        <v>0.06852789115646259</v>
-      </c>
-      <c r="R21">
-        <v>0.3096901131333005</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-      <c r="T21">
-        <v>0</v>
-      </c>
-      <c r="U21">
-        <v>11358</v>
-      </c>
-      <c r="V21">
-        <v>1.236244897959184</v>
-      </c>
-      <c r="W21">
-        <v>0.09045726972996303</v>
-      </c>
-      <c r="X21">
-        <v>0.2244042543255101</v>
-      </c>
-      <c r="Y21">
-        <v>-0.1339469845955471</v>
-      </c>
-      <c r="Z21">
-        <v>0.06967850002852027</v>
-      </c>
-      <c r="AA21">
-        <v>0</v>
-      </c>
-      <c r="AB21">
-        <v>0.06330371435665214</v>
-      </c>
-      <c r="AC21">
-        <v>-0.06330371435665214</v>
-      </c>
-      <c r="AD21">
-        <v>90318.39999999999</v>
-      </c>
-      <c r="AE21">
-        <v>0</v>
-      </c>
-      <c r="AF21">
-        <v>90318.39999999999</v>
-      </c>
-      <c r="AG21">
-        <v>78960.39999999999</v>
-      </c>
-      <c r="AH21">
-        <v>0.9076687914987955</v>
-      </c>
-      <c r="AI21">
-        <v>0.7791852400790586</v>
-      </c>
-      <c r="AJ21">
-        <v>0.895771765407911</v>
-      </c>
-      <c r="AK21">
-        <v>0.7551979371800156</v>
-      </c>
-      <c r="AL21">
-        <v>0</v>
-      </c>
-      <c r="AM21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Hua Xia Bank Co., Limited (SHSE:600015)</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D22">
-        <v>0.05980000000000001</v>
-      </c>
-      <c r="E22">
-        <v>0.0521</v>
-      </c>
-      <c r="G22">
-        <v>0</v>
-      </c>
-      <c r="H22">
-        <v>0</v>
-      </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
-      <c r="J22">
-        <v>0</v>
-      </c>
-      <c r="K22">
-        <v>3551.5</v>
-      </c>
-      <c r="L22">
-        <v>0.399246810184925</v>
-      </c>
-      <c r="M22">
-        <v>174.5</v>
-      </c>
-      <c r="N22">
-        <v>0.01383427411682628</v>
-      </c>
-      <c r="O22">
-        <v>0.0491341686611291</v>
-      </c>
-      <c r="P22">
-        <v>174.5</v>
-      </c>
-      <c r="Q22">
-        <v>0.01383427411682628</v>
-      </c>
-      <c r="R22">
-        <v>0.0491341686611291</v>
-      </c>
-      <c r="S22">
-        <v>0</v>
-      </c>
-      <c r="T22">
-        <v>0</v>
-      </c>
-      <c r="U22">
-        <v>24168.9</v>
-      </c>
-      <c r="V22">
-        <v>1.916098496860531</v>
-      </c>
-      <c r="W22">
-        <v>0.08814886149844377</v>
-      </c>
-      <c r="X22">
-        <v>0.2557287820104563</v>
-      </c>
-      <c r="Y22">
-        <v>-0.1675799205120125</v>
-      </c>
-      <c r="Z22">
-        <v>0.05687099863568421</v>
-      </c>
-      <c r="AA22">
-        <v>0</v>
-      </c>
-      <c r="AB22">
-        <v>0.06333893519560696</v>
-      </c>
-      <c r="AC22">
-        <v>-0.06333893519560696</v>
-      </c>
-      <c r="AD22">
-        <v>147764.7</v>
-      </c>
-      <c r="AE22">
-        <v>0</v>
-      </c>
-      <c r="AF22">
-        <v>147764.7</v>
-      </c>
-      <c r="AG22">
-        <v>123595.8</v>
-      </c>
-      <c r="AH22">
-        <v>0.9213509558338004</v>
-      </c>
-      <c r="AI22">
-        <v>0.7750501175441302</v>
-      </c>
-      <c r="AJ22">
-        <v>0.9073955248316196</v>
-      </c>
-      <c r="AK22">
-        <v>0.7423933629219578</v>
-      </c>
-      <c r="AL22">
-        <v>0</v>
-      </c>
-      <c r="AM22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>China Bohai Bank Co., Ltd. (SEHK:9668)</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D23">
-        <v>-0.00641</v>
-      </c>
-      <c r="E23">
-        <v>-0.0444</v>
-      </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-      <c r="H23">
-        <v>0</v>
-      </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-      <c r="J23">
-        <v>0</v>
-      </c>
-      <c r="K23">
-        <v>800.2</v>
-      </c>
-      <c r="L23">
-        <v>0.3298705581663781</v>
-      </c>
-      <c r="M23">
-        <v>344.1</v>
-      </c>
-      <c r="N23">
-        <v>0.1339275288989219</v>
-      </c>
-      <c r="O23">
-        <v>0.4300174956260935</v>
-      </c>
-      <c r="P23">
-        <v>344.1</v>
-      </c>
-      <c r="Q23">
-        <v>0.1339275288989219</v>
-      </c>
-      <c r="R23">
-        <v>0.4300174956260935</v>
-      </c>
-      <c r="S23">
-        <v>0</v>
-      </c>
-      <c r="T23">
-        <v>0</v>
-      </c>
-      <c r="U23">
-        <v>8135.8</v>
-      </c>
-      <c r="V23">
-        <v>3.166543416494765</v>
-      </c>
-      <c r="W23">
-        <v>0.04899133682309365</v>
-      </c>
-      <c r="X23">
-        <v>0.4895453001744814</v>
-      </c>
-      <c r="Y23">
-        <v>-0.4405539633513878</v>
-      </c>
-      <c r="Z23">
-        <v>0.03104360411918348</v>
-      </c>
-      <c r="AA23">
-        <v>0</v>
-      </c>
-      <c r="AB23">
-        <v>0.06344526498581979</v>
-      </c>
-      <c r="AC23">
-        <v>-0.06344526498581979</v>
-      </c>
-      <c r="AD23">
-        <v>66232.8</v>
-      </c>
-      <c r="AE23">
-        <v>0</v>
-      </c>
-      <c r="AF23">
-        <v>66232.8</v>
-      </c>
-      <c r="AG23">
-        <v>58097</v>
-      </c>
-      <c r="AH23">
-        <v>0.9626566630960391</v>
-      </c>
-      <c r="AI23">
-        <v>0.8078885031701849</v>
-      </c>
-      <c r="AJ23">
-        <v>0.9576486451291738</v>
-      </c>
-      <c r="AK23">
-        <v>0.7867233245042439</v>
-      </c>
-      <c r="AL23">
-        <v>0</v>
-      </c>
-      <c r="AM23">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/china/china_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/china/china_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ18"/>
+  <dimension ref="A1:AQ24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,112 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.03605</v>
+        <v>0.0387</v>
       </c>
       <c r="E2">
-        <v>0.04535</v>
+        <v>0.0387</v>
       </c>
       <c r="F2">
-        <v>0.011995</v>
+        <v>0.0146</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.007231623003009946</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.007231623003009946</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>0.007246687121143775</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.006446333656052309</v>
       </c>
       <c r="K2">
-        <v>259760.2</v>
+        <v>278232.5</v>
       </c>
       <c r="L2">
-        <v>0.4715312500850901</v>
+        <v>0.4709356459180725</v>
       </c>
       <c r="M2">
-        <v>141104.5081</v>
+        <v>145774.7825</v>
       </c>
       <c r="N2">
-        <v>0.09587547383291307</v>
+        <v>0.09251583830358796</v>
       </c>
       <c r="O2">
-        <v>0.5432106539031</v>
+        <v>0.5239315410672729</v>
       </c>
       <c r="P2">
-        <v>94983.50810000001</v>
+        <v>99653.7825</v>
       </c>
       <c r="Q2">
-        <v>0.06453790150309052</v>
+        <v>0.06324518596425224</v>
       </c>
       <c r="R2">
-        <v>0.3656584345869768</v>
+        <v>0.3581672971345907</v>
       </c>
       <c r="S2">
         <v>46121</v>
       </c>
       <c r="T2">
-        <v>0.3268570269017507</v>
+        <v>0.3163853117050612</v>
       </c>
       <c r="U2">
-        <v>1409670.8</v>
+        <v>1497739.7</v>
       </c>
       <c r="V2">
-        <v>0.957820963470845</v>
+        <v>0.9505391915509415</v>
       </c>
       <c r="W2">
         <v>0.09870087969447311</v>
       </c>
       <c r="X2">
-        <v>0.1444013036825047</v>
+        <v>0.1443577704392799</v>
       </c>
       <c r="Y2">
-        <v>-0.04570042398803162</v>
+        <v>-0.04565689074480683</v>
       </c>
       <c r="Z2">
-        <v>0.1042209615719441</v>
+        <v>0.1000778864200255</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06389506258956437</v>
+        <v>0.06361763530931856</v>
       </c>
       <c r="AC2">
-        <v>-0.06389506258956437</v>
+        <v>-0.06344630172481372</v>
       </c>
       <c r="AD2">
-        <v>4845258.5</v>
+        <v>5391020</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>4845258.5</v>
+        <v>5391020</v>
       </c>
       <c r="AG2">
-        <v>3435587.7</v>
+        <v>3893280.3</v>
       </c>
       <c r="AH2">
-        <v>0.7670181643956594</v>
+        <v>0.7738276081546744</v>
       </c>
       <c r="AI2">
-        <v>0.6231343619496005</v>
+        <v>0.6294656310821993</v>
       </c>
       <c r="AJ2">
-        <v>0.7000922944863316</v>
+        <v>0.7118875435432892</v>
       </c>
       <c r="AK2">
-        <v>0.5396815829560293</v>
+        <v>0.5509333473408158</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>2789.9</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>2188.3</v>
+      </c>
+      <c r="AN2">
+        <v>1235.452378769823</v>
+      </c>
+      <c r="AO2">
+        <v>1.5346069751604</v>
+      </c>
+      <c r="AP2">
+        <v>892.2175038958657</v>
+      </c>
+      <c r="AQ2">
+        <v>1.956495910067175</v>
       </c>
     </row>
     <row r="3">
@@ -704,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bank of China Limited (SEHK:3988)</t>
+          <t>CNPC Capital Company Limited (SZSE:000617)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,112 +725,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0391</v>
+        <v>0.0385</v>
       </c>
       <c r="E3">
-        <v>0.0455</v>
-      </c>
-      <c r="F3">
-        <v>0.00555</v>
+        <v>-0.12</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.7493642024028765</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.7493642024028765</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>0.7509251951240901</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>0.5692110532947328</v>
       </c>
       <c r="K3">
-        <v>33189.7</v>
+        <v>570.6</v>
       </c>
       <c r="L3">
-        <v>0.437788954533643</v>
+        <v>0.1000789265982636</v>
       </c>
       <c r="M3">
-        <v>15623.8</v>
+        <v>449.2</v>
       </c>
       <c r="N3">
-        <v>0.0774050928288396</v>
+        <v>0.03764193237524616</v>
       </c>
       <c r="O3">
-        <v>0.4707424291271087</v>
+        <v>0.7872415001752541</v>
       </c>
       <c r="P3">
-        <v>9921.299999999999</v>
+        <v>449.2</v>
       </c>
       <c r="Q3">
-        <v>0.04915316040161589</v>
+        <v>0.03764193237524616</v>
       </c>
       <c r="R3">
-        <v>0.2989270767738184</v>
+        <v>0.7872415001752541</v>
       </c>
       <c r="S3">
-        <v>5702.5</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>0.364988031080787</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>76029.39999999999</v>
+        <v>5364.1</v>
       </c>
       <c r="V3">
-        <v>0.3766729454243511</v>
+        <v>0.4494993086688734</v>
       </c>
       <c r="W3">
-        <v>0.09900900605275953</v>
+        <v>0.04153896552979289</v>
       </c>
       <c r="X3">
-        <v>0.1387775609890181</v>
+        <v>0.08304657578110811</v>
       </c>
       <c r="Y3">
-        <v>-0.03976855493625855</v>
+        <v>-0.04150761025131522</v>
       </c>
       <c r="Z3">
-        <v>0.07509027223109692</v>
+        <v>0.2225057231367707</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>0.1266527170307874</v>
       </c>
       <c r="AB3">
-        <v>0.06242487499525222</v>
+        <v>0.06435155294400365</v>
       </c>
       <c r="AC3">
-        <v>-0.06242487499525222</v>
+        <v>0.06230116408678378</v>
       </c>
       <c r="AD3">
-        <v>936196.9</v>
+        <v>12648.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>936196.9</v>
+        <v>12648.4</v>
       </c>
       <c r="AG3">
-        <v>860167.5</v>
+        <v>7284.299999999999</v>
       </c>
       <c r="AH3">
-        <v>0.8226386296106074</v>
+        <v>0.51454118680818</v>
       </c>
       <c r="AI3">
-        <v>0.6955828337731326</v>
+        <v>0.3231562434530227</v>
       </c>
       <c r="AJ3">
-        <v>0.8099413368265765</v>
+        <v>0.3790392240527011</v>
       </c>
       <c r="AK3">
-        <v>0.6773570861929692</v>
+        <v>0.2156643306953733</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>2789.9</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>2188.3</v>
+      </c>
+      <c r="AN3">
+        <v>2.898615821798515</v>
+      </c>
+      <c r="AO3">
+        <v>1.5346069751604</v>
+      </c>
+      <c r="AP3">
+        <v>1.669332661105509</v>
+      </c>
+      <c r="AQ3">
+        <v>1.956495910067175</v>
       </c>
     </row>
     <row r="4">
@@ -829,7 +850,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bank of Communications Co., Ltd. (SEHK:3328)</t>
+          <t>Bank of Beijing Co., Ltd. (SHSE:601169)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -838,13 +859,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0216</v>
+        <v>0.0387</v>
       </c>
       <c r="E4">
-        <v>0.0382</v>
-      </c>
-      <c r="F4">
-        <v>0.0146</v>
+        <v>0.0392</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -859,28 +877,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>13151.6</v>
+        <v>3707.9</v>
       </c>
       <c r="L4">
-        <v>0.4579439252336449</v>
+        <v>0.5280705252364133</v>
       </c>
       <c r="M4">
-        <v>5866.753299999999</v>
+        <v>972.578</v>
       </c>
       <c r="N4">
-        <v>0.0831147348915227</v>
+        <v>0.05459504670379019</v>
       </c>
       <c r="O4">
-        <v>0.4460866586575017</v>
+        <v>0.262298875374201</v>
       </c>
       <c r="P4">
-        <v>5866.753299999999</v>
+        <v>972.578</v>
       </c>
       <c r="Q4">
-        <v>0.0831147348915227</v>
+        <v>0.05459504670379019</v>
       </c>
       <c r="R4">
-        <v>0.4460866586575017</v>
+        <v>0.262298875374201</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -889,55 +907,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>22847.1</v>
+        <v>23068.9</v>
       </c>
       <c r="V4">
-        <v>0.3236765826748004</v>
+        <v>1.294958011496318</v>
       </c>
       <c r="W4">
-        <v>0.09441002706330805</v>
+        <v>0.08860103131705592</v>
       </c>
       <c r="X4">
-        <v>0.1634185212218977</v>
+        <v>0.1733012063745591</v>
       </c>
       <c r="Y4">
-        <v>-0.06900849415858969</v>
+        <v>-0.08470017505750317</v>
       </c>
       <c r="Z4">
-        <v>0.05793543922929735</v>
+        <v>0.05497134625622397</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.06287560304862097</v>
+        <v>0.06052933594138908</v>
       </c>
       <c r="AC4">
-        <v>-0.06287560304862097</v>
+        <v>-0.06052933594138908</v>
       </c>
       <c r="AD4">
-        <v>439101.7</v>
+        <v>122191.2</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>439101.7</v>
+        <v>122191.2</v>
       </c>
       <c r="AG4">
-        <v>416254.6</v>
+        <v>99122.29999999999</v>
       </c>
       <c r="AH4">
-        <v>0.8615109363985294</v>
+        <v>0.8727593753392721</v>
       </c>
       <c r="AI4">
-        <v>0.7299054451134341</v>
+        <v>0.7070738517179024</v>
       </c>
       <c r="AJ4">
-        <v>0.8550117410044515</v>
+        <v>0.8476577498766427</v>
       </c>
       <c r="AK4">
-        <v>0.7192428378892076</v>
+        <v>0.6619468210995328</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -954,7 +972,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>China Construction Bank Corporation (SEHK:939)</t>
+          <t>Bank of Shanghai Co., Ltd. (SHSE:601229)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -963,13 +981,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0312</v>
+        <v>0.04219999999999999</v>
       </c>
       <c r="E5">
-        <v>0.046</v>
-      </c>
-      <c r="F5">
-        <v>0.00481</v>
+        <v>0.0252</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -984,28 +999,28 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>47469.5</v>
+        <v>3248.6</v>
       </c>
       <c r="L5">
-        <v>0.5379845822217286</v>
+        <v>0.5751668702749597</v>
       </c>
       <c r="M5">
-        <v>21250.935</v>
+        <v>121.7</v>
       </c>
       <c r="N5">
-        <v>0.1001830794687938</v>
+        <v>0.006833546706196797</v>
       </c>
       <c r="O5">
-        <v>0.447675560096483</v>
+        <v>0.03746229144862402</v>
       </c>
       <c r="P5">
-        <v>21250.935</v>
+        <v>121.7</v>
       </c>
       <c r="Q5">
-        <v>0.1001830794687938</v>
+        <v>0.006833546706196797</v>
       </c>
       <c r="R5">
-        <v>0.447675560096483</v>
+        <v>0.03746229144862402</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1014,55 +1029,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>197560.6</v>
+        <v>8015.7</v>
       </c>
       <c r="V5">
-        <v>0.9313580456437599</v>
+        <v>0.4500875951755272</v>
       </c>
       <c r="W5">
-        <v>0.1148303772726833</v>
+        <v>0.1020927024113689</v>
       </c>
       <c r="X5">
-        <v>0.1084589001396917</v>
+        <v>0.1621410201729092</v>
       </c>
       <c r="Y5">
-        <v>0.006371477132991618</v>
+        <v>-0.06004831776154032</v>
       </c>
       <c r="Z5">
-        <v>0.1183040685316712</v>
+        <v>0.05117182120621299</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.06289523690518523</v>
+        <v>0.06061748062223465</v>
       </c>
       <c r="AC5">
-        <v>-0.06289523690518523</v>
+        <v>-0.06061748062223465</v>
       </c>
       <c r="AD5">
-        <v>570811.7</v>
+        <v>109384.8</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>570811.7</v>
+        <v>109384.8</v>
       </c>
       <c r="AG5">
-        <v>373251.1</v>
+        <v>101369.1</v>
       </c>
       <c r="AH5">
-        <v>0.7290686670770041</v>
+        <v>0.8599839615076184</v>
       </c>
       <c r="AI5">
-        <v>0.5449576554240744</v>
+        <v>0.7563846978846638</v>
       </c>
       <c r="AJ5">
-        <v>0.6376304917846273</v>
+        <v>0.8505667558607566</v>
       </c>
       <c r="AK5">
-        <v>0.4391800647078293</v>
+        <v>0.7420892886948425</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1079,7 +1094,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>China CITIC Bank Corporation Limited (SEHK:998)</t>
+          <t>Industrial Bank Co., Ltd. (SHSE:601166)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1088,13 +1103,13 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0567</v>
+        <v>0.0407</v>
       </c>
       <c r="E6">
-        <v>0.0682</v>
+        <v>0.0297</v>
       </c>
       <c r="F6">
-        <v>-0.00461</v>
+        <v>0.0365</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1109,85 +1124,85 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>9610</v>
+        <v>10714.5</v>
       </c>
       <c r="L6">
-        <v>0.4466090706720514</v>
+        <v>0.5157723467653812</v>
       </c>
       <c r="M6">
-        <v>3713.5</v>
+        <v>3074.5964</v>
       </c>
       <c r="N6">
-        <v>0.07842843233950525</v>
+        <v>0.05638140471392079</v>
       </c>
       <c r="O6">
-        <v>0.386420395421436</v>
+        <v>0.2869565915348359</v>
       </c>
       <c r="P6">
-        <v>3212.3</v>
+        <v>3074.5964</v>
       </c>
       <c r="Q6">
-        <v>0.06784318115098767</v>
+        <v>0.05638140471392079</v>
       </c>
       <c r="R6">
-        <v>0.3342663891779397</v>
+        <v>0.2869565915348359</v>
       </c>
       <c r="S6">
-        <v>501.1999999999998</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>0.1349670122525918</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>33779.6</v>
+        <v>47422.8</v>
       </c>
       <c r="V6">
-        <v>0.7134188967431133</v>
+        <v>0.8696309146356</v>
       </c>
       <c r="W6">
-        <v>0.1050179109631705</v>
+        <v>0.1074467103626985</v>
       </c>
       <c r="X6">
-        <v>0.1500250463759914</v>
+        <v>0.151057130985047</v>
       </c>
       <c r="Y6">
-        <v>-0.04500713541282085</v>
+        <v>-0.04361042062234852</v>
       </c>
       <c r="Z6">
-        <v>0.07336225633507497</v>
+        <v>0.05955603821343067</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.06295570511968698</v>
+        <v>0.0607244821225883</v>
       </c>
       <c r="AC6">
-        <v>-0.06295570511968698</v>
+        <v>-0.0607244821225883</v>
       </c>
       <c r="AD6">
-        <v>253817.7</v>
+        <v>296101.4</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>253817.7</v>
+        <v>296101.4</v>
       </c>
       <c r="AG6">
-        <v>220038.1</v>
+        <v>248678.6</v>
       </c>
       <c r="AH6">
-        <v>0.8427817028847155</v>
+        <v>0.8444754993461835</v>
       </c>
       <c r="AI6">
-        <v>0.6820540918779417</v>
+        <v>0.7025120916445349</v>
       </c>
       <c r="AJ6">
-        <v>0.8229199624514281</v>
+        <v>0.8201511358273307</v>
       </c>
       <c r="AK6">
-        <v>0.6503122731689787</v>
+        <v>0.6647976590264942</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1204,7 +1219,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Agricultural Bank of China Limited (SEHK:1288)</t>
+          <t>Zhejiang Shaoxing RuiFeng Rural Commercial Bank Co.,Ltd (SHSE:601528)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1212,15 +1227,6 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D7">
-        <v>0.033</v>
-      </c>
-      <c r="E7">
-        <v>0.0546</v>
-      </c>
-      <c r="F7">
-        <v>0.0216</v>
-      </c>
       <c r="G7">
         <v>0</v>
       </c>
@@ -1234,85 +1240,85 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>39400.1</v>
+        <v>272.4</v>
       </c>
       <c r="L7">
-        <v>0.4888926114120151</v>
+        <v>0.6621293145357317</v>
       </c>
       <c r="M7">
-        <v>30483.8</v>
+        <v>52.2</v>
       </c>
       <c r="N7">
-        <v>0.1214058220535179</v>
+        <v>0.03448959365708622</v>
       </c>
       <c r="O7">
-        <v>0.7736985439123252</v>
+        <v>0.1916299559471366</v>
       </c>
       <c r="P7">
-        <v>13376.4</v>
+        <v>52.2</v>
       </c>
       <c r="Q7">
-        <v>0.05327330707184393</v>
+        <v>0.03448959365708622</v>
       </c>
       <c r="R7">
-        <v>0.3395016763916843</v>
+        <v>0.1916299559471366</v>
       </c>
       <c r="S7">
-        <v>17107.4</v>
+        <v>0</v>
       </c>
       <c r="T7">
-        <v>0.561196438764196</v>
+        <v>0</v>
       </c>
       <c r="U7">
-        <v>396326.5</v>
+        <v>1190.5</v>
       </c>
       <c r="V7">
-        <v>1.578423442421665</v>
+        <v>0.7865873802444665</v>
       </c>
       <c r="W7">
-        <v>0.105090137235635</v>
+        <v>0.1238519596253524</v>
       </c>
       <c r="X7">
-        <v>0.1044092230825776</v>
+        <v>0.1129733542631618</v>
       </c>
       <c r="Y7">
-        <v>0.0006809141530574048</v>
+        <v>0.01087860536219058</v>
       </c>
       <c r="Z7">
-        <v>0.1462374086725014</v>
+        <v>0.08448332511910628</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.06299848405221703</v>
+        <v>0.06138376090361815</v>
       </c>
       <c r="AC7">
-        <v>-0.06299848405221703</v>
+        <v>-0.06138376090361815</v>
       </c>
       <c r="AD7">
-        <v>610369.7</v>
+        <v>4514.5</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>610369.7</v>
+        <v>4514.5</v>
       </c>
       <c r="AG7">
-        <v>214043.2</v>
+        <v>3324</v>
       </c>
       <c r="AH7">
-        <v>0.7085295216329305</v>
+        <v>0.748921698739217</v>
       </c>
       <c r="AI7">
-        <v>0.5871638118288982</v>
+        <v>0.6358540261130439</v>
       </c>
       <c r="AJ7">
-        <v>0.4601760398578214</v>
+        <v>0.6871317829457364</v>
       </c>
       <c r="AK7">
-        <v>0.3327809351900005</v>
+        <v>0.5624936541780892</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1329,7 +1335,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Industrial and Commercial Bank of China Limited (SEHK:1398)</t>
+          <t>Bank of China Limited (SEHK:3988)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1338,13 +1344,13 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.00369</v>
+        <v>0.0391</v>
       </c>
       <c r="E8">
-        <v>0.033</v>
+        <v>0.0455</v>
       </c>
       <c r="F8">
-        <v>0.009389999999999999</v>
+        <v>0.00555</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1359,85 +1365,85 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>51941.7</v>
+        <v>33189.7</v>
       </c>
       <c r="L8">
-        <v>0.5595357104384359</v>
+        <v>0.437788954533643</v>
       </c>
       <c r="M8">
-        <v>28273.5</v>
+        <v>15623.8</v>
       </c>
       <c r="N8">
-        <v>0.09009271677648842</v>
+        <v>0.0774050928288396</v>
       </c>
       <c r="O8">
-        <v>0.5443314331259855</v>
+        <v>0.4707424291271087</v>
       </c>
       <c r="P8">
-        <v>16868.6</v>
+        <v>9921.299999999999</v>
       </c>
       <c r="Q8">
-        <v>0.05375132198758104</v>
+        <v>0.04915316040161589</v>
       </c>
       <c r="R8">
-        <v>0.3247602600607989</v>
+        <v>0.2989270767738184</v>
       </c>
       <c r="S8">
-        <v>11404.9</v>
+        <v>5702.5</v>
       </c>
       <c r="T8">
-        <v>0.4033777211876846</v>
+        <v>0.364988031080787</v>
       </c>
       <c r="U8">
-        <v>432605.6</v>
+        <v>76029.39999999999</v>
       </c>
       <c r="V8">
-        <v>1.378485641916382</v>
+        <v>0.3766729454243511</v>
       </c>
       <c r="W8">
-        <v>0.107626142143497</v>
+        <v>0.09900900605275953</v>
       </c>
       <c r="X8">
-        <v>0.0930236297858274</v>
+        <v>0.1387365106719755</v>
       </c>
       <c r="Y8">
-        <v>0.01460251235766956</v>
+        <v>-0.03972750461921593</v>
       </c>
       <c r="Z8">
-        <v>0.258150311168039</v>
+        <v>0.07509027223109692</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.06339535511300028</v>
+        <v>0.06241759425476662</v>
       </c>
       <c r="AC8">
-        <v>-0.06339535511300028</v>
+        <v>-0.06241759425476662</v>
       </c>
       <c r="AD8">
-        <v>533390.1</v>
+        <v>936196.9</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>533390.1</v>
+        <v>936196.9</v>
       </c>
       <c r="AG8">
-        <v>100784.5</v>
+        <v>860167.5</v>
       </c>
       <c r="AH8">
-        <v>0.6295792293070676</v>
+        <v>0.8226386296106074</v>
       </c>
       <c r="AI8">
-        <v>0.4882033189472077</v>
+        <v>0.6955828337731326</v>
       </c>
       <c r="AJ8">
-        <v>0.2430819524412269</v>
+        <v>0.8099413368265765</v>
       </c>
       <c r="AK8">
-        <v>0.1527149638375051</v>
+        <v>0.6773570861929692</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1454,7 +1460,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>China Everbright Bank Company Limited (SHSE:601818)</t>
+          <t>Bank of Communications Co., Ltd. (SEHK:3328)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1463,13 +1469,13 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.026</v>
+        <v>0.0216</v>
       </c>
       <c r="E9">
-        <v>0.0217</v>
+        <v>0.0382</v>
       </c>
       <c r="F9">
-        <v>-0.174</v>
+        <v>0.0146</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1484,28 +1490,28 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>5918.6</v>
+        <v>13151.6</v>
       </c>
       <c r="L9">
-        <v>0.4394825947487228</v>
+        <v>0.4579439252336449</v>
       </c>
       <c r="M9">
-        <v>2304.3384</v>
+        <v>5866.753299999999</v>
       </c>
       <c r="N9">
-        <v>0.0780221843003413</v>
+        <v>0.0831147348915227</v>
       </c>
       <c r="O9">
-        <v>0.3893384246274457</v>
+        <v>0.4460866586575017</v>
       </c>
       <c r="P9">
-        <v>2304.3384</v>
+        <v>5866.753299999999</v>
       </c>
       <c r="Q9">
-        <v>0.0780221843003413</v>
+        <v>0.0831147348915227</v>
       </c>
       <c r="R9">
-        <v>0.3893384246274457</v>
+        <v>0.4460866586575017</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1514,55 +1520,55 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>17130.9</v>
+        <v>22847.1</v>
       </c>
       <c r="V9">
-        <v>0.5800320981634975</v>
+        <v>0.3236765826748004</v>
       </c>
       <c r="W9">
-        <v>0.09065302465212098</v>
+        <v>0.09441002706330805</v>
       </c>
       <c r="X9">
-        <v>0.1840873109489738</v>
+        <v>0.1633665917290729</v>
       </c>
       <c r="Y9">
-        <v>-0.09343428629685281</v>
+        <v>-0.0689565646657649</v>
       </c>
       <c r="Z9">
-        <v>0.05239690797859178</v>
+        <v>0.05793543922929735</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.06351211384848231</v>
+        <v>0.06286841138178637</v>
       </c>
       <c r="AC9">
-        <v>-0.06351211384848231</v>
+        <v>-0.06286841138178637</v>
       </c>
       <c r="AD9">
-        <v>222933.1</v>
+        <v>439101.7</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>222933.1</v>
+        <v>439101.7</v>
       </c>
       <c r="AG9">
-        <v>205802.2</v>
+        <v>416254.6</v>
       </c>
       <c r="AH9">
-        <v>0.8830170219929298</v>
+        <v>0.8615109363985294</v>
       </c>
       <c r="AI9">
-        <v>0.7285421614260704</v>
+        <v>0.7299054451134341</v>
       </c>
       <c r="AJ9">
-        <v>0.8745014587616207</v>
+        <v>0.8550117410044515</v>
       </c>
       <c r="AK9">
-        <v>0.7124437459323982</v>
+        <v>0.7192428378892076</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1579,7 +1585,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ping An Bank Co., Ltd. (SZSE:000001)</t>
+          <t>China Construction Bank Corporation (SEHK:939)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1588,13 +1594,13 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.0524</v>
+        <v>0.0312</v>
       </c>
       <c r="E10">
-        <v>0.107</v>
+        <v>0.046</v>
       </c>
       <c r="F10">
-        <v>0.046</v>
+        <v>0.00481</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1609,28 +1615,28 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>6636.1</v>
+        <v>47469.5</v>
       </c>
       <c r="L10">
-        <v>0.4611413005712062</v>
+        <v>0.5379845822217286</v>
       </c>
       <c r="M10">
-        <v>1070.1</v>
+        <v>21250.935</v>
       </c>
       <c r="N10">
-        <v>0.03440128076537304</v>
+        <v>0.1001830794687938</v>
       </c>
       <c r="O10">
-        <v>0.1612543512002531</v>
+        <v>0.447675560096483</v>
       </c>
       <c r="P10">
-        <v>1070.1</v>
+        <v>21250.935</v>
       </c>
       <c r="Q10">
-        <v>0.03440128076537304</v>
+        <v>0.1001830794687938</v>
       </c>
       <c r="R10">
-        <v>0.1612543512002531</v>
+        <v>0.447675560096483</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1639,55 +1645,55 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>39585.6</v>
+        <v>197560.6</v>
       </c>
       <c r="V10">
-        <v>1.272586991744464</v>
+        <v>0.9313580456437599</v>
       </c>
       <c r="W10">
-        <v>0.1085898585538588</v>
+        <v>0.1148303772726833</v>
       </c>
       <c r="X10">
-        <v>0.1363975747985429</v>
+        <v>0.1084312357474564</v>
       </c>
       <c r="Y10">
-        <v>-0.02780771624468405</v>
+        <v>0.006399141525226845</v>
       </c>
       <c r="Z10">
-        <v>0.0906754948192993</v>
+        <v>0.1183040685316712</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.06373759122272799</v>
+        <v>0.06288774175452244</v>
       </c>
       <c r="AC10">
-        <v>-0.06373759122272799</v>
+        <v>-0.06288774175452244</v>
       </c>
       <c r="AD10">
-        <v>139523.1</v>
+        <v>570811.7</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>139523.1</v>
+        <v>570811.7</v>
       </c>
       <c r="AG10">
-        <v>99937.5</v>
+        <v>373251.1</v>
       </c>
       <c r="AH10">
-        <v>0.8176962365827715</v>
+        <v>0.7290686670770041</v>
       </c>
       <c r="AI10">
-        <v>0.6661553159703274</v>
+        <v>0.5449576554240744</v>
       </c>
       <c r="AJ10">
-        <v>0.7626261123180859</v>
+        <v>0.6376304917846273</v>
       </c>
       <c r="AK10">
-        <v>0.5883532115033759</v>
+        <v>0.4391800647078293</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1704,7 +1710,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Postal Savings Bank of China Co., Ltd. (SEHK:1658)</t>
+          <t>China CITIC Bank Corporation Limited (SEHK:998)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1713,13 +1719,13 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.08199999999999999</v>
+        <v>0.0567</v>
       </c>
       <c r="E11">
-        <v>0.0761</v>
+        <v>0.0682</v>
       </c>
       <c r="F11">
-        <v>0.0148</v>
+        <v>-0.00461</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1734,85 +1740,85 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>12322</v>
+        <v>9610</v>
       </c>
       <c r="L11">
-        <v>0.2708173532340058</v>
+        <v>0.4466090706720514</v>
       </c>
       <c r="M11">
-        <v>5751.343800000001</v>
+        <v>3713.5</v>
       </c>
       <c r="N11">
-        <v>0.07833323753941285</v>
+        <v>0.07842843233950525</v>
       </c>
       <c r="O11">
-        <v>0.4667540821295245</v>
+        <v>0.386420395421436</v>
       </c>
       <c r="P11">
-        <v>5751.343800000001</v>
+        <v>3212.3</v>
       </c>
       <c r="Q11">
-        <v>0.07833323753941285</v>
+        <v>0.06784318115098767</v>
       </c>
       <c r="R11">
-        <v>0.4667540821295245</v>
+        <v>0.3342663891779397</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>501.1999999999998</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>0.1349670122525918</v>
       </c>
       <c r="U11">
-        <v>53255.8</v>
+        <v>33779.6</v>
       </c>
       <c r="V11">
-        <v>0.725343393964983</v>
+        <v>0.7134188967431133</v>
       </c>
       <c r="W11">
-        <v>0.09839275333618669</v>
+        <v>0.1050179109631705</v>
       </c>
       <c r="X11">
-        <v>0.08205852752123782</v>
+        <v>0.1499790302065844</v>
       </c>
       <c r="Y11">
-        <v>0.01633422581494887</v>
+        <v>-0.04496111924341388</v>
       </c>
       <c r="Z11">
-        <v>0.2331527866029885</v>
+        <v>0.07336225633507497</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.06405253395640077</v>
+        <v>0.06294847053589306</v>
       </c>
       <c r="AC11">
-        <v>-0.06405253395640077</v>
+        <v>-0.06294847053589306</v>
       </c>
       <c r="AD11">
-        <v>73083.2</v>
+        <v>253817.7</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>73083.2</v>
+        <v>253817.7</v>
       </c>
       <c r="AG11">
-        <v>19827.39999999999</v>
+        <v>220038.1</v>
       </c>
       <c r="AH11">
-        <v>0.4988454295322948</v>
+        <v>0.8427817028847155</v>
       </c>
       <c r="AI11">
-        <v>0.3316976110466626</v>
+        <v>0.6820540918779417</v>
       </c>
       <c r="AJ11">
-        <v>0.2126287816799983</v>
+        <v>0.8229199624514281</v>
       </c>
       <c r="AK11">
-        <v>0.1186736495585814</v>
+        <v>0.6503122731689787</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1829,7 +1835,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Shanghai Pudong Development Bank Co., Ltd. (SHSE:600000)</t>
+          <t>Agricultural Bank of China Limited (SEHK:1288)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1838,13 +1844,13 @@
         </is>
       </c>
       <c r="D12">
-        <v>-0.035</v>
+        <v>0.033</v>
       </c>
       <c r="E12">
-        <v>-0.06370000000000001</v>
+        <v>0.0546</v>
       </c>
       <c r="F12">
-        <v>0.118</v>
+        <v>0.0216</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1859,85 +1865,85 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>6264</v>
+        <v>39400.1</v>
       </c>
       <c r="L12">
-        <v>0.4410460056609353</v>
+        <v>0.4888926114120151</v>
       </c>
       <c r="M12">
-        <v>3945.3</v>
+        <v>30483.8</v>
       </c>
       <c r="N12">
-        <v>0.09534408259142187</v>
+        <v>0.1214058220535179</v>
       </c>
       <c r="O12">
-        <v>0.6298371647509579</v>
+        <v>0.7736985439123252</v>
       </c>
       <c r="P12">
-        <v>3945.3</v>
+        <v>13376.4</v>
       </c>
       <c r="Q12">
-        <v>0.09534408259142187</v>
+        <v>0.05327330707184393</v>
       </c>
       <c r="R12">
-        <v>0.6298371647509579</v>
+        <v>0.3395016763916843</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>17107.4</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>0.561196438764196</v>
       </c>
       <c r="U12">
-        <v>61446.3</v>
+        <v>396326.5</v>
       </c>
       <c r="V12">
-        <v>1.484941855407012</v>
+        <v>1.578423442421665</v>
       </c>
       <c r="W12">
-        <v>0.06386225979012317</v>
+        <v>0.105090137235635</v>
       </c>
       <c r="X12">
-        <v>0.1929374315812532</v>
+        <v>0.1043833466542913</v>
       </c>
       <c r="Y12">
-        <v>-0.1290751717911301</v>
+        <v>0.0007067905813436526</v>
       </c>
       <c r="Z12">
-        <v>0.04015147338826294</v>
+        <v>0.1462374086725014</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.06442176350752948</v>
+        <v>0.062990941837286</v>
       </c>
       <c r="AC12">
-        <v>-0.06442176350752948</v>
+        <v>-0.062990941837286</v>
       </c>
       <c r="AD12">
-        <v>335864</v>
+        <v>610369.7</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>335864</v>
+        <v>610369.7</v>
       </c>
       <c r="AG12">
-        <v>274417.7</v>
+        <v>214043.2</v>
       </c>
       <c r="AH12">
-        <v>0.8903106639847569</v>
+        <v>0.7085295216329305</v>
       </c>
       <c r="AI12">
-        <v>0.7631940606730462</v>
+        <v>0.5871638118288982</v>
       </c>
       <c r="AJ12">
-        <v>0.868967847413515</v>
+        <v>0.4601760398578214</v>
       </c>
       <c r="AK12">
-        <v>0.724763852885597</v>
+        <v>0.3327809351900005</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -1954,7 +1960,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>China Merchants Bank Co., Ltd. (SHSE:600036)</t>
+          <t>Industrial and Commercial Bank of China Limited (SEHK:1398)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1963,13 +1969,13 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.0725</v>
+        <v>0.00369</v>
       </c>
       <c r="E13">
-        <v>0.1</v>
+        <v>0.033</v>
       </c>
       <c r="F13">
-        <v>0.0285</v>
+        <v>0.009389999999999999</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1984,85 +1990,85 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>20799.2</v>
+        <v>51941.7</v>
       </c>
       <c r="L13">
-        <v>0.4966688476361952</v>
+        <v>0.5595357104384359</v>
       </c>
       <c r="M13">
-        <v>7077.3</v>
+        <v>28273.5</v>
       </c>
       <c r="N13">
-        <v>0.0525364053616485</v>
+        <v>0.09009271677648842</v>
       </c>
       <c r="O13">
-        <v>0.3402678949190354</v>
+        <v>0.5443314331259855</v>
       </c>
       <c r="P13">
-        <v>7077.3</v>
+        <v>16868.6</v>
       </c>
       <c r="Q13">
-        <v>0.0525364053616485</v>
+        <v>0.05375132198758104</v>
       </c>
       <c r="R13">
-        <v>0.3402678949190354</v>
+        <v>0.3247602600607989</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>11404.9</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>0.4033777211876846</v>
       </c>
       <c r="U13">
-        <v>2184.8</v>
+        <v>432605.6</v>
       </c>
       <c r="V13">
-        <v>0.01621826663192596</v>
+        <v>1.378485641916382</v>
       </c>
       <c r="W13">
-        <v>0.1541110709353124</v>
+        <v>0.107626142143497</v>
       </c>
       <c r="X13">
-        <v>0.07996128533455701</v>
+        <v>0.09300278018562289</v>
       </c>
       <c r="Y13">
-        <v>0.07414978560075536</v>
+        <v>0.01462336195787407</v>
       </c>
       <c r="Z13">
-        <v>0.1644920912807102</v>
+        <v>0.258150311168039</v>
       </c>
       <c r="AA13">
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.06458182697923021</v>
+        <v>0.06338763198802388</v>
       </c>
       <c r="AC13">
-        <v>-0.06458182697923021</v>
+        <v>-0.06338763198802388</v>
       </c>
       <c r="AD13">
-        <v>115946.3</v>
+        <v>533390.1</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>115946.3</v>
+        <v>533390.1</v>
       </c>
       <c r="AG13">
-        <v>113761.5</v>
+        <v>100784.5</v>
       </c>
       <c r="AH13">
-        <v>0.462566614510733</v>
+        <v>0.6295792293070676</v>
       </c>
       <c r="AI13">
-        <v>0.4122300598010424</v>
+        <v>0.4882033189472077</v>
       </c>
       <c r="AJ13">
-        <v>0.4578410279071677</v>
+        <v>0.2430819524412269</v>
       </c>
       <c r="AK13">
-        <v>0.4076286758119142</v>
+        <v>0.1527149638375051</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2079,7 +2085,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Shanghai Rural Commercial Bank Co., Ltd. (SHSE:601825)</t>
+          <t>China Everbright Bank Company Limited (SHSE:601818)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2088,10 +2094,13 @@
         </is>
       </c>
       <c r="D14">
-        <v>0.0688</v>
+        <v>0.026</v>
       </c>
       <c r="E14">
-        <v>0.0745</v>
+        <v>0.0217</v>
+      </c>
+      <c r="F14">
+        <v>-0.174</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2106,28 +2115,28 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>1743</v>
+        <v>5918.6</v>
       </c>
       <c r="L14">
-        <v>0.5161385845424933</v>
+        <v>0.4394825947487228</v>
       </c>
       <c r="M14">
-        <v>1218</v>
+        <v>2304.3384</v>
       </c>
       <c r="N14">
-        <v>0.1083205862473765</v>
+        <v>0.0780221843003413</v>
       </c>
       <c r="O14">
-        <v>0.6987951807228916</v>
+        <v>0.3893384246274457</v>
       </c>
       <c r="P14">
-        <v>1218</v>
+        <v>2304.3384</v>
       </c>
       <c r="Q14">
-        <v>0.1083205862473765</v>
+        <v>0.0780221843003413</v>
       </c>
       <c r="R14">
-        <v>0.6987951807228916</v>
+        <v>0.3893384246274457</v>
       </c>
       <c r="S14">
         <v>0</v>
@@ -2136,55 +2145,55 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>5334.7</v>
+        <v>17130.9</v>
       </c>
       <c r="V14">
-        <v>0.4744317171214115</v>
+        <v>0.5800320981634975</v>
       </c>
       <c r="W14">
-        <v>0.1156809780119862</v>
+        <v>0.09065302465212098</v>
       </c>
       <c r="X14">
-        <v>0.116549329645686</v>
+        <v>0.1840262560245701</v>
       </c>
       <c r="Y14">
-        <v>-0.0008683516336997349</v>
+        <v>-0.09337323137244909</v>
       </c>
       <c r="Z14">
-        <v>0.07604605549087649</v>
+        <v>0.05239690797859178</v>
       </c>
       <c r="AA14">
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.06472873727423292</v>
+        <v>0.06350497146160357</v>
       </c>
       <c r="AC14">
-        <v>-0.06472873727423292</v>
+        <v>-0.06350497146160357</v>
       </c>
       <c r="AD14">
-        <v>36101.1</v>
+        <v>222933.1</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>36101.1</v>
+        <v>222933.1</v>
       </c>
       <c r="AG14">
-        <v>30766.4</v>
+        <v>205802.2</v>
       </c>
       <c r="AH14">
-        <v>0.7625033002080451</v>
+        <v>0.8830170219929298</v>
       </c>
       <c r="AI14">
-        <v>0.6719534076864661</v>
+        <v>0.7285421614260704</v>
       </c>
       <c r="AJ14">
-        <v>0.7323450160434936</v>
+        <v>0.8745014587616207</v>
       </c>
       <c r="AK14">
-        <v>0.6357889603210521</v>
+        <v>0.7124437459323982</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2201,7 +2210,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>China Bohai Bank Co., Ltd. (SEHK:9668)</t>
+          <t>Ping An Bank Co., Ltd. (SZSE:000001)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2210,10 +2219,13 @@
         </is>
       </c>
       <c r="D15">
-        <v>-0.017</v>
+        <v>0.0524</v>
       </c>
       <c r="E15">
-        <v>-0.0605</v>
+        <v>0.107</v>
+      </c>
+      <c r="F15">
+        <v>0.046</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2228,28 +2240,28 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>643.9</v>
+        <v>6636.1</v>
       </c>
       <c r="L15">
-        <v>0.3121485359705254</v>
+        <v>0.4611413005712062</v>
       </c>
       <c r="M15">
-        <v>130.7</v>
+        <v>1070.1</v>
       </c>
       <c r="N15">
-        <v>0.06421973270440251</v>
+        <v>0.03440128076537304</v>
       </c>
       <c r="O15">
-        <v>0.2029818294766268</v>
+        <v>0.1612543512002531</v>
       </c>
       <c r="P15">
-        <v>130.7</v>
+        <v>1070.1</v>
       </c>
       <c r="Q15">
-        <v>0.06421973270440251</v>
+        <v>0.03440128076537304</v>
       </c>
       <c r="R15">
-        <v>0.2029818294766268</v>
+        <v>0.1612543512002531</v>
       </c>
       <c r="S15">
         <v>0</v>
@@ -2258,55 +2270,55 @@
         <v>0</v>
       </c>
       <c r="U15">
-        <v>5608.1</v>
+        <v>39585.6</v>
       </c>
       <c r="V15">
-        <v>2.755552279874214</v>
+        <v>1.272586991744464</v>
       </c>
       <c r="W15">
-        <v>0.04088305883249311</v>
+        <v>0.1085898585538588</v>
       </c>
       <c r="X15">
-        <v>0.5877145275547386</v>
+        <v>0.1363575752639325</v>
       </c>
       <c r="Y15">
-        <v>-0.5468314687222455</v>
+        <v>-0.02776771671007362</v>
       </c>
       <c r="Z15">
-        <v>0.02793350558182616</v>
+        <v>0.0906754948192993</v>
       </c>
       <c r="AA15">
         <v>0</v>
       </c>
       <c r="AB15">
-        <v>0.06568446862480602</v>
+        <v>0.06373029915703356</v>
       </c>
       <c r="AC15">
-        <v>-0.06568446862480602</v>
+        <v>-0.06373029915703356</v>
       </c>
       <c r="AD15">
-        <v>68121.10000000001</v>
+        <v>139523.1</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>68121.10000000001</v>
+        <v>139523.1</v>
       </c>
       <c r="AG15">
-        <v>62513.00000000001</v>
+        <v>99937.5</v>
       </c>
       <c r="AH15">
-        <v>0.9709904883809437</v>
+        <v>0.8176962365827715</v>
       </c>
       <c r="AI15">
-        <v>0.8067626270760894</v>
+        <v>0.6661553159703274</v>
       </c>
       <c r="AJ15">
-        <v>0.9684700735264501</v>
+        <v>0.7626261123180859</v>
       </c>
       <c r="AK15">
-        <v>0.7930153051839731</v>
+        <v>0.5883532115033759</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2323,7 +2335,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>China Zheshang Bank Co., Ltd (SEHK:2016)</t>
+          <t>Postal Savings Bank of China Co., Ltd. (SEHK:1658)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2332,10 +2344,13 @@
         </is>
       </c>
       <c r="D16">
-        <v>0.0674</v>
+        <v>0.08199999999999999</v>
       </c>
       <c r="E16">
-        <v>0.0338</v>
+        <v>0.0761</v>
+      </c>
+      <c r="F16">
+        <v>0.0148</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2350,28 +2365,28 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>2166.9</v>
+        <v>12322</v>
       </c>
       <c r="L16">
-        <v>0.3951384963256077</v>
+        <v>0.2708173532340058</v>
       </c>
       <c r="M16">
-        <v>797.8</v>
+        <v>5751.343800000001</v>
       </c>
       <c r="N16">
-        <v>0.07759643628299648</v>
+        <v>0.07833323753941285</v>
       </c>
       <c r="O16">
-        <v>0.3681757349208546</v>
+        <v>0.4667540821295245</v>
       </c>
       <c r="P16">
-        <v>797.8</v>
+        <v>5751.343800000001</v>
       </c>
       <c r="Q16">
-        <v>0.07759643628299648</v>
+        <v>0.07833323753941285</v>
       </c>
       <c r="R16">
-        <v>0.3681757349208546</v>
+        <v>0.4667540821295245</v>
       </c>
       <c r="S16">
         <v>0</v>
@@ -2380,55 +2395,55 @@
         <v>0</v>
       </c>
       <c r="U16">
-        <v>19510.6</v>
+        <v>53255.8</v>
       </c>
       <c r="V16">
-        <v>1.89765985177116</v>
+        <v>0.725343393964983</v>
       </c>
       <c r="W16">
-        <v>0.08615630516723127</v>
+        <v>0.09839275333618669</v>
       </c>
       <c r="X16">
-        <v>0.2264395264810633</v>
+        <v>0.08204251909905065</v>
       </c>
       <c r="Y16">
-        <v>-0.140283221313832</v>
+        <v>0.01635023423713604</v>
       </c>
       <c r="Z16">
-        <v>0.05267348757866588</v>
+        <v>0.2331527866029885</v>
       </c>
       <c r="AA16">
         <v>0</v>
       </c>
       <c r="AB16">
-        <v>0.06573834014289463</v>
+        <v>0.06404451126245569</v>
       </c>
       <c r="AC16">
-        <v>-0.06573834014289463</v>
+        <v>-0.06404451126245569</v>
       </c>
       <c r="AD16">
-        <v>105573</v>
+        <v>73083.2</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>105573</v>
+        <v>73083.2</v>
       </c>
       <c r="AG16">
-        <v>86062.39999999999</v>
+        <v>19827.39999999999</v>
       </c>
       <c r="AH16">
-        <v>0.9112558521730725</v>
+        <v>0.4988454295322948</v>
       </c>
       <c r="AI16">
-        <v>0.7880805182357411</v>
+        <v>0.3316976110466626</v>
       </c>
       <c r="AJ16">
-        <v>0.8932842590805014</v>
+        <v>0.2126287816799983</v>
       </c>
       <c r="AK16">
-        <v>0.7519545379881103</v>
+        <v>0.1186736495585814</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -2445,7 +2460,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hua Xia Bank Co., Limited (SHSE:600015)</t>
+          <t>Shanghai Pudong Development Bank Co., Ltd. (SHSE:600000)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2454,10 +2469,13 @@
         </is>
       </c>
       <c r="D17">
-        <v>0.0583</v>
+        <v>-0.035</v>
       </c>
       <c r="E17">
-        <v>0.0452</v>
+        <v>-0.06370000000000001</v>
+      </c>
+      <c r="F17">
+        <v>0.118</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2472,85 +2490,85 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>3837.6</v>
+        <v>6264</v>
       </c>
       <c r="L17">
-        <v>0.3840326631908655</v>
+        <v>0.4410460056609353</v>
       </c>
       <c r="M17">
-        <v>5749.5</v>
+        <v>3945.3</v>
       </c>
       <c r="N17">
-        <v>0.3292031445928691</v>
+        <v>0.09534408259142187</v>
       </c>
       <c r="O17">
-        <v>1.498202001250782</v>
+        <v>0.6298371647509579</v>
       </c>
       <c r="P17">
-        <v>47</v>
+        <v>3945.3</v>
       </c>
       <c r="Q17">
-        <v>0.00269111188727104</v>
+        <v>0.09534408259142187</v>
       </c>
       <c r="R17">
-        <v>0.01224723785699395</v>
+        <v>0.6298371647509579</v>
       </c>
       <c r="S17">
-        <v>5702.5</v>
+        <v>0</v>
       </c>
       <c r="T17">
-        <v>0.9918253761196626</v>
+        <v>0</v>
       </c>
       <c r="U17">
-        <v>20356.1</v>
+        <v>61446.3</v>
       </c>
       <c r="V17">
-        <v>1.165543461456979</v>
+        <v>1.484941855407012</v>
       </c>
       <c r="W17">
-        <v>0.09038047126152542</v>
+        <v>0.06386225979012317</v>
       </c>
       <c r="X17">
-        <v>0.219876431080933</v>
+        <v>0.1928724692596888</v>
       </c>
       <c r="Y17">
-        <v>-0.1294959598194076</v>
+        <v>-0.1290102094695656</v>
       </c>
       <c r="Z17">
-        <v>0.06017778307718526</v>
+        <v>0.04015147338826294</v>
       </c>
       <c r="AA17">
         <v>0</v>
       </c>
       <c r="AB17">
-        <v>0.06574145033183033</v>
+        <v>0.06441463783361107</v>
       </c>
       <c r="AC17">
-        <v>-0.06574145033183033</v>
+        <v>-0.06441463783361107</v>
       </c>
       <c r="AD17">
-        <v>171973.9</v>
+        <v>335864</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>171973.9</v>
+        <v>335864</v>
       </c>
       <c r="AG17">
-        <v>151617.8</v>
+        <v>274417.7</v>
       </c>
       <c r="AH17">
-        <v>0.9078071651636307</v>
+        <v>0.8903106639847569</v>
       </c>
       <c r="AI17">
-        <v>0.7724661175036394</v>
+        <v>0.7631940606730462</v>
       </c>
       <c r="AJ17">
-        <v>0.8967079423264473</v>
+        <v>0.868967847413515</v>
       </c>
       <c r="AK17">
-        <v>0.7495679119766495</v>
+        <v>0.724763852885597</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -2567,120 +2585,849 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>China Merchants Bank Co., Ltd. (SHSE:600036)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D18">
+        <v>0.0725</v>
+      </c>
+      <c r="E18">
+        <v>0.1</v>
+      </c>
+      <c r="F18">
+        <v>0.0285</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>20799.2</v>
+      </c>
+      <c r="L18">
+        <v>0.4966688476361952</v>
+      </c>
+      <c r="M18">
+        <v>7077.3</v>
+      </c>
+      <c r="N18">
+        <v>0.0525364053616485</v>
+      </c>
+      <c r="O18">
+        <v>0.3402678949190354</v>
+      </c>
+      <c r="P18">
+        <v>7077.3</v>
+      </c>
+      <c r="Q18">
+        <v>0.0525364053616485</v>
+      </c>
+      <c r="R18">
+        <v>0.3402678949190354</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>2184.8</v>
+      </c>
+      <c r="V18">
+        <v>0.01621826663192596</v>
+      </c>
+      <c r="W18">
+        <v>0.1541110709353124</v>
+      </c>
+      <c r="X18">
+        <v>0.07994620286112308</v>
+      </c>
+      <c r="Y18">
+        <v>0.07416486807418929</v>
+      </c>
+      <c r="Z18">
+        <v>0.1644920912807102</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>0.06457372115447105</v>
+      </c>
+      <c r="AC18">
+        <v>-0.06457372115447105</v>
+      </c>
+      <c r="AD18">
+        <v>115946.3</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>115946.3</v>
+      </c>
+      <c r="AG18">
+        <v>113761.5</v>
+      </c>
+      <c r="AH18">
+        <v>0.462566614510733</v>
+      </c>
+      <c r="AI18">
+        <v>0.4122300598010424</v>
+      </c>
+      <c r="AJ18">
+        <v>0.4578410279071677</v>
+      </c>
+      <c r="AK18">
+        <v>0.4076286758119142</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Shanghai Rural Commercial Bank Co., Ltd. (SHSE:601825)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D19">
+        <v>0.0688</v>
+      </c>
+      <c r="E19">
+        <v>0.0745</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>1743</v>
+      </c>
+      <c r="L19">
+        <v>0.5161385845424933</v>
+      </c>
+      <c r="M19">
+        <v>1218</v>
+      </c>
+      <c r="N19">
+        <v>0.1083205862473765</v>
+      </c>
+      <c r="O19">
+        <v>0.6987951807228916</v>
+      </c>
+      <c r="P19">
+        <v>1218</v>
+      </c>
+      <c r="Q19">
+        <v>0.1083205862473765</v>
+      </c>
+      <c r="R19">
+        <v>0.6987951807228916</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>5334.7</v>
+      </c>
+      <c r="V19">
+        <v>0.4744317171214115</v>
+      </c>
+      <c r="W19">
+        <v>0.1156809780119862</v>
+      </c>
+      <c r="X19">
+        <v>0.1165180932658367</v>
+      </c>
+      <c r="Y19">
+        <v>-0.0008371152538504817</v>
+      </c>
+      <c r="Z19">
+        <v>0.07604605549087649</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0.06472131873710528</v>
+      </c>
+      <c r="AC19">
+        <v>-0.06472131873710528</v>
+      </c>
+      <c r="AD19">
+        <v>36101.1</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>36101.1</v>
+      </c>
+      <c r="AG19">
+        <v>30766.4</v>
+      </c>
+      <c r="AH19">
+        <v>0.7625033002080451</v>
+      </c>
+      <c r="AI19">
+        <v>0.6719534076864661</v>
+      </c>
+      <c r="AJ19">
+        <v>0.7323450160434936</v>
+      </c>
+      <c r="AK19">
+        <v>0.6357889603210521</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Jilin Jiutai Rural Commercial Bank Corporation Limited (SEHK:6122)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D20">
+        <v>-0.0876</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>-41.7</v>
+      </c>
+      <c r="L20">
+        <v>-0.114215283483977</v>
+      </c>
+      <c r="M20">
+        <v>-0</v>
+      </c>
+      <c r="N20">
+        <v>-0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>-0</v>
+      </c>
+      <c r="Q20">
+        <v>-0</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>3006.9</v>
+      </c>
+      <c r="V20">
+        <v>9.297773654916513</v>
+      </c>
+      <c r="W20">
+        <v>-0.01805663808781502</v>
+      </c>
+      <c r="X20">
+        <v>0.110882644082463</v>
+      </c>
+      <c r="Y20">
+        <v>-0.128939282170278</v>
+      </c>
+      <c r="Z20">
+        <v>1.157100751117167</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0.06477493877926577</v>
+      </c>
+      <c r="AC20">
+        <v>-0.06477493877926577</v>
+      </c>
+      <c r="AD20">
+        <v>921.2</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>921.2</v>
+      </c>
+      <c r="AG20">
+        <v>-2085.7</v>
+      </c>
+      <c r="AH20">
+        <v>0.7401574803149608</v>
+      </c>
+      <c r="AI20">
+        <v>0.2518522568827405</v>
+      </c>
+      <c r="AJ20">
+        <v>1.183510185552971</v>
+      </c>
+      <c r="AK20">
+        <v>-3.204824830977258</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>China Bohai Bank Co., Ltd. (SEHK:9668)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D21">
+        <v>-0.017</v>
+      </c>
+      <c r="E21">
+        <v>-0.0605</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>643.9</v>
+      </c>
+      <c r="L21">
+        <v>0.3121485359705254</v>
+      </c>
+      <c r="M21">
+        <v>130.7</v>
+      </c>
+      <c r="N21">
+        <v>0.06421973270440251</v>
+      </c>
+      <c r="O21">
+        <v>0.2029818294766268</v>
+      </c>
+      <c r="P21">
+        <v>130.7</v>
+      </c>
+      <c r="Q21">
+        <v>0.06421973270440251</v>
+      </c>
+      <c r="R21">
+        <v>0.2029818294766268</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>5608.1</v>
+      </c>
+      <c r="V21">
+        <v>2.755552279874214</v>
+      </c>
+      <c r="W21">
+        <v>0.04088305883249311</v>
+      </c>
+      <c r="X21">
+        <v>0.5874752680718107</v>
+      </c>
+      <c r="Y21">
+        <v>-0.5465922092393176</v>
+      </c>
+      <c r="Z21">
+        <v>0.02793350558182616</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0.06567752782405606</v>
+      </c>
+      <c r="AC21">
+        <v>-0.06567752782405606</v>
+      </c>
+      <c r="AD21">
+        <v>68121.10000000001</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>68121.10000000001</v>
+      </c>
+      <c r="AG21">
+        <v>62513.00000000001</v>
+      </c>
+      <c r="AH21">
+        <v>0.9709904883809437</v>
+      </c>
+      <c r="AI21">
+        <v>0.8067626270760894</v>
+      </c>
+      <c r="AJ21">
+        <v>0.9684700735264501</v>
+      </c>
+      <c r="AK21">
+        <v>0.7930153051839731</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>China Zheshang Bank Co., Ltd (SEHK:2016)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D22">
+        <v>0.0674</v>
+      </c>
+      <c r="E22">
+        <v>0.0338</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>2166.9</v>
+      </c>
+      <c r="L22">
+        <v>0.3951384963256077</v>
+      </c>
+      <c r="M22">
+        <v>797.8</v>
+      </c>
+      <c r="N22">
+        <v>0.07759643628299648</v>
+      </c>
+      <c r="O22">
+        <v>0.3681757349208546</v>
+      </c>
+      <c r="P22">
+        <v>797.8</v>
+      </c>
+      <c r="Q22">
+        <v>0.07759643628299648</v>
+      </c>
+      <c r="R22">
+        <v>0.3681757349208546</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>19510.6</v>
+      </c>
+      <c r="V22">
+        <v>1.89765985177116</v>
+      </c>
+      <c r="W22">
+        <v>0.08615630516723127</v>
+      </c>
+      <c r="X22">
+        <v>0.2263597727237739</v>
+      </c>
+      <c r="Y22">
+        <v>-0.1402034675565426</v>
+      </c>
+      <c r="Z22">
+        <v>0.05267348757866588</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0.06573126246366799</v>
+      </c>
+      <c r="AC22">
+        <v>-0.06573126246366799</v>
+      </c>
+      <c r="AD22">
+        <v>105573</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>105573</v>
+      </c>
+      <c r="AG22">
+        <v>86062.39999999999</v>
+      </c>
+      <c r="AH22">
+        <v>0.9112558521730725</v>
+      </c>
+      <c r="AI22">
+        <v>0.7880805182357411</v>
+      </c>
+      <c r="AJ22">
+        <v>0.8932842590805014</v>
+      </c>
+      <c r="AK22">
+        <v>0.7519545379881103</v>
+      </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Hua Xia Bank Co., Limited (SHSE:600015)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D23">
+        <v>0.0583</v>
+      </c>
+      <c r="E23">
+        <v>0.0452</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>3837.6</v>
+      </c>
+      <c r="L23">
+        <v>0.3840326631908655</v>
+      </c>
+      <c r="M23">
+        <v>5749.5</v>
+      </c>
+      <c r="N23">
+        <v>0.3292031445928691</v>
+      </c>
+      <c r="O23">
+        <v>1.498202001250782</v>
+      </c>
+      <c r="P23">
+        <v>47</v>
+      </c>
+      <c r="Q23">
+        <v>0.00269111188727104</v>
+      </c>
+      <c r="R23">
+        <v>0.01224723785699395</v>
+      </c>
+      <c r="S23">
+        <v>5702.5</v>
+      </c>
+      <c r="T23">
+        <v>0.9918253761196626</v>
+      </c>
+      <c r="U23">
+        <v>20356.1</v>
+      </c>
+      <c r="V23">
+        <v>1.165543461456979</v>
+      </c>
+      <c r="W23">
+        <v>0.09038047126152542</v>
+      </c>
+      <c r="X23">
+        <v>0.219799574981359</v>
+      </c>
+      <c r="Y23">
+        <v>-0.1294191037198336</v>
+      </c>
+      <c r="Z23">
+        <v>0.06017778307718526</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>0.06573436475013614</v>
+      </c>
+      <c r="AC23">
+        <v>-0.06573436475013614</v>
+      </c>
+      <c r="AD23">
+        <v>171973.9</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>171973.9</v>
+      </c>
+      <c r="AG23">
+        <v>151617.8</v>
+      </c>
+      <c r="AH23">
+        <v>0.9078071651636307</v>
+      </c>
+      <c r="AI23">
+        <v>0.7724661175036394</v>
+      </c>
+      <c r="AJ23">
+        <v>0.8967079423264473</v>
+      </c>
+      <c r="AK23">
+        <v>0.7495679119766495</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>China Minsheng Banking Corp., Ltd. (SHSE:600016)</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D18">
+      <c r="D24">
         <v>-0.04389999999999999</v>
       </c>
-      <c r="E18">
+      <c r="E24">
         <v>-0.0925</v>
       </c>
-      <c r="F18">
+      <c r="F24">
         <v>-0.0117</v>
       </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
-      <c r="K18">
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
         <v>4666.3</v>
       </c>
-      <c r="L18">
+      <c r="L24">
         <v>0.3637618004505804</v>
       </c>
-      <c r="M18">
+      <c r="M24">
         <v>7847.837600000001</v>
       </c>
-      <c r="N18">
+      <c r="N24">
         <v>0.3304338760678903</v>
       </c>
-      <c r="O18">
+      <c r="O24">
         <v>1.68181162805649</v>
       </c>
-      <c r="P18">
+      <c r="P24">
         <v>2145.3376</v>
       </c>
-      <c r="Q18">
+      <c r="Q24">
         <v>0.09032962387526791</v>
       </c>
-      <c r="R18">
+      <c r="R24">
         <v>0.4597513233182607</v>
       </c>
-      <c r="S18">
+      <c r="S24">
         <v>5702.5</v>
       </c>
-      <c r="T18">
+      <c r="T24">
         <v>0.7266332830332778</v>
       </c>
-      <c r="U18">
+      <c r="U24">
         <v>26109.1</v>
       </c>
-      <c r="V18">
+      <c r="V24">
         <v>1.099325897575168</v>
       </c>
-      <c r="W18">
+      <c r="W24">
         <v>0.05664394661293162</v>
       </c>
-      <c r="X18">
-        <v>0.2189512125328051</v>
-      </c>
-      <c r="Y18">
-        <v>-0.1623072659198734</v>
-      </c>
-      <c r="Z18">
+      <c r="X24">
+        <v>0.2188747649244232</v>
+      </c>
+      <c r="Y24">
+        <v>-0.1622308183114916</v>
+      </c>
+      <c r="Z24">
         <v>0.05752584041611938</v>
       </c>
-      <c r="AA18">
-        <v>0</v>
-      </c>
-      <c r="AB18">
-        <v>0.06574190833194742</v>
-      </c>
-      <c r="AC18">
-        <v>-0.06574190833194742</v>
-      </c>
-      <c r="AD18">
+      <c r="AA24">
+        <v>0</v>
+      </c>
+      <c r="AB24">
+        <v>0.06573482158655186</v>
+      </c>
+      <c r="AC24">
+        <v>-0.06573482158655186</v>
+      </c>
+      <c r="AD24">
         <v>232451.9</v>
       </c>
-      <c r="AE18">
-        <v>0</v>
-      </c>
-      <c r="AF18">
+      <c r="AE24">
+        <v>0</v>
+      </c>
+      <c r="AF24">
         <v>232451.9</v>
       </c>
-      <c r="AG18">
+      <c r="AG24">
         <v>206342.8</v>
       </c>
-      <c r="AH18">
+      <c r="AH24">
         <v>0.9072993185064909</v>
       </c>
-      <c r="AI18">
+      <c r="AI24">
         <v>0.7161444662156333</v>
       </c>
-      <c r="AJ18">
+      <c r="AJ24">
         <v>0.8967803874000457</v>
       </c>
-      <c r="AK18">
+      <c r="AK24">
         <v>0.6913145284306528</v>
       </c>
-      <c r="AL18">
-        <v>0</v>
-      </c>
-      <c r="AM18">
+      <c r="AL24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
         <v>0</v>
       </c>
     </row>
